--- a/research/traditional_assets/database/data/oman/oman_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_chemical_specialty.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="msm_gici" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0898</v>
+        <v>-0.0444</v>
+      </c>
+      <c r="E2">
+        <v>-0.121</v>
       </c>
       <c r="G2">
-        <v>0.01690821256038648</v>
+        <v>0.01146881287726358</v>
       </c>
       <c r="H2">
-        <v>0.01497584541062802</v>
+        <v>0.01146881287726358</v>
       </c>
       <c r="I2">
-        <v>-0.05072463768115942</v>
+        <v>0.04346076458752515</v>
       </c>
       <c r="J2">
-        <v>-0.05072463768115942</v>
+        <v>0.03924550648371836</v>
       </c>
       <c r="K2">
-        <v>-0.096</v>
+        <v>0.27</v>
       </c>
       <c r="L2">
-        <v>-0.02318840579710145</v>
+        <v>0.05432595573440645</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.797</v>
+        <v>1.03</v>
       </c>
       <c r="V2">
-        <v>0.1623217922606925</v>
+        <v>0.2861111111111111</v>
       </c>
       <c r="W2">
-        <v>-0.01352112676056338</v>
+        <v>0.04047976011994003</v>
       </c>
       <c r="X2">
-        <v>0.1636767428467576</v>
+        <v>0.1166833912518183</v>
       </c>
       <c r="Y2">
-        <v>-0.177197869607321</v>
+        <v>-0.07620363113187827</v>
       </c>
       <c r="Z2">
-        <v>0.8143194335169158</v>
+        <v>0.841089862920968</v>
       </c>
       <c r="AA2">
-        <v>-0.04130605822187254</v>
+        <v>0.03300899766865464</v>
       </c>
       <c r="AB2">
-        <v>0.1630502915044985</v>
+        <v>0.1162342478538334</v>
       </c>
       <c r="AC2">
-        <v>-0.204356349726371</v>
+        <v>-0.08322525018517876</v>
       </c>
       <c r="AD2">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AG2">
-        <v>-0.761</v>
+        <v>-0.996</v>
       </c>
       <c r="AH2">
-        <v>0.007278608976951071</v>
+        <v>0.009356081452944415</v>
       </c>
       <c r="AI2">
-        <v>0.005368326871458396</v>
+        <v>0.00492468134414832</v>
       </c>
       <c r="AJ2">
-        <v>-0.1834176910098819</v>
+        <v>-0.3824884792626728</v>
       </c>
       <c r="AK2">
-        <v>-0.1287865967168726</v>
+        <v>-0.1695607763023493</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM2">
-        <v>-0.049</v>
+        <v>-0.075</v>
       </c>
       <c r="AN2">
-        <v>-0.3302752293577981</v>
+        <v>0.1046153846153846</v>
+      </c>
+      <c r="AO2">
+        <v>72</v>
       </c>
       <c r="AP2">
-        <v>6.98165137614679</v>
+        <v>-3.064615384615384</v>
       </c>
       <c r="AQ2">
-        <v>4.285714285714286</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="3">
@@ -713,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0898</v>
+        <v>-0.0444</v>
+      </c>
+      <c r="E3">
+        <v>-0.121</v>
       </c>
       <c r="G3">
-        <v>0.01690821256038648</v>
+        <v>0.01146881287726358</v>
       </c>
       <c r="H3">
-        <v>0.01497584541062802</v>
+        <v>0.01146881287726358</v>
       </c>
       <c r="I3">
-        <v>-0.05072463768115942</v>
+        <v>0.04346076458752515</v>
       </c>
       <c r="J3">
-        <v>-0.05072463768115942</v>
+        <v>0.03924550648371836</v>
       </c>
       <c r="K3">
-        <v>-0.096</v>
+        <v>0.27</v>
       </c>
       <c r="L3">
-        <v>-0.02318840579710145</v>
+        <v>0.05432595573440645</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +760,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.797</v>
+        <v>1.03</v>
       </c>
       <c r="V3">
-        <v>0.1623217922606925</v>
+        <v>0.2861111111111111</v>
       </c>
       <c r="W3">
-        <v>-0.01352112676056338</v>
+        <v>0.04047976011994003</v>
       </c>
       <c r="X3">
-        <v>0.1636767428467576</v>
+        <v>0.1166833912518183</v>
       </c>
       <c r="Y3">
-        <v>-0.177197869607321</v>
+        <v>-0.07620363113187827</v>
       </c>
       <c r="Z3">
-        <v>0.8143194335169158</v>
+        <v>0.841089862920968</v>
       </c>
       <c r="AA3">
-        <v>-0.04130605822187254</v>
+        <v>0.03300899766865464</v>
       </c>
       <c r="AB3">
-        <v>0.1630502915044985</v>
+        <v>0.1162342478538334</v>
       </c>
       <c r="AC3">
-        <v>-0.204356349726371</v>
+        <v>-0.08322525018517876</v>
       </c>
       <c r="AD3">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="AG3">
-        <v>-0.761</v>
+        <v>-0.996</v>
       </c>
       <c r="AH3">
-        <v>0.007278608976951071</v>
+        <v>0.009356081452944415</v>
       </c>
       <c r="AI3">
-        <v>0.005368326871458396</v>
+        <v>0.00492468134414832</v>
       </c>
       <c r="AJ3">
-        <v>-0.1834176910098819</v>
+        <v>-0.3824884792626728</v>
       </c>
       <c r="AK3">
-        <v>-0.1287865967168726</v>
+        <v>-0.1695607763023493</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM3">
-        <v>-0.049</v>
+        <v>-0.075</v>
       </c>
       <c r="AN3">
-        <v>-0.3302752293577981</v>
+        <v>0.1046153846153846</v>
+      </c>
+      <c r="AO3">
+        <v>72</v>
       </c>
       <c r="AP3">
-        <v>6.98165137614679</v>
+        <v>-3.064615384615384</v>
       </c>
       <c r="AQ3">
-        <v>4.285714285714286</v>
+        <v>-2.88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gulf International Chemicals SAOG (MSM:GICI)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MSM:GICI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chemical (Specialty)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>72</v>
+      </c>
+      <c r="F2">
+        <v>4.67101258254015</v>
+      </c>
+      <c r="G2">
+        <v>0.104615384615385</v>
+      </c>
+      <c r="H2">
+        <v>2.79538461538462</v>
+      </c>
+      <c r="I2">
+        <v>0.00935608145294442</v>
+      </c>
+      <c r="J2">
+        <v>0.25</v>
+      </c>
+      <c r="K2">
+        <v>3.6</v>
+      </c>
+      <c r="L2">
+        <v>2.79284842934129</v>
+      </c>
+      <c r="M2">
+        <v>2.604</v>
+      </c>
+      <c r="N2">
+        <v>2.67134842934129</v>
+      </c>
+      <c r="O2">
+        <v>0.034</v>
+      </c>
+      <c r="P2">
+        <v>0.9085</v>
+      </c>
+      <c r="Q2">
+        <v>0.116234247853833</v>
+      </c>
+      <c r="R2">
+        <v>0.114282022186489</v>
+      </c>
+      <c r="S2">
+        <v>0.0686778880671956</v>
+      </c>
+      <c r="T2">
+        <v>0.043265</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.116683391251818</v>
+      </c>
+      <c r="X2">
+        <v>0.137954362915319</v>
+      </c>
+      <c r="Y2">
+        <v>0.942749291456907</v>
+      </c>
+      <c r="Z2">
+        <v>1.2002264395632</v>
+      </c>
+      <c r="AA2">
+        <v>0.034</v>
+      </c>
+      <c r="AB2">
+        <v>0.08079751537317134</v>
+      </c>
+      <c r="AC2">
+        <v>72</v>
+      </c>
+      <c r="AD2">
+        <v>0.034</v>
+      </c>
+      <c r="AE2">
+        <v>0.003</v>
+      </c>
+      <c r="AF2">
+        <v>0.109</v>
+      </c>
+      <c r="AG2">
+        <v>0.325</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>3.6</v>
+      </c>
+      <c r="AK2">
+        <v>0.08261304671092226</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.15</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.1120000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>0.003</v>
+      </c>
+      <c r="AS2">
+        <v>0.034</v>
+      </c>
+      <c r="AT2">
+        <v>1.03</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1160631399340147</v>
+      </c>
+      <c r="C2">
+        <v>3.639766851095988</v>
+      </c>
+      <c r="D2">
+        <v>2.609766851095988</v>
+      </c>
+      <c r="E2">
+        <v>-0.034</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.03</v>
+      </c>
+      <c r="H2">
+        <v>3.6</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.325</v>
+      </c>
+      <c r="K2">
+        <v>0.109</v>
+      </c>
+      <c r="L2">
+        <v>0.216</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.216</v>
+      </c>
+      <c r="O2">
+        <v>0.0324</v>
+      </c>
+      <c r="P2">
+        <v>0.1836</v>
+      </c>
+      <c r="Q2">
+        <v>0.2926</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1160631399340147</v>
+      </c>
+      <c r="T2">
+        <v>0.9352413814778209</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.037995</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1159391952241137</v>
+      </c>
+      <c r="C3">
+        <v>3.607620138235277</v>
+      </c>
+      <c r="D3">
+        <v>2.613960138235277</v>
+      </c>
+      <c r="E3">
+        <v>0.002339999999999995</v>
+      </c>
+      <c r="F3">
+        <v>0.03634</v>
+      </c>
+      <c r="G3">
+        <v>1.03</v>
+      </c>
+      <c r="H3">
+        <v>3.6</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.325</v>
+      </c>
+      <c r="K3">
+        <v>0.109</v>
+      </c>
+      <c r="L3">
+        <v>0.216</v>
+      </c>
+      <c r="M3">
+        <v>0.001624398</v>
+      </c>
+      <c r="N3">
+        <v>0.214375602</v>
+      </c>
+      <c r="O3">
+        <v>0.0321563403</v>
+      </c>
+      <c r="P3">
+        <v>0.1822192617</v>
+      </c>
+      <c r="Q3">
+        <v>0.2912192617</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1167265103273875</v>
+      </c>
+      <c r="T3">
+        <v>0.9432712317228323</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.037995</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>132.9723380600075</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1158152505142126</v>
+      </c>
+      <c r="C4">
+        <v>3.575486922331455</v>
+      </c>
+      <c r="D4">
+        <v>2.618166922331456</v>
+      </c>
+      <c r="E4">
+        <v>0.03867999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.07267999999999999</v>
+      </c>
+      <c r="G4">
+        <v>1.03</v>
+      </c>
+      <c r="H4">
+        <v>3.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.325</v>
+      </c>
+      <c r="K4">
+        <v>0.109</v>
+      </c>
+      <c r="L4">
+        <v>0.216</v>
+      </c>
+      <c r="M4">
+        <v>0.003248796</v>
+      </c>
+      <c r="N4">
+        <v>0.212751204</v>
+      </c>
+      <c r="O4">
+        <v>0.0319126806</v>
+      </c>
+      <c r="P4">
+        <v>0.1808385234</v>
+      </c>
+      <c r="Q4">
+        <v>0.2898385234</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1174034188920537</v>
+      </c>
+      <c r="T4">
+        <v>0.9514649564626403</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.037995</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>66.48616903000374</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1156913058043116</v>
+      </c>
+      <c r="C5">
+        <v>3.543367268653661</v>
+      </c>
+      <c r="D5">
+        <v>2.622387268653661</v>
+      </c>
+      <c r="E5">
+        <v>0.07501999999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.10902</v>
+      </c>
+      <c r="G5">
+        <v>1.03</v>
+      </c>
+      <c r="H5">
+        <v>3.6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.325</v>
+      </c>
+      <c r="K5">
+        <v>0.109</v>
+      </c>
+      <c r="L5">
+        <v>0.216</v>
+      </c>
+      <c r="M5">
+        <v>0.004873194</v>
+      </c>
+      <c r="N5">
+        <v>0.211126806</v>
+      </c>
+      <c r="O5">
+        <v>0.0316690209</v>
+      </c>
+      <c r="P5">
+        <v>0.1794577851</v>
+      </c>
+      <c r="Q5">
+        <v>0.2884577851</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1180942843343419</v>
+      </c>
+      <c r="T5">
+        <v>0.9598276239805883</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.037995</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>44.32411268666915</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1155673610944106</v>
+      </c>
+      <c r="C6">
+        <v>3.511261242892552</v>
+      </c>
+      <c r="D6">
+        <v>2.626621242892553</v>
+      </c>
+      <c r="E6">
+        <v>0.11136</v>
+      </c>
+      <c r="F6">
+        <v>0.14536</v>
+      </c>
+      <c r="G6">
+        <v>1.03</v>
+      </c>
+      <c r="H6">
+        <v>3.6</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.325</v>
+      </c>
+      <c r="K6">
+        <v>0.109</v>
+      </c>
+      <c r="L6">
+        <v>0.216</v>
+      </c>
+      <c r="M6">
+        <v>0.006497592</v>
+      </c>
+      <c r="N6">
+        <v>0.209502408</v>
+      </c>
+      <c r="O6">
+        <v>0.0314253612</v>
+      </c>
+      <c r="P6">
+        <v>0.1780770468</v>
+      </c>
+      <c r="Q6">
+        <v>0.2870770468</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1187995428066777</v>
+      </c>
+      <c r="T6">
+        <v>0.9683645137384936</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.037995</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>33.24308451500187</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1154434163845096</v>
+      </c>
+      <c r="C7">
+        <v>3.479168911163717</v>
+      </c>
+      <c r="D7">
+        <v>2.630868911163717</v>
+      </c>
+      <c r="E7">
+        <v>0.1477</v>
+      </c>
+      <c r="F7">
+        <v>0.1817</v>
+      </c>
+      <c r="G7">
+        <v>1.03</v>
+      </c>
+      <c r="H7">
+        <v>3.6</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.325</v>
+      </c>
+      <c r="K7">
+        <v>0.109</v>
+      </c>
+      <c r="L7">
+        <v>0.216</v>
+      </c>
+      <c r="M7">
+        <v>0.008121990000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.20787801</v>
+      </c>
+      <c r="O7">
+        <v>0.0311817015</v>
+      </c>
+      <c r="P7">
+        <v>0.1766963085</v>
+      </c>
+      <c r="Q7">
+        <v>0.2856963085000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1195196488257996</v>
+      </c>
+      <c r="T7">
+        <v>0.9770811274913024</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.037995</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>26.59446761200149</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1153194716746085</v>
+      </c>
+      <c r="C8">
+        <v>3.447090340011116</v>
+      </c>
+      <c r="D8">
+        <v>2.635130340011116</v>
+      </c>
+      <c r="E8">
+        <v>0.18404</v>
+      </c>
+      <c r="F8">
+        <v>0.21804</v>
+      </c>
+      <c r="G8">
+        <v>1.03</v>
+      </c>
+      <c r="H8">
+        <v>3.6</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.325</v>
+      </c>
+      <c r="K8">
+        <v>0.109</v>
+      </c>
+      <c r="L8">
+        <v>0.216</v>
+      </c>
+      <c r="M8">
+        <v>0.009746388</v>
+      </c>
+      <c r="N8">
+        <v>0.206253612</v>
+      </c>
+      <c r="O8">
+        <v>0.0309380418</v>
+      </c>
+      <c r="P8">
+        <v>0.1753155702</v>
+      </c>
+      <c r="Q8">
+        <v>0.2843155702</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1202550762495836</v>
+      </c>
+      <c r="T8">
+        <v>0.985983201111192</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.037995</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>22.16205634333458</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1151955269647075</v>
+      </c>
+      <c r="C9">
+        <v>3.415025596410551</v>
+      </c>
+      <c r="D9">
+        <v>2.639405596410551</v>
+      </c>
+      <c r="E9">
+        <v>0.22038</v>
+      </c>
+      <c r="F9">
+        <v>0.25438</v>
+      </c>
+      <c r="G9">
+        <v>1.03</v>
+      </c>
+      <c r="H9">
+        <v>3.6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.325</v>
+      </c>
+      <c r="K9">
+        <v>0.109</v>
+      </c>
+      <c r="L9">
+        <v>0.216</v>
+      </c>
+      <c r="M9">
+        <v>0.011370786</v>
+      </c>
+      <c r="N9">
+        <v>0.204629214</v>
+      </c>
+      <c r="O9">
+        <v>0.0306943821</v>
+      </c>
+      <c r="P9">
+        <v>0.1739348319</v>
+      </c>
+      <c r="Q9">
+        <v>0.2829348319</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1210063193168898</v>
+      </c>
+      <c r="T9">
+        <v>0.9950767171745202</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.037995</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>18.99604829428678</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1150715822548065</v>
+      </c>
+      <c r="C10">
+        <v>3.382974747773181</v>
+      </c>
+      <c r="D10">
+        <v>2.643694747773181</v>
+      </c>
+      <c r="E10">
+        <v>0.2567199999999999</v>
+      </c>
+      <c r="F10">
+        <v>0.29072</v>
+      </c>
+      <c r="G10">
+        <v>1.03</v>
+      </c>
+      <c r="H10">
+        <v>3.6</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.325</v>
+      </c>
+      <c r="K10">
+        <v>0.109</v>
+      </c>
+      <c r="L10">
+        <v>0.216</v>
+      </c>
+      <c r="M10">
+        <v>0.012995184</v>
+      </c>
+      <c r="N10">
+        <v>0.203004816</v>
+      </c>
+      <c r="O10">
+        <v>0.0304507224</v>
+      </c>
+      <c r="P10">
+        <v>0.1725540936</v>
+      </c>
+      <c r="Q10">
+        <v>0.2815540936000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1217738937552245</v>
+      </c>
+      <c r="T10">
+        <v>1.00436791836966</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.037995</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>16.62154225750093</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1149476375449055</v>
+      </c>
+      <c r="C11">
+        <v>3.350937861949066</v>
+      </c>
+      <c r="D11">
+        <v>2.647997861949067</v>
+      </c>
+      <c r="E11">
+        <v>0.29306</v>
+      </c>
+      <c r="F11">
+        <v>0.32706</v>
+      </c>
+      <c r="G11">
+        <v>1.03</v>
+      </c>
+      <c r="H11">
+        <v>3.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.325</v>
+      </c>
+      <c r="K11">
+        <v>0.109</v>
+      </c>
+      <c r="L11">
+        <v>0.216</v>
+      </c>
+      <c r="M11">
+        <v>0.014619582</v>
+      </c>
+      <c r="N11">
+        <v>0.201380418</v>
+      </c>
+      <c r="O11">
+        <v>0.0302070627</v>
+      </c>
+      <c r="P11">
+        <v>0.1711733553</v>
+      </c>
+      <c r="Q11">
+        <v>0.2801733553</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1225583379614346</v>
+      </c>
+      <c r="T11">
+        <v>1.013863321788868</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.037995</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>14.77470422888972</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1148236928350045</v>
+      </c>
+      <c r="C12">
+        <v>3.318915007230736</v>
+      </c>
+      <c r="D12">
+        <v>2.652315007230736</v>
+      </c>
+      <c r="E12">
+        <v>0.3294</v>
+      </c>
+      <c r="F12">
+        <v>0.3634</v>
+      </c>
+      <c r="G12">
+        <v>1.03</v>
+      </c>
+      <c r="H12">
+        <v>3.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.325</v>
+      </c>
+      <c r="K12">
+        <v>0.109</v>
+      </c>
+      <c r="L12">
+        <v>0.216</v>
+      </c>
+      <c r="M12">
+        <v>0.01624398</v>
+      </c>
+      <c r="N12">
+        <v>0.19975602</v>
+      </c>
+      <c r="O12">
+        <v>0.029963403</v>
+      </c>
+      <c r="P12">
+        <v>0.169792617</v>
+      </c>
+      <c r="Q12">
+        <v>0.278792617</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1233602142611161</v>
+      </c>
+      <c r="T12">
+        <v>1.023569734172949</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.037995</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>13.29723380600075</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1148025981251034</v>
+      </c>
+      <c r="C13">
+        <v>3.283311163849377</v>
+      </c>
+      <c r="D13">
+        <v>2.653051163849376</v>
+      </c>
+      <c r="E13">
+        <v>0.36574</v>
+      </c>
+      <c r="F13">
+        <v>0.39974</v>
+      </c>
+      <c r="G13">
+        <v>1.03</v>
+      </c>
+      <c r="H13">
+        <v>3.6</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.325</v>
+      </c>
+      <c r="K13">
+        <v>0.109</v>
+      </c>
+      <c r="L13">
+        <v>0.216</v>
+      </c>
+      <c r="M13">
+        <v>0.018308092</v>
+      </c>
+      <c r="N13">
+        <v>0.197691908</v>
+      </c>
+      <c r="O13">
+        <v>0.0296537862</v>
+      </c>
+      <c r="P13">
+        <v>0.1680381218</v>
+      </c>
+      <c r="Q13">
+        <v>0.2770381218</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1241801102529252</v>
+      </c>
+      <c r="T13">
+        <v>1.033494268183637</v>
+      </c>
+      <c r="U13">
+        <v>0.0458</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.03893</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>11.79806175324004</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1146880034152024</v>
+      </c>
+      <c r="C14">
+        <v>3.250977404820173</v>
+      </c>
+      <c r="D14">
+        <v>2.657057404820173</v>
+      </c>
+      <c r="E14">
+        <v>0.40208</v>
+      </c>
+      <c r="F14">
+        <v>0.43608</v>
+      </c>
+      <c r="G14">
+        <v>1.03</v>
+      </c>
+      <c r="H14">
+        <v>3.6</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.325</v>
+      </c>
+      <c r="K14">
+        <v>0.109</v>
+      </c>
+      <c r="L14">
+        <v>0.216</v>
+      </c>
+      <c r="M14">
+        <v>0.019972464</v>
+      </c>
+      <c r="N14">
+        <v>0.196027536</v>
+      </c>
+      <c r="O14">
+        <v>0.0294041304</v>
+      </c>
+      <c r="P14">
+        <v>0.1666234056</v>
+      </c>
+      <c r="Q14">
+        <v>0.2756234056</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1250186402445482</v>
+      </c>
+      <c r="T14">
+        <v>1.043644359785477</v>
+      </c>
+      <c r="U14">
+        <v>0.0458</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.03893</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>10.81488994047004</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1145734087053014</v>
+      </c>
+      <c r="C15">
+        <v>3.218655763340639</v>
+      </c>
+      <c r="D15">
+        <v>2.661075763340639</v>
+      </c>
+      <c r="E15">
+        <v>0.43842</v>
+      </c>
+      <c r="F15">
+        <v>0.47242</v>
+      </c>
+      <c r="G15">
+        <v>1.03</v>
+      </c>
+      <c r="H15">
+        <v>3.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.325</v>
+      </c>
+      <c r="K15">
+        <v>0.109</v>
+      </c>
+      <c r="L15">
+        <v>0.216</v>
+      </c>
+      <c r="M15">
+        <v>0.021636836</v>
+      </c>
+      <c r="N15">
+        <v>0.194363164</v>
+      </c>
+      <c r="O15">
+        <v>0.0291544746</v>
+      </c>
+      <c r="P15">
+        <v>0.1652086894</v>
+      </c>
+      <c r="Q15">
+        <v>0.2742086894</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1258764467877027</v>
+      </c>
+      <c r="T15">
+        <v>1.05402778682644</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.03893</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>9.982975329664653</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1147206139954004</v>
+      </c>
+      <c r="C16">
+        <v>3.177156104993545</v>
+      </c>
+      <c r="D16">
+        <v>2.655916104993545</v>
+      </c>
+      <c r="E16">
+        <v>0.47476</v>
+      </c>
+      <c r="F16">
+        <v>0.50876</v>
+      </c>
+      <c r="G16">
+        <v>1.03</v>
+      </c>
+      <c r="H16">
+        <v>3.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.325</v>
+      </c>
+      <c r="K16">
+        <v>0.109</v>
+      </c>
+      <c r="L16">
+        <v>0.216</v>
+      </c>
+      <c r="M16">
+        <v>0.02442048</v>
+      </c>
+      <c r="N16">
+        <v>0.19157952</v>
+      </c>
+      <c r="O16">
+        <v>0.028736928</v>
+      </c>
+      <c r="P16">
+        <v>0.162842592</v>
+      </c>
+      <c r="Q16">
+        <v>0.271842592</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.126754202320233</v>
+      </c>
+      <c r="T16">
+        <v>1.064652688914868</v>
+      </c>
+      <c r="U16">
+        <v>0.048</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.0408</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.845034987027281</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1146247192854994</v>
+      </c>
+      <c r="C17">
+        <v>3.144175013629274</v>
+      </c>
+      <c r="D17">
+        <v>2.659275013629274</v>
+      </c>
+      <c r="E17">
+        <v>0.5110999999999999</v>
+      </c>
+      <c r="F17">
+        <v>0.5450999999999999</v>
+      </c>
+      <c r="G17">
+        <v>1.03</v>
+      </c>
+      <c r="H17">
+        <v>3.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.325</v>
+      </c>
+      <c r="K17">
+        <v>0.109</v>
+      </c>
+      <c r="L17">
+        <v>0.216</v>
+      </c>
+      <c r="M17">
+        <v>0.0261648</v>
+      </c>
+      <c r="N17">
+        <v>0.1898352</v>
+      </c>
+      <c r="O17">
+        <v>0.02847528</v>
+      </c>
+      <c r="P17">
+        <v>0.16135992</v>
+      </c>
+      <c r="Q17">
+        <v>0.27035992</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1276526109241169</v>
+      </c>
+      <c r="T17">
+        <v>1.075527588699494</v>
+      </c>
+      <c r="U17">
+        <v>0.048</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.0408</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.255365987892132</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1145288245755983</v>
+      </c>
+      <c r="C18">
+        <v>3.11120242897486</v>
+      </c>
+      <c r="D18">
+        <v>2.662642428974859</v>
+      </c>
+      <c r="E18">
+        <v>0.5474399999999999</v>
+      </c>
+      <c r="F18">
+        <v>0.58144</v>
+      </c>
+      <c r="G18">
+        <v>1.03</v>
+      </c>
+      <c r="H18">
+        <v>3.6</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.325</v>
+      </c>
+      <c r="K18">
+        <v>0.109</v>
+      </c>
+      <c r="L18">
+        <v>0.216</v>
+      </c>
+      <c r="M18">
+        <v>0.02790912</v>
+      </c>
+      <c r="N18">
+        <v>0.18809088</v>
+      </c>
+      <c r="O18">
+        <v>0.028213632</v>
+      </c>
+      <c r="P18">
+        <v>0.159877248</v>
+      </c>
+      <c r="Q18">
+        <v>0.268877248</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1285724102090456</v>
+      </c>
+      <c r="T18">
+        <v>1.086661414669468</v>
+      </c>
+      <c r="U18">
+        <v>0.048</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.0408</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.739405613648872</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1146496798656973</v>
+      </c>
+      <c r="C19">
+        <v>3.070619900545559</v>
+      </c>
+      <c r="D19">
+        <v>2.658399900545558</v>
+      </c>
+      <c r="E19">
+        <v>0.58378</v>
+      </c>
+      <c r="F19">
+        <v>0.61778</v>
+      </c>
+      <c r="G19">
+        <v>1.03</v>
+      </c>
+      <c r="H19">
+        <v>3.6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.325</v>
+      </c>
+      <c r="K19">
+        <v>0.109</v>
+      </c>
+      <c r="L19">
+        <v>0.216</v>
+      </c>
+      <c r="M19">
+        <v>0.03058011</v>
+      </c>
+      <c r="N19">
+        <v>0.18541989</v>
+      </c>
+      <c r="O19">
+        <v>0.0278129835</v>
+      </c>
+      <c r="P19">
+        <v>0.1576069065</v>
+      </c>
+      <c r="Q19">
+        <v>0.2666069065</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1295143733321654</v>
+      </c>
+      <c r="T19">
+        <v>1.098063525602574</v>
+      </c>
+      <c r="U19">
+        <v>0.0495</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.042075</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.063414748998614</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1145665351557963</v>
+      </c>
+      <c r="C20">
+        <v>3.037197176465293</v>
+      </c>
+      <c r="D20">
+        <v>2.661317176465293</v>
+      </c>
+      <c r="E20">
+        <v>0.6201199999999999</v>
+      </c>
+      <c r="F20">
+        <v>0.6541199999999999</v>
+      </c>
+      <c r="G20">
+        <v>1.03</v>
+      </c>
+      <c r="H20">
+        <v>3.6</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.325</v>
+      </c>
+      <c r="K20">
+        <v>0.109</v>
+      </c>
+      <c r="L20">
+        <v>0.216</v>
+      </c>
+      <c r="M20">
+        <v>0.03237893999999999</v>
+      </c>
+      <c r="N20">
+        <v>0.18362106</v>
+      </c>
+      <c r="O20">
+        <v>0.027543159</v>
+      </c>
+      <c r="P20">
+        <v>0.156077901</v>
+      </c>
+      <c r="Q20">
+        <v>0.265077901</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1304793111656052</v>
+      </c>
+      <c r="T20">
+        <v>1.109743736802341</v>
+      </c>
+      <c r="U20">
+        <v>0.0495</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.042075</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.671002818498692</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1144833904458953</v>
+      </c>
+      <c r="C21">
+        <v>3.003780862141743</v>
+      </c>
+      <c r="D21">
+        <v>2.664240862141743</v>
+      </c>
+      <c r="E21">
+        <v>0.6564599999999999</v>
+      </c>
+      <c r="F21">
+        <v>0.69046</v>
+      </c>
+      <c r="G21">
+        <v>1.03</v>
+      </c>
+      <c r="H21">
+        <v>3.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.325</v>
+      </c>
+      <c r="K21">
+        <v>0.109</v>
+      </c>
+      <c r="L21">
+        <v>0.216</v>
+      </c>
+      <c r="M21">
+        <v>0.03417777</v>
+      </c>
+      <c r="N21">
+        <v>0.18182223</v>
+      </c>
+      <c r="O21">
+        <v>0.0272733345</v>
+      </c>
+      <c r="P21">
+        <v>0.1545488955</v>
+      </c>
+      <c r="Q21">
+        <v>0.2635488955</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1314680746245621</v>
+      </c>
+      <c r="T21">
+        <v>1.121712348278646</v>
+      </c>
+      <c r="U21">
+        <v>0.0495</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.042075</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.319897406998759</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1146382457359942</v>
+      </c>
+      <c r="C22">
+        <v>2.962000707407197</v>
+      </c>
+      <c r="D22">
+        <v>2.658800707407196</v>
+      </c>
+      <c r="E22">
+        <v>0.6928</v>
+      </c>
+      <c r="F22">
+        <v>0.7268</v>
+      </c>
+      <c r="G22">
+        <v>1.03</v>
+      </c>
+      <c r="H22">
+        <v>3.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.325</v>
+      </c>
+      <c r="K22">
+        <v>0.109</v>
+      </c>
+      <c r="L22">
+        <v>0.216</v>
+      </c>
+      <c r="M22">
+        <v>0.03699412</v>
+      </c>
+      <c r="N22">
+        <v>0.17900588</v>
+      </c>
+      <c r="O22">
+        <v>0.026850882</v>
+      </c>
+      <c r="P22">
+        <v>0.152154998</v>
+      </c>
+      <c r="Q22">
+        <v>0.261154998</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1324815571699928</v>
+      </c>
+      <c r="T22">
+        <v>1.133980175041858</v>
+      </c>
+      <c r="U22">
+        <v>0.0509</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.043265</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.838765728175181</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1145670010260932</v>
+      </c>
+      <c r="C23">
+        <v>2.928160812763333</v>
+      </c>
+      <c r="D23">
+        <v>2.661300812763333</v>
+      </c>
+      <c r="E23">
+        <v>0.7291399999999999</v>
+      </c>
+      <c r="F23">
+        <v>0.7631399999999999</v>
+      </c>
+      <c r="G23">
+        <v>1.03</v>
+      </c>
+      <c r="H23">
+        <v>3.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.325</v>
+      </c>
+      <c r="K23">
+        <v>0.109</v>
+      </c>
+      <c r="L23">
+        <v>0.216</v>
+      </c>
+      <c r="M23">
+        <v>0.038843826</v>
+      </c>
+      <c r="N23">
+        <v>0.177156174</v>
+      </c>
+      <c r="O23">
+        <v>0.0265734261</v>
+      </c>
+      <c r="P23">
+        <v>0.1505827479</v>
+      </c>
+      <c r="Q23">
+        <v>0.2595827479</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1335206975013838</v>
+      </c>
+      <c r="T23">
+        <v>1.146558579697809</v>
+      </c>
+      <c r="U23">
+        <v>0.0509</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.043265</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.560729264928743</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1144957563161922</v>
+      </c>
+      <c r="C24">
+        <v>2.894325624308813</v>
+      </c>
+      <c r="D24">
+        <v>2.663805624308813</v>
+      </c>
+      <c r="E24">
+        <v>0.7654799999999999</v>
+      </c>
+      <c r="F24">
+        <v>0.79948</v>
+      </c>
+      <c r="G24">
+        <v>1.03</v>
+      </c>
+      <c r="H24">
+        <v>3.6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.325</v>
+      </c>
+      <c r="K24">
+        <v>0.109</v>
+      </c>
+      <c r="L24">
+        <v>0.216</v>
+      </c>
+      <c r="M24">
+        <v>0.040693532</v>
+      </c>
+      <c r="N24">
+        <v>0.175306468</v>
+      </c>
+      <c r="O24">
+        <v>0.0262959702</v>
+      </c>
+      <c r="P24">
+        <v>0.1490104978</v>
+      </c>
+      <c r="Q24">
+        <v>0.2580104978</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1345864824566567</v>
+      </c>
+      <c r="T24">
+        <v>1.159459507550068</v>
+      </c>
+      <c r="U24">
+        <v>0.0509</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.043265</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.307968843795619</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1144245116062912</v>
+      </c>
+      <c r="C25">
+        <v>2.860495155344527</v>
+      </c>
+      <c r="D25">
+        <v>2.666315155344527</v>
+      </c>
+      <c r="E25">
+        <v>0.80182</v>
+      </c>
+      <c r="F25">
+        <v>0.83582</v>
+      </c>
+      <c r="G25">
+        <v>1.03</v>
+      </c>
+      <c r="H25">
+        <v>3.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.325</v>
+      </c>
+      <c r="K25">
+        <v>0.109</v>
+      </c>
+      <c r="L25">
+        <v>0.216</v>
+      </c>
+      <c r="M25">
+        <v>0.042543238</v>
+      </c>
+      <c r="N25">
+        <v>0.173456762</v>
+      </c>
+      <c r="O25">
+        <v>0.0260185143</v>
+      </c>
+      <c r="P25">
+        <v>0.1474382477</v>
+      </c>
+      <c r="Q25">
+        <v>0.2564382477</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1356799501380405</v>
+      </c>
+      <c r="T25">
+        <v>1.172695524437449</v>
+      </c>
+      <c r="U25">
+        <v>0.0509</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.043265</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.077187589717547</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1143532668963901</v>
+      </c>
+      <c r="C26">
+        <v>2.82666941922153</v>
+      </c>
+      <c r="D26">
+        <v>2.66882941922153</v>
+      </c>
+      <c r="E26">
+        <v>0.8381599999999999</v>
+      </c>
+      <c r="F26">
+        <v>0.8721599999999999</v>
+      </c>
+      <c r="G26">
+        <v>1.03</v>
+      </c>
+      <c r="H26">
+        <v>3.6</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.325</v>
+      </c>
+      <c r="K26">
+        <v>0.109</v>
+      </c>
+      <c r="L26">
+        <v>0.216</v>
+      </c>
+      <c r="M26">
+        <v>0.044392944</v>
+      </c>
+      <c r="N26">
+        <v>0.171607056</v>
+      </c>
+      <c r="O26">
+        <v>0.0257410584</v>
+      </c>
+      <c r="P26">
+        <v>0.1458659976</v>
+      </c>
+      <c r="Q26">
+        <v>0.2548659976000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1368021932847239</v>
+      </c>
+      <c r="T26">
+        <v>1.18627985755871</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.043265</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.865638106812651</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1142820221864891</v>
+      </c>
+      <c r="C27">
+        <v>2.792848429341291</v>
+      </c>
+      <c r="D27">
+        <v>2.671348429341291</v>
+      </c>
+      <c r="E27">
+        <v>0.8744999999999999</v>
+      </c>
+      <c r="F27">
+        <v>0.9085</v>
+      </c>
+      <c r="G27">
+        <v>1.03</v>
+      </c>
+      <c r="H27">
+        <v>3.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.325</v>
+      </c>
+      <c r="K27">
+        <v>0.109</v>
+      </c>
+      <c r="L27">
+        <v>0.216</v>
+      </c>
+      <c r="M27">
+        <v>0.04624265</v>
+      </c>
+      <c r="N27">
+        <v>0.16975735</v>
+      </c>
+      <c r="O27">
+        <v>0.0254636025</v>
+      </c>
+      <c r="P27">
+        <v>0.1442937475</v>
+      </c>
+      <c r="Q27">
+        <v>0.2532937475</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1379543629153188</v>
+      </c>
+      <c r="T27">
+        <v>1.200226439563203</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.043265</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.671012582540145</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1147853774765881</v>
+      </c>
+      <c r="C28">
+        <v>2.738812427712282</v>
+      </c>
+      <c r="D28">
+        <v>2.653652427712282</v>
+      </c>
+      <c r="E28">
+        <v>0.91084</v>
+      </c>
+      <c r="F28">
+        <v>0.94484</v>
+      </c>
+      <c r="G28">
+        <v>1.03</v>
+      </c>
+      <c r="H28">
+        <v>3.6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.325</v>
+      </c>
+      <c r="K28">
+        <v>0.109</v>
+      </c>
+      <c r="L28">
+        <v>0.216</v>
+      </c>
+      <c r="M28">
+        <v>0.05054894</v>
+      </c>
+      <c r="N28">
+        <v>0.16545106</v>
+      </c>
+      <c r="O28">
+        <v>0.024817659</v>
+      </c>
+      <c r="P28">
+        <v>0.140633401</v>
+      </c>
+      <c r="Q28">
+        <v>0.249633401</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1391376722656596</v>
+      </c>
+      <c r="T28">
+        <v>1.214549956216467</v>
+      </c>
+      <c r="U28">
+        <v>0.0535</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.273086636435897</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1147362327666871</v>
+      </c>
+      <c r="C29">
+        <v>2.704189828931522</v>
+      </c>
+      <c r="D29">
+        <v>2.655369828931522</v>
+      </c>
+      <c r="E29">
+        <v>0.94718</v>
+      </c>
+      <c r="F29">
+        <v>0.9811800000000001</v>
+      </c>
+      <c r="G29">
+        <v>1.03</v>
+      </c>
+      <c r="H29">
+        <v>3.6</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.325</v>
+      </c>
+      <c r="K29">
+        <v>0.109</v>
+      </c>
+      <c r="L29">
+        <v>0.216</v>
+      </c>
+      <c r="M29">
+        <v>0.05249313</v>
+      </c>
+      <c r="N29">
+        <v>0.16350687</v>
+      </c>
+      <c r="O29">
+        <v>0.0245260305</v>
+      </c>
+      <c r="P29">
+        <v>0.1389808395</v>
+      </c>
+      <c r="Q29">
+        <v>0.2479808395</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1403534010502563</v>
+      </c>
+      <c r="T29">
+        <v>1.229265897983519</v>
+      </c>
+      <c r="U29">
+        <v>0.0535</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.04547499999999999</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.114824168419753</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1153296880567861</v>
+      </c>
+      <c r="C30">
+        <v>2.647258561514107</v>
+      </c>
+      <c r="D30">
+        <v>2.634778561514107</v>
+      </c>
+      <c r="E30">
+        <v>0.9835199999999999</v>
+      </c>
+      <c r="F30">
+        <v>1.01752</v>
+      </c>
+      <c r="G30">
+        <v>1.03</v>
+      </c>
+      <c r="H30">
+        <v>3.6</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.325</v>
+      </c>
+      <c r="K30">
+        <v>0.109</v>
+      </c>
+      <c r="L30">
+        <v>0.216</v>
+      </c>
+      <c r="M30">
+        <v>0.057184624</v>
+      </c>
+      <c r="N30">
+        <v>0.158815376</v>
+      </c>
+      <c r="O30">
+        <v>0.0238223064</v>
+      </c>
+      <c r="P30">
+        <v>0.1349930696</v>
+      </c>
+      <c r="Q30">
+        <v>0.2439930696</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1416029000788696</v>
+      </c>
+      <c r="T30">
+        <v>1.244390615910767</v>
+      </c>
+      <c r="U30">
+        <v>0.0562</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.04777</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.777239140367523</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1153034933468851</v>
+      </c>
+      <c r="C31">
+        <v>2.611820706724122</v>
+      </c>
+      <c r="D31">
+        <v>2.635680706724122</v>
+      </c>
+      <c r="E31">
+        <v>1.01986</v>
+      </c>
+      <c r="F31">
+        <v>1.05386</v>
+      </c>
+      <c r="G31">
+        <v>1.03</v>
+      </c>
+      <c r="H31">
+        <v>3.6</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.325</v>
+      </c>
+      <c r="K31">
+        <v>0.109</v>
+      </c>
+      <c r="L31">
+        <v>0.216</v>
+      </c>
+      <c r="M31">
+        <v>0.05922693199999999</v>
+      </c>
+      <c r="N31">
+        <v>0.156773068</v>
+      </c>
+      <c r="O31">
+        <v>0.0235159602</v>
+      </c>
+      <c r="P31">
+        <v>0.1332571078</v>
+      </c>
+      <c r="Q31">
+        <v>0.2422571078</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1428875962632184</v>
+      </c>
+      <c r="T31">
+        <v>1.259941382230332</v>
+      </c>
+      <c r="U31">
+        <v>0.0562</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.04777</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.646989514837609</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.115277298636984</v>
+      </c>
+      <c r="C32">
+        <v>2.576383469932745</v>
+      </c>
+      <c r="D32">
+        <v>2.636583469932746</v>
+      </c>
+      <c r="E32">
+        <v>1.0562</v>
+      </c>
+      <c r="F32">
+        <v>1.0902</v>
+      </c>
+      <c r="G32">
+        <v>1.03</v>
+      </c>
+      <c r="H32">
+        <v>3.6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.325</v>
+      </c>
+      <c r="K32">
+        <v>0.109</v>
+      </c>
+      <c r="L32">
+        <v>0.216</v>
+      </c>
+      <c r="M32">
+        <v>0.06126923999999999</v>
+      </c>
+      <c r="N32">
+        <v>0.15473076</v>
+      </c>
+      <c r="O32">
+        <v>0.023209614</v>
+      </c>
+      <c r="P32">
+        <v>0.131521146</v>
+      </c>
+      <c r="Q32">
+        <v>0.240521146</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1442089980528343</v>
+      </c>
+      <c r="T32">
+        <v>1.275936456159027</v>
+      </c>
+      <c r="U32">
+        <v>0.0562</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.04777</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.525423197676355</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.116489553927083</v>
+      </c>
+      <c r="C33">
+        <v>2.498902646004045</v>
+      </c>
+      <c r="D33">
+        <v>2.595442646004044</v>
+      </c>
+      <c r="E33">
+        <v>1.09254</v>
+      </c>
+      <c r="F33">
+        <v>1.12654</v>
+      </c>
+      <c r="G33">
+        <v>1.03</v>
+      </c>
+      <c r="H33">
+        <v>3.6</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.325</v>
+      </c>
+      <c r="K33">
+        <v>0.109</v>
+      </c>
+      <c r="L33">
+        <v>0.216</v>
+      </c>
+      <c r="M33">
+        <v>0.06860628599999999</v>
+      </c>
+      <c r="N33">
+        <v>0.147393714</v>
+      </c>
+      <c r="O33">
+        <v>0.0221090571</v>
+      </c>
+      <c r="P33">
+        <v>0.1252846569</v>
+      </c>
+      <c r="Q33">
+        <v>0.2342846569</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1455687013435986</v>
+      </c>
+      <c r="T33">
+        <v>1.292395155418989</v>
+      </c>
+      <c r="U33">
+        <v>0.0609</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.051765</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>3.148399550443527</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.116503309217182</v>
+      </c>
+      <c r="C34">
+        <v>2.462103192386293</v>
+      </c>
+      <c r="D34">
+        <v>2.594983192386293</v>
+      </c>
+      <c r="E34">
+        <v>1.12888</v>
+      </c>
+      <c r="F34">
+        <v>1.16288</v>
+      </c>
+      <c r="G34">
+        <v>1.03</v>
+      </c>
+      <c r="H34">
+        <v>3.6</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.325</v>
+      </c>
+      <c r="K34">
+        <v>0.109</v>
+      </c>
+      <c r="L34">
+        <v>0.216</v>
+      </c>
+      <c r="M34">
+        <v>0.07081939199999999</v>
+      </c>
+      <c r="N34">
+        <v>0.145180608</v>
+      </c>
+      <c r="O34">
+        <v>0.0217770912</v>
+      </c>
+      <c r="P34">
+        <v>0.1234035168</v>
+      </c>
+      <c r="Q34">
+        <v>0.2324035168</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1469683959076205</v>
+      </c>
+      <c r="T34">
+        <v>1.309337934068949</v>
+      </c>
+      <c r="U34">
+        <v>0.0609</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.051765</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>3.050012064492166</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1191257145072809</v>
+      </c>
+      <c r="C35">
+        <v>2.341044398496015</v>
+      </c>
+      <c r="D35">
+        <v>2.510264398496014</v>
+      </c>
+      <c r="E35">
+        <v>1.16522</v>
+      </c>
+      <c r="F35">
+        <v>1.19922</v>
+      </c>
+      <c r="G35">
+        <v>1.03</v>
+      </c>
+      <c r="H35">
+        <v>3.6</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.325</v>
+      </c>
+      <c r="K35">
+        <v>0.109</v>
+      </c>
+      <c r="L35">
+        <v>0.216</v>
+      </c>
+      <c r="M35">
+        <v>0.08418524399999999</v>
+      </c>
+      <c r="N35">
+        <v>0.131814756</v>
+      </c>
+      <c r="O35">
+        <v>0.0197722134</v>
+      </c>
+      <c r="P35">
+        <v>0.1120425426</v>
+      </c>
+      <c r="Q35">
+        <v>0.2210425426</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1484098723989268</v>
+      </c>
+      <c r="T35">
+        <v>1.326786467305476</v>
+      </c>
+      <c r="U35">
+        <v>0.0702</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.05966999999999999</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.565770314807189</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1205768197973799</v>
+      </c>
+      <c r="C36">
+        <v>2.260160505040262</v>
+      </c>
+      <c r="D36">
+        <v>2.465720505040262</v>
+      </c>
+      <c r="E36">
+        <v>1.20156</v>
+      </c>
+      <c r="F36">
+        <v>1.23556</v>
+      </c>
+      <c r="G36">
+        <v>1.03</v>
+      </c>
+      <c r="H36">
+        <v>3.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.325</v>
+      </c>
+      <c r="K36">
+        <v>0.109</v>
+      </c>
+      <c r="L36">
+        <v>0.216</v>
+      </c>
+      <c r="M36">
+        <v>0.09254344399999999</v>
+      </c>
+      <c r="N36">
+        <v>0.123456556</v>
+      </c>
+      <c r="O36">
+        <v>0.0185184834</v>
+      </c>
+      <c r="P36">
+        <v>0.1049380726</v>
+      </c>
+      <c r="Q36">
+        <v>0.2139380726</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1498950299960302</v>
+      </c>
+      <c r="T36">
+        <v>1.344763743973412</v>
+      </c>
+      <c r="U36">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.063665</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.334038919061625</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1207095750874789</v>
+      </c>
+      <c r="C37">
+        <v>2.219824178107789</v>
+      </c>
+      <c r="D37">
+        <v>2.461724178107788</v>
+      </c>
+      <c r="E37">
+        <v>1.2379</v>
+      </c>
+      <c r="F37">
+        <v>1.2719</v>
+      </c>
+      <c r="G37">
+        <v>1.03</v>
+      </c>
+      <c r="H37">
+        <v>3.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.325</v>
+      </c>
+      <c r="K37">
+        <v>0.109</v>
+      </c>
+      <c r="L37">
+        <v>0.216</v>
+      </c>
+      <c r="M37">
+        <v>0.09526530999999999</v>
+      </c>
+      <c r="N37">
+        <v>0.12073469</v>
+      </c>
+      <c r="O37">
+        <v>0.0181102035</v>
+      </c>
+      <c r="P37">
+        <v>0.1026244865</v>
+      </c>
+      <c r="Q37">
+        <v>0.2116244865</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1514258847499675</v>
+      </c>
+      <c r="T37">
+        <v>1.363294167615747</v>
+      </c>
+      <c r="U37">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.063665</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.267352092802721</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1208423303775779</v>
+      </c>
+      <c r="C38">
+        <v>2.179500784341371</v>
+      </c>
+      <c r="D38">
+        <v>2.457740784341371</v>
+      </c>
+      <c r="E38">
+        <v>1.27424</v>
+      </c>
+      <c r="F38">
+        <v>1.30824</v>
+      </c>
+      <c r="G38">
+        <v>1.03</v>
+      </c>
+      <c r="H38">
+        <v>3.6</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.325</v>
+      </c>
+      <c r="K38">
+        <v>0.109</v>
+      </c>
+      <c r="L38">
+        <v>0.216</v>
+      </c>
+      <c r="M38">
+        <v>0.09798717599999998</v>
+      </c>
+      <c r="N38">
+        <v>0.118012824</v>
+      </c>
+      <c r="O38">
+        <v>0.0177019236</v>
+      </c>
+      <c r="P38">
+        <v>0.1003109004</v>
+      </c>
+      <c r="Q38">
+        <v>0.2093109004</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1530045787149655</v>
+      </c>
+      <c r="T38">
+        <v>1.382403666996904</v>
+      </c>
+      <c r="U38">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.063665</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.204370090224868</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1209750856676769</v>
+      </c>
+      <c r="C39">
+        <v>2.139190261059743</v>
+      </c>
+      <c r="D39">
+        <v>2.453770261059742</v>
+      </c>
+      <c r="E39">
+        <v>1.31058</v>
+      </c>
+      <c r="F39">
+        <v>1.34458</v>
+      </c>
+      <c r="G39">
+        <v>1.03</v>
+      </c>
+      <c r="H39">
+        <v>3.6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.325</v>
+      </c>
+      <c r="K39">
+        <v>0.109</v>
+      </c>
+      <c r="L39">
+        <v>0.216</v>
+      </c>
+      <c r="M39">
+        <v>0.100709042</v>
+      </c>
+      <c r="N39">
+        <v>0.115290958</v>
+      </c>
+      <c r="O39">
+        <v>0.0172936437</v>
+      </c>
+      <c r="P39">
+        <v>0.09799731430000001</v>
+      </c>
+      <c r="Q39">
+        <v>0.2069973143</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1546333899486934</v>
+      </c>
+      <c r="T39">
+        <v>1.402119817152066</v>
+      </c>
+      <c r="U39">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.063665</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>2.144792520218791</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1211078409577758</v>
+      </c>
+      <c r="C40">
+        <v>2.098892545986032</v>
+      </c>
+      <c r="D40">
+        <v>2.449812545986031</v>
+      </c>
+      <c r="E40">
+        <v>1.34692</v>
+      </c>
+      <c r="F40">
+        <v>1.38092</v>
+      </c>
+      <c r="G40">
+        <v>1.03</v>
+      </c>
+      <c r="H40">
+        <v>3.6</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.325</v>
+      </c>
+      <c r="K40">
+        <v>0.109</v>
+      </c>
+      <c r="L40">
+        <v>0.216</v>
+      </c>
+      <c r="M40">
+        <v>0.103430908</v>
+      </c>
+      <c r="N40">
+        <v>0.112569092</v>
+      </c>
+      <c r="O40">
+        <v>0.0168853638</v>
+      </c>
+      <c r="P40">
+        <v>0.09568372820000001</v>
+      </c>
+      <c r="Q40">
+        <v>0.2046837282</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1563147434802836</v>
+      </c>
+      <c r="T40">
+        <v>1.422471972150944</v>
+      </c>
+      <c r="U40">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.063665</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>2.08835061179198</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1212405962478748</v>
+      </c>
+      <c r="C41">
+        <v>2.058607577244507</v>
+      </c>
+      <c r="D41">
+        <v>2.445867577244507</v>
+      </c>
+      <c r="E41">
+        <v>1.38326</v>
+      </c>
+      <c r="F41">
+        <v>1.41726</v>
+      </c>
+      <c r="G41">
+        <v>1.03</v>
+      </c>
+      <c r="H41">
+        <v>3.6</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.325</v>
+      </c>
+      <c r="K41">
+        <v>0.109</v>
+      </c>
+      <c r="L41">
+        <v>0.216</v>
+      </c>
+      <c r="M41">
+        <v>0.106152774</v>
+      </c>
+      <c r="N41">
+        <v>0.109847226</v>
+      </c>
+      <c r="O41">
+        <v>0.0164770839</v>
+      </c>
+      <c r="P41">
+        <v>0.0933701421</v>
+      </c>
+      <c r="Q41">
+        <v>0.2023701421</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1580512233571718</v>
+      </c>
+      <c r="T41">
+        <v>1.443491410920276</v>
+      </c>
+      <c r="U41">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.063665</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>2.03480316020757</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1269153515379738</v>
+      </c>
+      <c r="C42">
+        <v>1.864750189745141</v>
+      </c>
+      <c r="D42">
+        <v>2.288350189745141</v>
+      </c>
+      <c r="E42">
+        <v>1.4196</v>
+      </c>
+      <c r="F42">
+        <v>1.4536</v>
+      </c>
+      <c r="G42">
+        <v>1.03</v>
+      </c>
+      <c r="H42">
+        <v>3.6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.325</v>
+      </c>
+      <c r="K42">
+        <v>0.109</v>
+      </c>
+      <c r="L42">
+        <v>0.216</v>
+      </c>
+      <c r="M42">
+        <v>0.13256832</v>
+      </c>
+      <c r="N42">
+        <v>0.08343167999999998</v>
+      </c>
+      <c r="O42">
+        <v>0.012514752</v>
+      </c>
+      <c r="P42">
+        <v>0.07091692799999999</v>
+      </c>
+      <c r="Q42">
+        <v>0.179916928</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.159845585896623</v>
+      </c>
+      <c r="T42">
+        <v>1.465211497648586</v>
+      </c>
+      <c r="U42">
+        <v>0.0912</v>
+      </c>
+      <c r="V42">
+        <v>0.15</v>
+      </c>
+      <c r="W42">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>1.629348550241867</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1271866568280728</v>
+      </c>
+      <c r="C43">
+        <v>1.821386035485245</v>
+      </c>
+      <c r="D43">
+        <v>2.281326035485245</v>
+      </c>
+      <c r="E43">
+        <v>1.45594</v>
+      </c>
+      <c r="F43">
+        <v>1.48994</v>
+      </c>
+      <c r="G43">
+        <v>1.03</v>
+      </c>
+      <c r="H43">
+        <v>3.6</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.325</v>
+      </c>
+      <c r="K43">
+        <v>0.109</v>
+      </c>
+      <c r="L43">
+        <v>0.216</v>
+      </c>
+      <c r="M43">
+        <v>0.135882528</v>
+      </c>
+      <c r="N43">
+        <v>0.080117472</v>
+      </c>
+      <c r="O43">
+        <v>0.0120176208</v>
+      </c>
+      <c r="P43">
+        <v>0.06809985119999999</v>
+      </c>
+      <c r="Q43">
+        <v>0.1770998512</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1617007742848691</v>
+      </c>
+      <c r="T43">
+        <v>1.48766785850328</v>
+      </c>
+      <c r="U43">
+        <v>0.0912</v>
+      </c>
+      <c r="V43">
+        <v>0.15</v>
+      </c>
+      <c r="W43">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>1.589608341699383</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1274579621181718</v>
+      </c>
+      <c r="C44">
+        <v>1.778064870939159</v>
+      </c>
+      <c r="D44">
+        <v>2.274344870939158</v>
+      </c>
+      <c r="E44">
+        <v>1.49228</v>
+      </c>
+      <c r="F44">
+        <v>1.52628</v>
+      </c>
+      <c r="G44">
+        <v>1.03</v>
+      </c>
+      <c r="H44">
+        <v>3.6</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.325</v>
+      </c>
+      <c r="K44">
+        <v>0.109</v>
+      </c>
+      <c r="L44">
+        <v>0.216</v>
+      </c>
+      <c r="M44">
+        <v>0.139196736</v>
+      </c>
+      <c r="N44">
+        <v>0.07680326400000001</v>
+      </c>
+      <c r="O44">
+        <v>0.0115204896</v>
+      </c>
+      <c r="P44">
+        <v>0.06528277440000001</v>
+      </c>
+      <c r="Q44">
+        <v>0.1742827744</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.163619934686503</v>
+      </c>
+      <c r="T44">
+        <v>1.510898576628824</v>
+      </c>
+      <c r="U44">
+        <v>0.0912</v>
+      </c>
+      <c r="V44">
+        <v>0.15</v>
+      </c>
+      <c r="W44">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>1.551760524039874</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1277292674082707</v>
+      </c>
+      <c r="C45">
+        <v>1.734786302647997</v>
+      </c>
+      <c r="D45">
+        <v>2.267406302647997</v>
+      </c>
+      <c r="E45">
+        <v>1.52862</v>
+      </c>
+      <c r="F45">
+        <v>1.56262</v>
+      </c>
+      <c r="G45">
+        <v>1.03</v>
+      </c>
+      <c r="H45">
+        <v>3.6</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.325</v>
+      </c>
+      <c r="K45">
+        <v>0.109</v>
+      </c>
+      <c r="L45">
+        <v>0.216</v>
+      </c>
+      <c r="M45">
+        <v>0.142510944</v>
+      </c>
+      <c r="N45">
+        <v>0.073489056</v>
+      </c>
+      <c r="O45">
+        <v>0.0110233584</v>
+      </c>
+      <c r="P45">
+        <v>0.06246569759999999</v>
+      </c>
+      <c r="Q45">
+        <v>0.1714656976</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1656064340495978</v>
+      </c>
+      <c r="T45">
+        <v>1.534944407671055</v>
+      </c>
+      <c r="U45">
+        <v>0.0912</v>
+      </c>
+      <c r="V45">
+        <v>0.15</v>
+      </c>
+      <c r="W45">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>1.515673069992435</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1545804791668911</v>
+      </c>
+      <c r="C46">
+        <v>1.172601123794721</v>
+      </c>
+      <c r="D46">
+        <v>1.741561123794721</v>
+      </c>
+      <c r="E46">
+        <v>1.56496</v>
+      </c>
+      <c r="F46">
+        <v>1.59896</v>
+      </c>
+      <c r="G46">
+        <v>1.03</v>
+      </c>
+      <c r="H46">
+        <v>3.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.325</v>
+      </c>
+      <c r="K46">
+        <v>0.109</v>
+      </c>
+      <c r="L46">
+        <v>0.216</v>
+      </c>
+      <c r="M46">
+        <v>0.250397136</v>
+      </c>
+      <c r="N46">
+        <v>-0.03439713600000002</v>
+      </c>
+      <c r="O46">
+        <v>-0.005159570400000003</v>
+      </c>
+      <c r="P46">
+        <v>-0.02923756560000002</v>
+      </c>
+      <c r="Q46">
+        <v>0.0797624344</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1689147757746689</v>
+      </c>
+      <c r="T46">
+        <v>1.574990645605453</v>
+      </c>
+      <c r="U46">
+        <v>0.1566</v>
+      </c>
+      <c r="V46">
+        <v>0.1293944512208798</v>
+      </c>
+      <c r="W46">
+        <v>0.1363368289388102</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.8626296748058651</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1557584791668911</v>
+      </c>
+      <c r="C47">
+        <v>1.118720206552606</v>
+      </c>
+      <c r="D47">
+        <v>1.724020206552606</v>
+      </c>
+      <c r="E47">
+        <v>1.6013</v>
+      </c>
+      <c r="F47">
+        <v>1.6353</v>
+      </c>
+      <c r="G47">
+        <v>1.03</v>
+      </c>
+      <c r="H47">
+        <v>3.6</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.325</v>
+      </c>
+      <c r="K47">
+        <v>0.109</v>
+      </c>
+      <c r="L47">
+        <v>0.216</v>
+      </c>
+      <c r="M47">
+        <v>0.25608798</v>
+      </c>
+      <c r="N47">
+        <v>-0.04008798000000005</v>
+      </c>
+      <c r="O47">
+        <v>-0.006013197000000007</v>
+      </c>
+      <c r="P47">
+        <v>-0.03407478300000005</v>
+      </c>
+      <c r="Q47">
+        <v>0.07492521699999996</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.171280498970572</v>
+      </c>
+      <c r="T47">
+        <v>1.603626839161916</v>
+      </c>
+      <c r="U47">
+        <v>0.1566</v>
+      </c>
+      <c r="V47">
+        <v>0.1265190189715269</v>
+      </c>
+      <c r="W47">
+        <v>0.1367871216290589</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.8434601264768458</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1569364791668911</v>
+      </c>
+      <c r="C48">
+        <v>1.065189108446067</v>
+      </c>
+      <c r="D48">
+        <v>1.706829108446067</v>
+      </c>
+      <c r="E48">
+        <v>1.63764</v>
+      </c>
+      <c r="F48">
+        <v>1.67164</v>
+      </c>
+      <c r="G48">
+        <v>1.03</v>
+      </c>
+      <c r="H48">
+        <v>3.6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.325</v>
+      </c>
+      <c r="K48">
+        <v>0.109</v>
+      </c>
+      <c r="L48">
+        <v>0.216</v>
+      </c>
+      <c r="M48">
+        <v>0.261778824</v>
+      </c>
+      <c r="N48">
+        <v>-0.04577882400000002</v>
+      </c>
+      <c r="O48">
+        <v>-0.006866823600000003</v>
+      </c>
+      <c r="P48">
+        <v>-0.03891200040000002</v>
+      </c>
+      <c r="Q48">
+        <v>0.07008799959999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1737338415441011</v>
+      </c>
+      <c r="T48">
+        <v>1.633323632479729</v>
+      </c>
+      <c r="U48">
+        <v>0.1566</v>
+      </c>
+      <c r="V48">
+        <v>0.1237686055156241</v>
+      </c>
+      <c r="W48">
+        <v>0.1372178363762533</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.8251240367708275</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1581144791668911</v>
+      </c>
+      <c r="C49">
+        <v>1.011997468110471</v>
+      </c>
+      <c r="D49">
+        <v>1.689977468110471</v>
+      </c>
+      <c r="E49">
+        <v>1.67398</v>
+      </c>
+      <c r="F49">
+        <v>1.70798</v>
+      </c>
+      <c r="G49">
+        <v>1.03</v>
+      </c>
+      <c r="H49">
+        <v>3.6</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.325</v>
+      </c>
+      <c r="K49">
+        <v>0.109</v>
+      </c>
+      <c r="L49">
+        <v>0.216</v>
+      </c>
+      <c r="M49">
+        <v>0.267469668</v>
+      </c>
+      <c r="N49">
+        <v>-0.05146966800000005</v>
+      </c>
+      <c r="O49">
+        <v>-0.007720450200000007</v>
+      </c>
+      <c r="P49">
+        <v>-0.04374921780000005</v>
+      </c>
+      <c r="Q49">
+        <v>0.06525078219999997</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.176279763082669</v>
+      </c>
+      <c r="T49">
+        <v>1.664141059507648</v>
+      </c>
+      <c r="U49">
+        <v>0.1566</v>
+      </c>
+      <c r="V49">
+        <v>0.1211352309301853</v>
+      </c>
+      <c r="W49">
+        <v>0.137630222836333</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.8075682062012354</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1854481955419411</v>
+      </c>
+      <c r="C50">
+        <v>0.6606630379175302</v>
+      </c>
+      <c r="D50">
+        <v>1.37498303791753</v>
+      </c>
+      <c r="E50">
+        <v>1.71032</v>
+      </c>
+      <c r="F50">
+        <v>1.74432</v>
+      </c>
+      <c r="G50">
+        <v>1.03</v>
+      </c>
+      <c r="H50">
+        <v>3.6</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.325</v>
+      </c>
+      <c r="K50">
+        <v>0.109</v>
+      </c>
+      <c r="L50">
+        <v>0.216</v>
+      </c>
+      <c r="M50">
+        <v>0.364214016</v>
+      </c>
+      <c r="N50">
+        <v>-0.148214016</v>
+      </c>
+      <c r="O50">
+        <v>-0.0222321024</v>
+      </c>
+      <c r="P50">
+        <v>-0.1259819136</v>
+      </c>
+      <c r="Q50">
+        <v>-0.01698191359999998</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1810384438632011</v>
+      </c>
+      <c r="T50">
+        <v>1.72174310869951</v>
+      </c>
+      <c r="U50">
+        <v>0.2088</v>
+      </c>
+      <c r="V50">
+        <v>0.08895868521435485</v>
+      </c>
+      <c r="W50">
+        <v>0.1902254265272427</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5930579014290324</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1871481955419411</v>
+      </c>
+      <c r="C51">
+        <v>0.6085663840807876</v>
+      </c>
+      <c r="D51">
+        <v>1.359226384080787</v>
+      </c>
+      <c r="E51">
+        <v>1.74666</v>
+      </c>
+      <c r="F51">
+        <v>1.78066</v>
+      </c>
+      <c r="G51">
+        <v>1.03</v>
+      </c>
+      <c r="H51">
+        <v>3.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.325</v>
+      </c>
+      <c r="K51">
+        <v>0.109</v>
+      </c>
+      <c r="L51">
+        <v>0.216</v>
+      </c>
+      <c r="M51">
+        <v>0.371801808</v>
+      </c>
+      <c r="N51">
+        <v>-0.155801808</v>
+      </c>
+      <c r="O51">
+        <v>-0.0233702712</v>
+      </c>
+      <c r="P51">
+        <v>-0.1324315368</v>
+      </c>
+      <c r="Q51">
+        <v>-0.02343153680000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1838274329585581</v>
+      </c>
+      <c r="T51">
+        <v>1.75550277749754</v>
+      </c>
+      <c r="U51">
+        <v>0.2088</v>
+      </c>
+      <c r="V51">
+        <v>0.08714320184263331</v>
+      </c>
+      <c r="W51">
+        <v>0.1906044994552582</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5809546789508888</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1888481955419411</v>
+      </c>
+      <c r="C52">
+        <v>0.5568267663473538</v>
+      </c>
+      <c r="D52">
+        <v>1.343826766347354</v>
+      </c>
+      <c r="E52">
+        <v>1.783</v>
+      </c>
+      <c r="F52">
+        <v>1.817</v>
+      </c>
+      <c r="G52">
+        <v>1.03</v>
+      </c>
+      <c r="H52">
+        <v>3.6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.325</v>
+      </c>
+      <c r="K52">
+        <v>0.109</v>
+      </c>
+      <c r="L52">
+        <v>0.216</v>
+      </c>
+      <c r="M52">
+        <v>0.3793896</v>
+      </c>
+      <c r="N52">
+        <v>-0.1633896</v>
+      </c>
+      <c r="O52">
+        <v>-0.02450844</v>
+      </c>
+      <c r="P52">
+        <v>-0.13888116</v>
+      </c>
+      <c r="Q52">
+        <v>-0.02988115999999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1867279816177292</v>
+      </c>
+      <c r="T52">
+        <v>1.790612833047491</v>
+      </c>
+      <c r="U52">
+        <v>0.2088</v>
+      </c>
+      <c r="V52">
+        <v>0.08540033780578064</v>
+      </c>
+      <c r="W52">
+        <v>0.190968409466153</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.569335585371871</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1905481955419411</v>
+      </c>
+      <c r="C53">
+        <v>0.5054321853381245</v>
+      </c>
+      <c r="D53">
+        <v>1.328772185338124</v>
+      </c>
+      <c r="E53">
+        <v>1.81934</v>
+      </c>
+      <c r="F53">
+        <v>1.85334</v>
+      </c>
+      <c r="G53">
+        <v>1.03</v>
+      </c>
+      <c r="H53">
+        <v>3.6</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.325</v>
+      </c>
+      <c r="K53">
+        <v>0.109</v>
+      </c>
+      <c r="L53">
+        <v>0.216</v>
+      </c>
+      <c r="M53">
+        <v>0.386977392</v>
+      </c>
+      <c r="N53">
+        <v>-0.170977392</v>
+      </c>
+      <c r="O53">
+        <v>-0.02564660880000001</v>
+      </c>
+      <c r="P53">
+        <v>-0.1453307832</v>
+      </c>
+      <c r="Q53">
+        <v>-0.03633078320000002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.189746920018091</v>
+      </c>
+      <c r="T53">
+        <v>1.827155952089277</v>
+      </c>
+      <c r="U53">
+        <v>0.2088</v>
+      </c>
+      <c r="V53">
+        <v>0.08372582137821631</v>
+      </c>
+      <c r="W53">
+        <v>0.1913180484962285</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5581721425214421</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1922481955419411</v>
+      </c>
+      <c r="C54">
+        <v>0.4543711734220388</v>
+      </c>
+      <c r="D54">
+        <v>1.314051173422039</v>
+      </c>
+      <c r="E54">
+        <v>1.85568</v>
+      </c>
+      <c r="F54">
+        <v>1.88968</v>
+      </c>
+      <c r="G54">
+        <v>1.03</v>
+      </c>
+      <c r="H54">
+        <v>3.6</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.325</v>
+      </c>
+      <c r="K54">
+        <v>0.109</v>
+      </c>
+      <c r="L54">
+        <v>0.216</v>
+      </c>
+      <c r="M54">
+        <v>0.394565184</v>
+      </c>
+      <c r="N54">
+        <v>-0.178565184</v>
+      </c>
+      <c r="O54">
+        <v>-0.0267847776</v>
+      </c>
+      <c r="P54">
+        <v>-0.1517804064</v>
+      </c>
+      <c r="Q54">
+        <v>-0.0427804064</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1928916475184679</v>
+      </c>
+      <c r="T54">
+        <v>1.865221701091136</v>
+      </c>
+      <c r="U54">
+        <v>0.2088</v>
+      </c>
+      <c r="V54">
+        <v>0.08211570942863523</v>
+      </c>
+      <c r="W54">
+        <v>0.191654239871301</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5474380628575684</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1939481955419411</v>
+      </c>
+      <c r="C55">
+        <v>0.4036327655835563</v>
+      </c>
+      <c r="D55">
+        <v>1.299652765583556</v>
+      </c>
+      <c r="E55">
+        <v>1.89202</v>
+      </c>
+      <c r="F55">
+        <v>1.92602</v>
+      </c>
+      <c r="G55">
+        <v>1.03</v>
+      </c>
+      <c r="H55">
+        <v>3.6</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.325</v>
+      </c>
+      <c r="K55">
+        <v>0.109</v>
+      </c>
+      <c r="L55">
+        <v>0.216</v>
+      </c>
+      <c r="M55">
+        <v>0.4021529760000001</v>
+      </c>
+      <c r="N55">
+        <v>-0.1861529760000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.02792294640000001</v>
+      </c>
+      <c r="P55">
+        <v>-0.1582300296</v>
+      </c>
+      <c r="Q55">
+        <v>-0.04923002960000003</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1961701932103503</v>
+      </c>
+      <c r="T55">
+        <v>1.904907269199459</v>
+      </c>
+      <c r="U55">
+        <v>0.2088</v>
+      </c>
+      <c r="V55">
+        <v>0.08056635642054777</v>
+      </c>
+      <c r="W55">
+        <v>0.1919777447793896</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5371090428036518</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1956481955419411</v>
+      </c>
+      <c r="C56">
+        <v>0.3532064721846548</v>
+      </c>
+      <c r="D56">
+        <v>1.285566472184655</v>
+      </c>
+      <c r="E56">
+        <v>1.92836</v>
+      </c>
+      <c r="F56">
+        <v>1.96236</v>
+      </c>
+      <c r="G56">
+        <v>1.03</v>
+      </c>
+      <c r="H56">
+        <v>3.6</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.325</v>
+      </c>
+      <c r="K56">
+        <v>0.109</v>
+      </c>
+      <c r="L56">
+        <v>0.216</v>
+      </c>
+      <c r="M56">
+        <v>0.409740768</v>
+      </c>
+      <c r="N56">
+        <v>-0.193740768</v>
+      </c>
+      <c r="O56">
+        <v>-0.0290611152</v>
+      </c>
+      <c r="P56">
+        <v>-0.1646796528</v>
+      </c>
+      <c r="Q56">
+        <v>-0.05567965280000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.199591284367097</v>
+      </c>
+      <c r="T56">
+        <v>1.946318296790751</v>
+      </c>
+      <c r="U56">
+        <v>0.2088</v>
+      </c>
+      <c r="V56">
+        <v>0.07907438685720429</v>
+      </c>
+      <c r="W56">
+        <v>0.1922892680242158</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5271625790480287</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1973481955419411</v>
+      </c>
+      <c r="C57">
+        <v>0.3030822534791462</v>
+      </c>
+      <c r="D57">
+        <v>1.271782253479146</v>
+      </c>
+      <c r="E57">
+        <v>1.9647</v>
+      </c>
+      <c r="F57">
+        <v>1.9987</v>
+      </c>
+      <c r="G57">
+        <v>1.03</v>
+      </c>
+      <c r="H57">
+        <v>3.6</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.325</v>
+      </c>
+      <c r="K57">
+        <v>0.109</v>
+      </c>
+      <c r="L57">
+        <v>0.216</v>
+      </c>
+      <c r="M57">
+        <v>0.4173285600000001</v>
+      </c>
+      <c r="N57">
+        <v>-0.2013285600000001</v>
+      </c>
+      <c r="O57">
+        <v>-0.03019928400000001</v>
+      </c>
+      <c r="P57">
+        <v>-0.1711292760000001</v>
+      </c>
+      <c r="Q57">
+        <v>-0.06212927600000004</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2031644240196991</v>
+      </c>
+      <c r="T57">
+        <v>1.989569814497212</v>
+      </c>
+      <c r="U57">
+        <v>0.2088</v>
+      </c>
+      <c r="V57">
+        <v>0.07763667073252785</v>
+      </c>
+      <c r="W57">
+        <v>0.1925894631510482</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.517577804883519</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1990481955419411</v>
+      </c>
+      <c r="C58">
+        <v>0.2532504957491892</v>
+      </c>
+      <c r="D58">
+        <v>1.258290495749189</v>
+      </c>
+      <c r="E58">
+        <v>2.00104</v>
+      </c>
+      <c r="F58">
+        <v>2.03504</v>
+      </c>
+      <c r="G58">
+        <v>1.03</v>
+      </c>
+      <c r="H58">
+        <v>3.6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.325</v>
+      </c>
+      <c r="K58">
+        <v>0.109</v>
+      </c>
+      <c r="L58">
+        <v>0.216</v>
+      </c>
+      <c r="M58">
+        <v>0.424916352</v>
+      </c>
+      <c r="N58">
+        <v>-0.208916352</v>
+      </c>
+      <c r="O58">
+        <v>-0.0313374528</v>
+      </c>
+      <c r="P58">
+        <v>-0.1775788992</v>
+      </c>
+      <c r="Q58">
+        <v>-0.06857889919999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.206899979111056</v>
+      </c>
+      <c r="T58">
+        <v>2.03478731028124</v>
+      </c>
+      <c r="U58">
+        <v>0.2088</v>
+      </c>
+      <c r="V58">
+        <v>0.07625030161230416</v>
+      </c>
+      <c r="W58">
+        <v>0.1928789370233509</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5083353440820277</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2182626615124374</v>
+      </c>
+      <c r="C59">
+        <v>0.08218954762652908</v>
+      </c>
+      <c r="D59">
+        <v>1.123569547626529</v>
+      </c>
+      <c r="E59">
+        <v>2.03738</v>
+      </c>
+      <c r="F59">
+        <v>2.07138</v>
+      </c>
+      <c r="G59">
+        <v>1.03</v>
+      </c>
+      <c r="H59">
+        <v>3.6</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.325</v>
+      </c>
+      <c r="K59">
+        <v>0.109</v>
+      </c>
+      <c r="L59">
+        <v>0.216</v>
+      </c>
+      <c r="M59">
+        <v>0.494645544</v>
+      </c>
+      <c r="N59">
+        <v>-0.2786455440000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.04179683160000001</v>
+      </c>
+      <c r="P59">
+        <v>-0.2368487124000001</v>
+      </c>
+      <c r="Q59">
+        <v>-0.1278487124000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2117731553008392</v>
+      </c>
+      <c r="T59">
+        <v>2.093775283534852</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.06550144925595447</v>
+      </c>
+      <c r="W59">
+        <v>0.2231582539176781</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.4366763283730298</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2202626615124373</v>
+      </c>
+      <c r="C60">
+        <v>0.03346606842191635</v>
+      </c>
+      <c r="D60">
+        <v>1.111186068421916</v>
+      </c>
+      <c r="E60">
+        <v>2.07372</v>
+      </c>
+      <c r="F60">
+        <v>2.10772</v>
+      </c>
+      <c r="G60">
+        <v>1.03</v>
+      </c>
+      <c r="H60">
+        <v>3.6</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.325</v>
+      </c>
+      <c r="K60">
+        <v>0.109</v>
+      </c>
+      <c r="L60">
+        <v>0.216</v>
+      </c>
+      <c r="M60">
+        <v>0.5033235359999999</v>
+      </c>
+      <c r="N60">
+        <v>-0.2873235359999999</v>
+      </c>
+      <c r="O60">
+        <v>-0.04309853039999999</v>
+      </c>
+      <c r="P60">
+        <v>-0.2442250055999999</v>
+      </c>
+      <c r="Q60">
+        <v>-0.1352250055999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.215891563760383</v>
+      </c>
+      <c r="T60">
+        <v>2.143627075999967</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.06437211392395528</v>
+      </c>
+      <c r="W60">
+        <v>0.2234279391949595</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.4291474261597018</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2222626615124373</v>
+      </c>
+      <c r="C61">
+        <v>-0.01498741624315336</v>
+      </c>
+      <c r="D61">
+        <v>1.099072583756846</v>
+      </c>
+      <c r="E61">
+        <v>2.11006</v>
+      </c>
+      <c r="F61">
+        <v>2.14406</v>
+      </c>
+      <c r="G61">
+        <v>1.03</v>
+      </c>
+      <c r="H61">
+        <v>3.6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.325</v>
+      </c>
+      <c r="K61">
+        <v>0.109</v>
+      </c>
+      <c r="L61">
+        <v>0.216</v>
+      </c>
+      <c r="M61">
+        <v>0.512001528</v>
+      </c>
+      <c r="N61">
+        <v>-0.296001528</v>
+      </c>
+      <c r="O61">
+        <v>-0.0444002292</v>
+      </c>
+      <c r="P61">
+        <v>-0.2516012988</v>
+      </c>
+      <c r="Q61">
+        <v>-0.1426012988</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.220210870193563</v>
+      </c>
+      <c r="T61">
+        <v>2.195910663219478</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.06328106114558314</v>
+      </c>
+      <c r="W61">
+        <v>0.2236884825984347</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.4218737409705543</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2242626615124373</v>
+      </c>
+      <c r="C62">
+        <v>-0.06317964110387742</v>
+      </c>
+      <c r="D62">
+        <v>1.087220358896122</v>
+      </c>
+      <c r="E62">
+        <v>2.1464</v>
+      </c>
+      <c r="F62">
+        <v>2.1804</v>
+      </c>
+      <c r="G62">
+        <v>1.03</v>
+      </c>
+      <c r="H62">
+        <v>3.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.325</v>
+      </c>
+      <c r="K62">
+        <v>0.109</v>
+      </c>
+      <c r="L62">
+        <v>0.216</v>
+      </c>
+      <c r="M62">
+        <v>0.52067952</v>
+      </c>
+      <c r="N62">
+        <v>-0.30467952</v>
+      </c>
+      <c r="O62">
+        <v>-0.045701928</v>
+      </c>
+      <c r="P62">
+        <v>-0.258977592</v>
+      </c>
+      <c r="Q62">
+        <v>-0.149977592</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2247461419484021</v>
+      </c>
+      <c r="T62">
+        <v>2.250808429799965</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.06222637679315676</v>
+      </c>
+      <c r="W62">
+        <v>0.2239403412217942</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.4148425119543784</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2262626615124373</v>
+      </c>
+      <c r="C63">
+        <v>-0.1111189681391869</v>
+      </c>
+      <c r="D63">
+        <v>1.075621031860813</v>
+      </c>
+      <c r="E63">
+        <v>2.18274</v>
+      </c>
+      <c r="F63">
+        <v>2.21674</v>
+      </c>
+      <c r="G63">
+        <v>1.03</v>
+      </c>
+      <c r="H63">
+        <v>3.6</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.325</v>
+      </c>
+      <c r="K63">
+        <v>0.109</v>
+      </c>
+      <c r="L63">
+        <v>0.216</v>
+      </c>
+      <c r="M63">
+        <v>0.5293575119999999</v>
+      </c>
+      <c r="N63">
+        <v>-0.3133575119999999</v>
+      </c>
+      <c r="O63">
+        <v>-0.04700362679999999</v>
+      </c>
+      <c r="P63">
+        <v>-0.2663538852</v>
+      </c>
+      <c r="Q63">
+        <v>-0.1573538852</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2295139917419509</v>
+      </c>
+      <c r="T63">
+        <v>2.308521466461503</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.06120627225556403</v>
+      </c>
+      <c r="W63">
+        <v>0.2241839421853713</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4080418150370935</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2282626615124373</v>
+      </c>
+      <c r="C64">
+        <v>-0.1588134062461402</v>
+      </c>
+      <c r="D64">
+        <v>1.06426659375386</v>
+      </c>
+      <c r="E64">
+        <v>2.21908</v>
+      </c>
+      <c r="F64">
+        <v>2.25308</v>
+      </c>
+      <c r="G64">
+        <v>1.03</v>
+      </c>
+      <c r="H64">
+        <v>3.6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.325</v>
+      </c>
+      <c r="K64">
+        <v>0.109</v>
+      </c>
+      <c r="L64">
+        <v>0.216</v>
+      </c>
+      <c r="M64">
+        <v>0.538035504</v>
+      </c>
+      <c r="N64">
+        <v>-0.322035504</v>
+      </c>
+      <c r="O64">
+        <v>-0.0483053256</v>
+      </c>
+      <c r="P64">
+        <v>-0.2737301784</v>
+      </c>
+      <c r="Q64">
+        <v>-0.1647301784</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.234532780998318</v>
+      </c>
+      <c r="T64">
+        <v>2.369272031368384</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.06021907431595815</v>
+      </c>
+      <c r="W64">
+        <v>0.2244196850533492</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.401460495439721</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2302626615124373</v>
+      </c>
+      <c r="C65">
+        <v>-0.2062706296812147</v>
+      </c>
+      <c r="D65">
+        <v>1.053149370318785</v>
+      </c>
+      <c r="E65">
+        <v>2.25542</v>
+      </c>
+      <c r="F65">
+        <v>2.28942</v>
+      </c>
+      <c r="G65">
+        <v>1.03</v>
+      </c>
+      <c r="H65">
+        <v>3.6</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.325</v>
+      </c>
+      <c r="K65">
+        <v>0.109</v>
+      </c>
+      <c r="L65">
+        <v>0.216</v>
+      </c>
+      <c r="M65">
+        <v>0.546713496</v>
+      </c>
+      <c r="N65">
+        <v>-0.330713496</v>
+      </c>
+      <c r="O65">
+        <v>-0.0496070244</v>
+      </c>
+      <c r="P65">
+        <v>-0.2811064716</v>
+      </c>
+      <c r="Q65">
+        <v>-0.1721064716</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2398228561604347</v>
+      </c>
+      <c r="T65">
+        <v>2.433306410594557</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.05926321599348262</v>
+      </c>
+      <c r="W65">
+        <v>0.2246479440207564</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3950881066232175</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2322626615124374</v>
+      </c>
+      <c r="C66">
+        <v>-0.2534979953577285</v>
+      </c>
+      <c r="D66">
+        <v>1.042262004642271</v>
+      </c>
+      <c r="E66">
+        <v>2.29176</v>
+      </c>
+      <c r="F66">
+        <v>2.32576</v>
+      </c>
+      <c r="G66">
+        <v>1.03</v>
+      </c>
+      <c r="H66">
+        <v>3.6</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.325</v>
+      </c>
+      <c r="K66">
+        <v>0.109</v>
+      </c>
+      <c r="L66">
+        <v>0.216</v>
+      </c>
+      <c r="M66">
+        <v>0.5553914879999999</v>
+      </c>
+      <c r="N66">
+        <v>-0.339391488</v>
+      </c>
+      <c r="O66">
+        <v>-0.05090872319999999</v>
+      </c>
+      <c r="P66">
+        <v>-0.2884827648</v>
+      </c>
+      <c r="Q66">
+        <v>-0.1794827647999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2454068243871135</v>
+      </c>
+      <c r="T66">
+        <v>2.500898255333295</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05833722824358446</v>
+      </c>
+      <c r="W66">
+        <v>0.224869069895432</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3889148549572298</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2342626615124374</v>
+      </c>
+      <c r="C67">
+        <v>-0.3005025590813322</v>
+      </c>
+      <c r="D67">
+        <v>1.031597440918668</v>
+      </c>
+      <c r="E67">
+        <v>2.3281</v>
+      </c>
+      <c r="F67">
+        <v>2.3621</v>
+      </c>
+      <c r="G67">
+        <v>1.03</v>
+      </c>
+      <c r="H67">
+        <v>3.6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.325</v>
+      </c>
+      <c r="K67">
+        <v>0.109</v>
+      </c>
+      <c r="L67">
+        <v>0.216</v>
+      </c>
+      <c r="M67">
+        <v>0.56406948</v>
+      </c>
+      <c r="N67">
+        <v>-0.34806948</v>
+      </c>
+      <c r="O67">
+        <v>-0.05221042200000001</v>
+      </c>
+      <c r="P67">
+        <v>-0.295859058</v>
+      </c>
+      <c r="Q67">
+        <v>-0.186859058</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2513098765124596</v>
+      </c>
+      <c r="T67">
+        <v>2.57235249119996</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.05743973242445239</v>
+      </c>
+      <c r="W67">
+        <v>0.2250833918970408</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3829315494963492</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2362626615124374</v>
+      </c>
+      <c r="C68">
+        <v>-0.3472910907988456</v>
+      </c>
+      <c r="D68">
+        <v>1.021148909201154</v>
+      </c>
+      <c r="E68">
+        <v>2.36444</v>
+      </c>
+      <c r="F68">
+        <v>2.39844</v>
+      </c>
+      <c r="G68">
+        <v>1.03</v>
+      </c>
+      <c r="H68">
+        <v>3.6</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.325</v>
+      </c>
+      <c r="K68">
+        <v>0.109</v>
+      </c>
+      <c r="L68">
+        <v>0.216</v>
+      </c>
+      <c r="M68">
+        <v>0.572747472</v>
+      </c>
+      <c r="N68">
+        <v>-0.356747472</v>
+      </c>
+      <c r="O68">
+        <v>-0.0535121208</v>
+      </c>
+      <c r="P68">
+        <v>-0.3032353512</v>
+      </c>
+      <c r="Q68">
+        <v>-0.1942353512</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2575601669981202</v>
+      </c>
+      <c r="T68">
+        <v>2.648009917411724</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.05656943344832432</v>
+      </c>
+      <c r="W68">
+        <v>0.2252912192925402</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3771295563221622</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2382626615124374</v>
+      </c>
+      <c r="C69">
+        <v>-0.393870088929706</v>
+      </c>
+      <c r="D69">
+        <v>1.010909911070294</v>
+      </c>
+      <c r="E69">
+        <v>2.40078</v>
+      </c>
+      <c r="F69">
+        <v>2.43478</v>
+      </c>
+      <c r="G69">
+        <v>1.03</v>
+      </c>
+      <c r="H69">
+        <v>3.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.325</v>
+      </c>
+      <c r="K69">
+        <v>0.109</v>
+      </c>
+      <c r="L69">
+        <v>0.216</v>
+      </c>
+      <c r="M69">
+        <v>0.5814254640000001</v>
+      </c>
+      <c r="N69">
+        <v>-0.3654254640000001</v>
+      </c>
+      <c r="O69">
+        <v>-0.05481381960000001</v>
+      </c>
+      <c r="P69">
+        <v>-0.3106116444000001</v>
+      </c>
+      <c r="Q69">
+        <v>-0.2016116444</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2641892629677602</v>
+      </c>
+      <c r="T69">
+        <v>2.728252642181777</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.05572511354611052</v>
+      </c>
+      <c r="W69">
+        <v>0.2254928428851888</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3715007569740701</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2402626615124374</v>
+      </c>
+      <c r="C70">
+        <v>-0.4402457938437694</v>
+      </c>
+      <c r="D70">
+        <v>1.000874206156231</v>
+      </c>
+      <c r="E70">
+        <v>2.43712</v>
+      </c>
+      <c r="F70">
+        <v>2.47112</v>
+      </c>
+      <c r="G70">
+        <v>1.03</v>
+      </c>
+      <c r="H70">
+        <v>3.6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.325</v>
+      </c>
+      <c r="K70">
+        <v>0.109</v>
+      </c>
+      <c r="L70">
+        <v>0.216</v>
+      </c>
+      <c r="M70">
+        <v>0.590103456</v>
+      </c>
+      <c r="N70">
+        <v>-0.3741034560000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.05611551840000001</v>
+      </c>
+      <c r="P70">
+        <v>-0.3179879376</v>
+      </c>
+      <c r="Q70">
+        <v>-0.2089879376</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2712326774355027</v>
+      </c>
+      <c r="T70">
+        <v>2.813510537249957</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.05490562658219713</v>
+      </c>
+      <c r="W70">
+        <v>0.2256885363721713</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3660375105479808</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2422626615124374</v>
+      </c>
+      <c r="C71">
+        <v>-0.4864242005442048</v>
+      </c>
+      <c r="D71">
+        <v>0.9910357994557951</v>
+      </c>
+      <c r="E71">
+        <v>2.47346</v>
+      </c>
+      <c r="F71">
+        <v>2.50746</v>
+      </c>
+      <c r="G71">
+        <v>1.03</v>
+      </c>
+      <c r="H71">
+        <v>3.6</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.325</v>
+      </c>
+      <c r="K71">
+        <v>0.109</v>
+      </c>
+      <c r="L71">
+        <v>0.216</v>
+      </c>
+      <c r="M71">
+        <v>0.598781448</v>
+      </c>
+      <c r="N71">
+        <v>-0.382781448</v>
+      </c>
+      <c r="O71">
+        <v>-0.0574172172</v>
+      </c>
+      <c r="P71">
+        <v>-0.3253642308</v>
+      </c>
+      <c r="Q71">
+        <v>-0.2163642308</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2787305057398738</v>
+      </c>
+      <c r="T71">
+        <v>2.904268941677375</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.05410989286361457</v>
+      </c>
+      <c r="W71">
+        <v>0.2258785575841689</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3607326190907638</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2442626615124374</v>
+      </c>
+      <c r="C72">
+        <v>-0.532411070609653</v>
+      </c>
+      <c r="D72">
+        <v>0.9813889293903471</v>
+      </c>
+      <c r="E72">
+        <v>2.5098</v>
+      </c>
+      <c r="F72">
+        <v>2.5438</v>
+      </c>
+      <c r="G72">
+        <v>1.03</v>
+      </c>
+      <c r="H72">
+        <v>3.6</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.325</v>
+      </c>
+      <c r="K72">
+        <v>0.109</v>
+      </c>
+      <c r="L72">
+        <v>0.216</v>
+      </c>
+      <c r="M72">
+        <v>0.6074594400000001</v>
+      </c>
+      <c r="N72">
+        <v>-0.3914594400000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.05871891600000001</v>
+      </c>
+      <c r="P72">
+        <v>-0.3327405240000001</v>
+      </c>
+      <c r="Q72">
+        <v>-0.2237405240000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2867281892645362</v>
+      </c>
+      <c r="T72">
+        <v>3.001077906399954</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.05333689439413435</v>
+      </c>
+      <c r="W72">
+        <v>0.2260631496186807</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3555792959608957</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2462626615124373</v>
+      </c>
+      <c r="C73">
+        <v>-0.5782119434456212</v>
+      </c>
+      <c r="D73">
+        <v>0.9719280565543786</v>
+      </c>
+      <c r="E73">
+        <v>2.54614</v>
+      </c>
+      <c r="F73">
+        <v>2.58014</v>
+      </c>
+      <c r="G73">
+        <v>1.03</v>
+      </c>
+      <c r="H73">
+        <v>3.6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.325</v>
+      </c>
+      <c r="K73">
+        <v>0.109</v>
+      </c>
+      <c r="L73">
+        <v>0.216</v>
+      </c>
+      <c r="M73">
+        <v>0.6161374319999999</v>
+      </c>
+      <c r="N73">
+        <v>-0.400137432</v>
+      </c>
+      <c r="O73">
+        <v>-0.06002061479999999</v>
+      </c>
+      <c r="P73">
+        <v>-0.3401168172</v>
+      </c>
+      <c r="Q73">
+        <v>-0.2311168172</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2952774371702098</v>
+      </c>
+      <c r="T73">
+        <v>3.104563351448228</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.05258567052942825</v>
+      </c>
+      <c r="W73">
+        <v>0.2262425418775725</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.350571136862855</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2482626615124374</v>
+      </c>
+      <c r="C74">
+        <v>-0.6238321468912997</v>
+      </c>
+      <c r="D74">
+        <v>0.9626478531087</v>
+      </c>
+      <c r="E74">
+        <v>2.58248</v>
+      </c>
+      <c r="F74">
+        <v>2.61648</v>
+      </c>
+      <c r="G74">
+        <v>1.03</v>
+      </c>
+      <c r="H74">
+        <v>3.6</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.325</v>
+      </c>
+      <c r="K74">
+        <v>0.109</v>
+      </c>
+      <c r="L74">
+        <v>0.216</v>
+      </c>
+      <c r="M74">
+        <v>0.624815424</v>
+      </c>
+      <c r="N74">
+        <v>-0.408815424</v>
+      </c>
+      <c r="O74">
+        <v>-0.0613223136</v>
+      </c>
+      <c r="P74">
+        <v>-0.3474931104</v>
+      </c>
+      <c r="Q74">
+        <v>-0.2384931104</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3044373456405745</v>
+      </c>
+      <c r="T74">
+        <v>3.21544061399995</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0518553139942973</v>
+      </c>
+      <c r="W74">
+        <v>0.2264169510181618</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3457020932953153</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2502626615124374</v>
+      </c>
+      <c r="C75">
+        <v>-0.6692768072244626</v>
+      </c>
+      <c r="D75">
+        <v>0.9535431927755371</v>
+      </c>
+      <c r="E75">
+        <v>2.61882</v>
+      </c>
+      <c r="F75">
+        <v>2.65282</v>
+      </c>
+      <c r="G75">
+        <v>1.03</v>
+      </c>
+      <c r="H75">
+        <v>3.6</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.325</v>
+      </c>
+      <c r="K75">
+        <v>0.109</v>
+      </c>
+      <c r="L75">
+        <v>0.216</v>
+      </c>
+      <c r="M75">
+        <v>0.633493416</v>
+      </c>
+      <c r="N75">
+        <v>-0.417493416</v>
+      </c>
+      <c r="O75">
+        <v>-0.0626240124</v>
+      </c>
+      <c r="P75">
+        <v>-0.3548694036</v>
+      </c>
+      <c r="Q75">
+        <v>-0.2458694036</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3142757658494846</v>
+      </c>
+      <c r="T75">
+        <v>3.334531007111059</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.05114496722725213</v>
+      </c>
+      <c r="W75">
+        <v>0.2265865818261322</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3409664481816809</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2522626615124374</v>
+      </c>
+      <c r="C76">
+        <v>-0.7145508586039351</v>
+      </c>
+      <c r="D76">
+        <v>0.9446091413960646</v>
+      </c>
+      <c r="E76">
+        <v>2.65516</v>
+      </c>
+      <c r="F76">
+        <v>2.68916</v>
+      </c>
+      <c r="G76">
+        <v>1.03</v>
+      </c>
+      <c r="H76">
+        <v>3.6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.325</v>
+      </c>
+      <c r="K76">
+        <v>0.109</v>
+      </c>
+      <c r="L76">
+        <v>0.216</v>
+      </c>
+      <c r="M76">
+        <v>0.6421714079999999</v>
+      </c>
+      <c r="N76">
+        <v>-0.426171408</v>
+      </c>
+      <c r="O76">
+        <v>-0.0639257112</v>
+      </c>
+      <c r="P76">
+        <v>-0.3622456968</v>
+      </c>
+      <c r="Q76">
+        <v>-0.2532456968</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3248709876129263</v>
+      </c>
+      <c r="T76">
+        <v>3.462782199692254</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.05045381902147845</v>
+      </c>
+      <c r="W76">
+        <v>0.226751628017671</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.336358793476523</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2542626615124374</v>
+      </c>
+      <c r="C77">
+        <v>-0.7596590519861706</v>
+      </c>
+      <c r="D77">
+        <v>0.9358409480138292</v>
+      </c>
+      <c r="E77">
+        <v>2.6915</v>
+      </c>
+      <c r="F77">
+        <v>2.7255</v>
+      </c>
+      <c r="G77">
+        <v>1.03</v>
+      </c>
+      <c r="H77">
+        <v>3.6</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.325</v>
+      </c>
+      <c r="K77">
+        <v>0.109</v>
+      </c>
+      <c r="L77">
+        <v>0.216</v>
+      </c>
+      <c r="M77">
+        <v>0.6508494</v>
+      </c>
+      <c r="N77">
+        <v>-0.4348494000000001</v>
+      </c>
+      <c r="O77">
+        <v>-0.06522741</v>
+      </c>
+      <c r="P77">
+        <v>-0.3696219900000001</v>
+      </c>
+      <c r="Q77">
+        <v>-0.2606219900000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3363138271174434</v>
+      </c>
+      <c r="T77">
+        <v>3.601293487679945</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.0497811014345254</v>
+      </c>
+      <c r="W77">
+        <v>0.2269122729774354</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3318740095635027</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2562626615124374</v>
+      </c>
+      <c r="C78">
+        <v>-0.8046059635497937</v>
+      </c>
+      <c r="D78">
+        <v>0.9272340364502061</v>
+      </c>
+      <c r="E78">
+        <v>2.72784</v>
+      </c>
+      <c r="F78">
+        <v>2.76184</v>
+      </c>
+      <c r="G78">
+        <v>1.03</v>
+      </c>
+      <c r="H78">
+        <v>3.6</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.325</v>
+      </c>
+      <c r="K78">
+        <v>0.109</v>
+      </c>
+      <c r="L78">
+        <v>0.216</v>
+      </c>
+      <c r="M78">
+        <v>0.659527392</v>
+      </c>
+      <c r="N78">
+        <v>-0.443527392</v>
+      </c>
+      <c r="O78">
+        <v>-0.0665291088</v>
+      </c>
+      <c r="P78">
+        <v>-0.3769982832</v>
+      </c>
+      <c r="Q78">
+        <v>-0.2679982832</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3487102365806702</v>
+      </c>
+      <c r="T78">
+        <v>3.751347382999942</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04912608694196586</v>
+      </c>
+      <c r="W78">
+        <v>0.2270686904382586</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3275072462797723</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2582626615124374</v>
+      </c>
+      <c r="C79">
+        <v>-0.8493960026595002</v>
+      </c>
+      <c r="D79">
+        <v>0.9187839973404995</v>
+      </c>
+      <c r="E79">
+        <v>2.76418</v>
+      </c>
+      <c r="F79">
+        <v>2.79818</v>
+      </c>
+      <c r="G79">
+        <v>1.03</v>
+      </c>
+      <c r="H79">
+        <v>3.6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.325</v>
+      </c>
+      <c r="K79">
+        <v>0.109</v>
+      </c>
+      <c r="L79">
+        <v>0.216</v>
+      </c>
+      <c r="M79">
+        <v>0.668205384</v>
+      </c>
+      <c r="N79">
+        <v>-0.452205384</v>
+      </c>
+      <c r="O79">
+        <v>-0.0678308076</v>
+      </c>
+      <c r="P79">
+        <v>-0.3843745764</v>
+      </c>
+      <c r="Q79">
+        <v>-0.2753745764</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3621845946928732</v>
+      </c>
+      <c r="T79">
+        <v>3.914449443130374</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04848808581284943</v>
+      </c>
+      <c r="W79">
+        <v>0.2272210451078916</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3232539054189961</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2602626615124374</v>
+      </c>
+      <c r="C80">
+        <v>-0.8940334193984292</v>
+      </c>
+      <c r="D80">
+        <v>0.9104865806015708</v>
+      </c>
+      <c r="E80">
+        <v>2.80052</v>
+      </c>
+      <c r="F80">
+        <v>2.83452</v>
+      </c>
+      <c r="G80">
+        <v>1.03</v>
+      </c>
+      <c r="H80">
+        <v>3.6</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.325</v>
+      </c>
+      <c r="K80">
+        <v>0.109</v>
+      </c>
+      <c r="L80">
+        <v>0.216</v>
+      </c>
+      <c r="M80">
+        <v>0.676883376</v>
+      </c>
+      <c r="N80">
+        <v>-0.4608833760000001</v>
+      </c>
+      <c r="O80">
+        <v>-0.0691325064</v>
+      </c>
+      <c r="P80">
+        <v>-0.3917508696000001</v>
+      </c>
+      <c r="Q80">
+        <v>-0.2827508696000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3768838944516402</v>
+      </c>
+      <c r="T80">
+        <v>4.092378963272664</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04786644368704365</v>
+      </c>
+      <c r="W80">
+        <v>0.227369493247534</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.319109624580291</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2622626615124374</v>
+      </c>
+      <c r="C81">
+        <v>-0.9385223116960439</v>
+      </c>
+      <c r="D81">
+        <v>0.9023376883039561</v>
+      </c>
+      <c r="E81">
+        <v>2.83686</v>
+      </c>
+      <c r="F81">
+        <v>2.87086</v>
+      </c>
+      <c r="G81">
+        <v>1.03</v>
+      </c>
+      <c r="H81">
+        <v>3.6</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.325</v>
+      </c>
+      <c r="K81">
+        <v>0.109</v>
+      </c>
+      <c r="L81">
+        <v>0.216</v>
+      </c>
+      <c r="M81">
+        <v>0.685561368</v>
+      </c>
+      <c r="N81">
+        <v>-0.469561368</v>
+      </c>
+      <c r="O81">
+        <v>-0.0704342052</v>
+      </c>
+      <c r="P81">
+        <v>-0.3991271628</v>
+      </c>
+      <c r="Q81">
+        <v>-0.2901271628000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.392983127520766</v>
+      </c>
+      <c r="T81">
+        <v>4.287254151999934</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04726053933657475</v>
+      </c>
+      <c r="W81">
+        <v>0.227514183206426</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3150702622438316</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2642626615124374</v>
+      </c>
+      <c r="C82">
+        <v>-0.9828666320766419</v>
+      </c>
+      <c r="D82">
+        <v>0.894333367923358</v>
+      </c>
+      <c r="E82">
+        <v>2.8732</v>
+      </c>
+      <c r="F82">
+        <v>2.9072</v>
+      </c>
+      <c r="G82">
+        <v>1.03</v>
+      </c>
+      <c r="H82">
+        <v>3.6</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.325</v>
+      </c>
+      <c r="K82">
+        <v>0.109</v>
+      </c>
+      <c r="L82">
+        <v>0.216</v>
+      </c>
+      <c r="M82">
+        <v>0.6942393600000001</v>
+      </c>
+      <c r="N82">
+        <v>-0.4782393600000001</v>
+      </c>
+      <c r="O82">
+        <v>-0.07173590400000002</v>
+      </c>
+      <c r="P82">
+        <v>-0.4065034560000001</v>
+      </c>
+      <c r="Q82">
+        <v>-0.2975034560000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4106922838968043</v>
+      </c>
+      <c r="T82">
+        <v>4.501616859599932</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04666978259486756</v>
+      </c>
+      <c r="W82">
+        <v>0.2276552559163456</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3111318839657837</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2662626615124373</v>
+      </c>
+      <c r="C83">
+        <v>-1.027070194051841</v>
+      </c>
+      <c r="D83">
+        <v>0.8864698059481594</v>
+      </c>
+      <c r="E83">
+        <v>2.90954</v>
+      </c>
+      <c r="F83">
+        <v>2.94354</v>
+      </c>
+      <c r="G83">
+        <v>1.03</v>
+      </c>
+      <c r="H83">
+        <v>3.6</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.325</v>
+      </c>
+      <c r="K83">
+        <v>0.109</v>
+      </c>
+      <c r="L83">
+        <v>0.216</v>
+      </c>
+      <c r="M83">
+        <v>0.7029173520000001</v>
+      </c>
+      <c r="N83">
+        <v>-0.4869173520000001</v>
+      </c>
+      <c r="O83">
+        <v>-0.0730376028</v>
+      </c>
+      <c r="P83">
+        <v>-0.4138797492000001</v>
+      </c>
+      <c r="Q83">
+        <v>-0.3048797492</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4302655619966361</v>
+      </c>
+      <c r="T83">
+        <v>4.73854406273677</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04609361243937537</v>
+      </c>
+      <c r="W83">
+        <v>0.2277928453494772</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3072907495958358</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2682626615124374</v>
+      </c>
+      <c r="C84">
+        <v>-1.071136678178759</v>
+      </c>
+      <c r="D84">
+        <v>0.8787433218212407</v>
+      </c>
+      <c r="E84">
+        <v>2.94588</v>
+      </c>
+      <c r="F84">
+        <v>2.97988</v>
+      </c>
+      <c r="G84">
+        <v>1.03</v>
+      </c>
+      <c r="H84">
+        <v>3.6</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.325</v>
+      </c>
+      <c r="K84">
+        <v>0.109</v>
+      </c>
+      <c r="L84">
+        <v>0.216</v>
+      </c>
+      <c r="M84">
+        <v>0.711595344</v>
+      </c>
+      <c r="N84">
+        <v>-0.495595344</v>
+      </c>
+      <c r="O84">
+        <v>-0.0743393016</v>
+      </c>
+      <c r="P84">
+        <v>-0.4212560424</v>
+      </c>
+      <c r="Q84">
+        <v>-0.3122560424</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4520136487742271</v>
+      </c>
+      <c r="T84">
+        <v>5.001796510666591</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04553149521450494</v>
+      </c>
+      <c r="W84">
+        <v>0.2279270789427762</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3035433014300329</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2702626615124374</v>
+      </c>
+      <c r="C85">
+        <v>-1.11506963780412</v>
+      </c>
+      <c r="D85">
+        <v>0.8711503621958799</v>
+      </c>
+      <c r="E85">
+        <v>2.98222</v>
+      </c>
+      <c r="F85">
+        <v>3.01622</v>
+      </c>
+      <c r="G85">
+        <v>1.03</v>
+      </c>
+      <c r="H85">
+        <v>3.6</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.325</v>
+      </c>
+      <c r="K85">
+        <v>0.109</v>
+      </c>
+      <c r="L85">
+        <v>0.216</v>
+      </c>
+      <c r="M85">
+        <v>0.7202733360000001</v>
+      </c>
+      <c r="N85">
+        <v>-0.5042733360000001</v>
+      </c>
+      <c r="O85">
+        <v>-0.07564100040000002</v>
+      </c>
+      <c r="P85">
+        <v>-0.4286323356000001</v>
+      </c>
+      <c r="Q85">
+        <v>-0.3196323356000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4763203339962404</v>
+      </c>
+      <c r="T85">
+        <v>5.296019834823449</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.04498292298300488</v>
+      </c>
+      <c r="W85">
+        <v>0.2280580779916584</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2998861532200325</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2722626615124374</v>
+      </c>
+      <c r="C86">
+        <v>-1.158872504513103</v>
+      </c>
+      <c r="D86">
+        <v>0.8636874954868968</v>
+      </c>
+      <c r="E86">
+        <v>3.01856</v>
+      </c>
+      <c r="F86">
+        <v>3.05256</v>
+      </c>
+      <c r="G86">
+        <v>1.03</v>
+      </c>
+      <c r="H86">
+        <v>3.6</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.325</v>
+      </c>
+      <c r="K86">
+        <v>0.109</v>
+      </c>
+      <c r="L86">
+        <v>0.216</v>
+      </c>
+      <c r="M86">
+        <v>0.728951328</v>
+      </c>
+      <c r="N86">
+        <v>-0.512951328</v>
+      </c>
+      <c r="O86">
+        <v>-0.07694269919999999</v>
+      </c>
+      <c r="P86">
+        <v>-0.4360086288</v>
+      </c>
+      <c r="Q86">
+        <v>-0.3270086288</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5036653548710053</v>
+      </c>
+      <c r="T86">
+        <v>5.627021074499913</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.04444741199511197</v>
+      </c>
+      <c r="W86">
+        <v>0.2281859580155673</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2963160799674132</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2742626615124374</v>
+      </c>
+      <c r="C87">
+        <v>-1.202548593300507</v>
+      </c>
+      <c r="D87">
+        <v>0.8563514066994925</v>
+      </c>
+      <c r="E87">
+        <v>3.0549</v>
+      </c>
+      <c r="F87">
+        <v>3.0889</v>
+      </c>
+      <c r="G87">
+        <v>1.03</v>
+      </c>
+      <c r="H87">
+        <v>3.6</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.325</v>
+      </c>
+      <c r="K87">
+        <v>0.109</v>
+      </c>
+      <c r="L87">
+        <v>0.216</v>
+      </c>
+      <c r="M87">
+        <v>0.73762932</v>
+      </c>
+      <c r="N87">
+        <v>-0.5216293200000001</v>
+      </c>
+      <c r="O87">
+        <v>-0.07824439800000001</v>
+      </c>
+      <c r="P87">
+        <v>-0.4433849220000001</v>
+      </c>
+      <c r="Q87">
+        <v>-0.334384922</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5346563785290723</v>
+      </c>
+      <c r="T87">
+        <v>6.002155812799907</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04392450126575771</v>
+      </c>
+      <c r="W87">
+        <v>0.2283108290977371</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2928300084383847</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2762626615124374</v>
+      </c>
+      <c r="C88">
+        <v>-1.246101107480591</v>
+      </c>
+      <c r="D88">
+        <v>0.8491388925194083</v>
+      </c>
+      <c r="E88">
+        <v>3.09124</v>
+      </c>
+      <c r="F88">
+        <v>3.12524</v>
+      </c>
+      <c r="G88">
+        <v>1.03</v>
+      </c>
+      <c r="H88">
+        <v>3.6</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.325</v>
+      </c>
+      <c r="K88">
+        <v>0.109</v>
+      </c>
+      <c r="L88">
+        <v>0.216</v>
+      </c>
+      <c r="M88">
+        <v>0.746307312</v>
+      </c>
+      <c r="N88">
+        <v>-0.530307312</v>
+      </c>
+      <c r="O88">
+        <v>-0.07954609680000001</v>
+      </c>
+      <c r="P88">
+        <v>-0.4507612152</v>
+      </c>
+      <c r="Q88">
+        <v>-0.3417612152</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.570074691281149</v>
+      </c>
+      <c r="T88">
+        <v>6.4308812279999</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.04341375125103959</v>
+      </c>
+      <c r="W88">
+        <v>0.2284327962012518</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.289425008340264</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2782626615124373</v>
+      </c>
+      <c r="C89">
+        <v>-1.289533143350871</v>
+      </c>
+      <c r="D89">
+        <v>0.8420468566491288</v>
+      </c>
+      <c r="E89">
+        <v>3.12758</v>
+      </c>
+      <c r="F89">
+        <v>3.16158</v>
+      </c>
+      <c r="G89">
+        <v>1.03</v>
+      </c>
+      <c r="H89">
+        <v>3.6</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.325</v>
+      </c>
+      <c r="K89">
+        <v>0.109</v>
+      </c>
+      <c r="L89">
+        <v>0.216</v>
+      </c>
+      <c r="M89">
+        <v>0.754985304</v>
+      </c>
+      <c r="N89">
+        <v>-0.538985304</v>
+      </c>
+      <c r="O89">
+        <v>-0.08084779559999999</v>
+      </c>
+      <c r="P89">
+        <v>-0.4581375084</v>
+      </c>
+      <c r="Q89">
+        <v>-0.3491375084</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6109419752258525</v>
+      </c>
+      <c r="T89">
+        <v>6.925564399384507</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04291474261597018</v>
+      </c>
+      <c r="W89">
+        <v>0.2285519594633063</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2860982841064679</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2802626615124374</v>
+      </c>
+      <c r="C90">
+        <v>-1.332847694624139</v>
+      </c>
+      <c r="D90">
+        <v>0.8350723053758606</v>
+      </c>
+      <c r="E90">
+        <v>3.16392</v>
+      </c>
+      <c r="F90">
+        <v>3.19792</v>
+      </c>
+      <c r="G90">
+        <v>1.03</v>
+      </c>
+      <c r="H90">
+        <v>3.6</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.325</v>
+      </c>
+      <c r="K90">
+        <v>0.109</v>
+      </c>
+      <c r="L90">
+        <v>0.216</v>
+      </c>
+      <c r="M90">
+        <v>0.763663296</v>
+      </c>
+      <c r="N90">
+        <v>-0.5476632960000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.08214949440000001</v>
+      </c>
+      <c r="P90">
+        <v>-0.4655138016000001</v>
+      </c>
+      <c r="Q90">
+        <v>-0.3565138016</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6586204731613405</v>
+      </c>
+      <c r="T90">
+        <v>7.502694765999885</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04242707508624324</v>
+      </c>
+      <c r="W90">
+        <v>0.2286684144694051</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2828471672416216</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2822626615124374</v>
+      </c>
+      <c r="C91">
+        <v>-1.376047656642037</v>
+      </c>
+      <c r="D91">
+        <v>0.8282123433579626</v>
+      </c>
+      <c r="E91">
+        <v>3.20026</v>
+      </c>
+      <c r="F91">
+        <v>3.23426</v>
+      </c>
+      <c r="G91">
+        <v>1.03</v>
+      </c>
+      <c r="H91">
+        <v>3.6</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.325</v>
+      </c>
+      <c r="K91">
+        <v>0.109</v>
+      </c>
+      <c r="L91">
+        <v>0.216</v>
+      </c>
+      <c r="M91">
+        <v>0.772341288</v>
+      </c>
+      <c r="N91">
+        <v>-0.556341288</v>
+      </c>
+      <c r="O91">
+        <v>-0.08345119320000001</v>
+      </c>
+      <c r="P91">
+        <v>-0.4728900948</v>
+      </c>
+      <c r="Q91">
+        <v>-0.3638900948</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7149677889032804</v>
+      </c>
+      <c r="T91">
+        <v>8.184757926545329</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04195036637740904</v>
+      </c>
+      <c r="W91">
+        <v>0.2287822525090747</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2796691091827269</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2842626615124373</v>
+      </c>
+      <c r="C92">
+        <v>-1.419135830382637</v>
+      </c>
+      <c r="D92">
+        <v>0.821464169617363</v>
+      </c>
+      <c r="E92">
+        <v>3.2366</v>
+      </c>
+      <c r="F92">
+        <v>3.2706</v>
+      </c>
+      <c r="G92">
+        <v>1.03</v>
+      </c>
+      <c r="H92">
+        <v>3.6</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.325</v>
+      </c>
+      <c r="K92">
+        <v>0.109</v>
+      </c>
+      <c r="L92">
+        <v>0.216</v>
+      </c>
+      <c r="M92">
+        <v>0.78101928</v>
+      </c>
+      <c r="N92">
+        <v>-0.56501928</v>
+      </c>
+      <c r="O92">
+        <v>-0.084752892</v>
+      </c>
+      <c r="P92">
+        <v>-0.480266388</v>
+      </c>
+      <c r="Q92">
+        <v>-0.371266388</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7825845677936085</v>
+      </c>
+      <c r="T92">
+        <v>9.003233719199862</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04148425119543784</v>
+      </c>
+      <c r="W92">
+        <v>0.2288935608145294</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2765616746362523</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2862626615124374</v>
+      </c>
+      <c r="C93">
+        <v>-1.462114926273684</v>
+      </c>
+      <c r="D93">
+        <v>0.8148250737263161</v>
+      </c>
+      <c r="E93">
+        <v>3.27294</v>
+      </c>
+      <c r="F93">
+        <v>3.30694</v>
+      </c>
+      <c r="G93">
+        <v>1.03</v>
+      </c>
+      <c r="H93">
+        <v>3.6</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.325</v>
+      </c>
+      <c r="K93">
+        <v>0.109</v>
+      </c>
+      <c r="L93">
+        <v>0.216</v>
+      </c>
+      <c r="M93">
+        <v>0.7896972720000001</v>
+      </c>
+      <c r="N93">
+        <v>-0.5736972720000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.08605459080000001</v>
+      </c>
+      <c r="P93">
+        <v>-0.4876426812000001</v>
+      </c>
+      <c r="Q93">
+        <v>-0.3786426812000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8652272975484541</v>
+      </c>
+      <c r="T93">
+        <v>10.00359302133318</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04102838030318028</v>
+      </c>
+      <c r="W93">
+        <v>0.2290024227836006</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2735225353545352</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2882626615124373</v>
+      </c>
+      <c r="C94">
+        <v>-1.504987567822412</v>
+      </c>
+      <c r="D94">
+        <v>0.8082924321775874</v>
+      </c>
+      <c r="E94">
+        <v>3.30928</v>
+      </c>
+      <c r="F94">
+        <v>3.34328</v>
+      </c>
+      <c r="G94">
+        <v>1.03</v>
+      </c>
+      <c r="H94">
+        <v>3.6</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.325</v>
+      </c>
+      <c r="K94">
+        <v>0.109</v>
+      </c>
+      <c r="L94">
+        <v>0.216</v>
+      </c>
+      <c r="M94">
+        <v>0.798375264</v>
+      </c>
+      <c r="N94">
+        <v>-0.5823752640000001</v>
+      </c>
+      <c r="O94">
+        <v>-0.08735628960000001</v>
+      </c>
+      <c r="P94">
+        <v>-0.4950189744</v>
+      </c>
+      <c r="Q94">
+        <v>-0.3860189744</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9685307097420111</v>
+      </c>
+      <c r="T94">
+        <v>11.25404214899983</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04058241964771093</v>
+      </c>
+      <c r="W94">
+        <v>0.2291089181881266</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2705494643180728</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2902626615124374</v>
+      </c>
+      <c r="C95">
+        <v>-1.547756295072145</v>
+      </c>
+      <c r="D95">
+        <v>0.8018637049278551</v>
+      </c>
+      <c r="E95">
+        <v>3.34562</v>
+      </c>
+      <c r="F95">
+        <v>3.37962</v>
+      </c>
+      <c r="G95">
+        <v>1.03</v>
+      </c>
+      <c r="H95">
+        <v>3.6</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.325</v>
+      </c>
+      <c r="K95">
+        <v>0.109</v>
+      </c>
+      <c r="L95">
+        <v>0.216</v>
+      </c>
+      <c r="M95">
+        <v>0.8070532560000001</v>
+      </c>
+      <c r="N95">
+        <v>-0.5910532560000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.08865798840000001</v>
+      </c>
+      <c r="P95">
+        <v>-0.5023952676000001</v>
+      </c>
+      <c r="Q95">
+        <v>-0.3933952676000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.101349382562298</v>
+      </c>
+      <c r="T95">
+        <v>12.86176245599981</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0401460495439721</v>
+      </c>
+      <c r="W95">
+        <v>0.2292131233688995</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2676403302931473</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2922626615124374</v>
+      </c>
+      <c r="C96">
+        <v>-1.590423567895235</v>
+      </c>
+      <c r="D96">
+        <v>0.7955364321047649</v>
+      </c>
+      <c r="E96">
+        <v>3.38196</v>
+      </c>
+      <c r="F96">
+        <v>3.41596</v>
+      </c>
+      <c r="G96">
+        <v>1.03</v>
+      </c>
+      <c r="H96">
+        <v>3.6</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.325</v>
+      </c>
+      <c r="K96">
+        <v>0.109</v>
+      </c>
+      <c r="L96">
+        <v>0.216</v>
+      </c>
+      <c r="M96">
+        <v>0.8157312480000001</v>
+      </c>
+      <c r="N96">
+        <v>-0.5997312480000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.08995968720000001</v>
+      </c>
+      <c r="P96">
+        <v>-0.5097715608000001</v>
+      </c>
+      <c r="Q96">
+        <v>-0.4007715608000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.278440946322682</v>
+      </c>
+      <c r="T96">
+        <v>15.00538953199978</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03971896391052559</v>
+      </c>
+      <c r="W96">
+        <v>0.2293151114181665</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2647930927368372</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2942626615124374</v>
+      </c>
+      <c r="C97">
+        <v>-1.632991769131336</v>
+      </c>
+      <c r="D97">
+        <v>0.7893082308686638</v>
+      </c>
+      <c r="E97">
+        <v>3.4183</v>
+      </c>
+      <c r="F97">
+        <v>3.4523</v>
+      </c>
+      <c r="G97">
+        <v>1.03</v>
+      </c>
+      <c r="H97">
+        <v>3.6</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.325</v>
+      </c>
+      <c r="K97">
+        <v>0.109</v>
+      </c>
+      <c r="L97">
+        <v>0.216</v>
+      </c>
+      <c r="M97">
+        <v>0.82440924</v>
+      </c>
+      <c r="N97">
+        <v>-0.6084092400000001</v>
+      </c>
+      <c r="O97">
+        <v>-0.09126138600000001</v>
+      </c>
+      <c r="P97">
+        <v>-0.5171478540000001</v>
+      </c>
+      <c r="Q97">
+        <v>-0.4081478540000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.526369135587219</v>
+      </c>
+      <c r="T97">
+        <v>18.00646743839975</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03930086955357269</v>
+      </c>
+      <c r="W97">
+        <v>0.2294149523506069</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2620057970238179</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2962626615124374</v>
+      </c>
+      <c r="C98">
+        <v>-1.675463207579396</v>
+      </c>
+      <c r="D98">
+        <v>0.7831767924206032</v>
+      </c>
+      <c r="E98">
+        <v>3.45464</v>
+      </c>
+      <c r="F98">
+        <v>3.48864</v>
+      </c>
+      <c r="G98">
+        <v>1.03</v>
+      </c>
+      <c r="H98">
+        <v>3.6</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.325</v>
+      </c>
+      <c r="K98">
+        <v>0.109</v>
+      </c>
+      <c r="L98">
+        <v>0.216</v>
+      </c>
+      <c r="M98">
+        <v>0.833087232</v>
+      </c>
+      <c r="N98">
+        <v>-0.617087232</v>
+      </c>
+      <c r="O98">
+        <v>-0.0925630848</v>
+      </c>
+      <c r="P98">
+        <v>-0.5245241472000001</v>
+      </c>
+      <c r="Q98">
+        <v>-0.4155241472000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.898261419484019</v>
+      </c>
+      <c r="T98">
+        <v>22.50808429799963</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03889148549572297</v>
+      </c>
+      <c r="W98">
+        <v>0.2295127132636214</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2592765699714864</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2982626615124374</v>
+      </c>
+      <c r="C99">
+        <v>-1.717840120851275</v>
+      </c>
+      <c r="D99">
+        <v>0.7771398791487253</v>
+      </c>
+      <c r="E99">
+        <v>3.49098</v>
+      </c>
+      <c r="F99">
+        <v>3.52498</v>
+      </c>
+      <c r="G99">
+        <v>1.03</v>
+      </c>
+      <c r="H99">
+        <v>3.6</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.325</v>
+      </c>
+      <c r="K99">
+        <v>0.109</v>
+      </c>
+      <c r="L99">
+        <v>0.216</v>
+      </c>
+      <c r="M99">
+        <v>0.841765224</v>
+      </c>
+      <c r="N99">
+        <v>-0.625765224</v>
+      </c>
+      <c r="O99">
+        <v>-0.0938647836</v>
+      </c>
+      <c r="P99">
+        <v>-0.5319004404000001</v>
+      </c>
+      <c r="Q99">
+        <v>-0.4229004404000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.518081892645359</v>
+      </c>
+      <c r="T99">
+        <v>30.01077906399951</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03849054234628253</v>
+      </c>
+      <c r="W99">
+        <v>0.2296084584877077</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2566036156418835</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3002626615124374</v>
+      </c>
+      <c r="C100">
+        <v>-1.760124678094388</v>
+      </c>
+      <c r="D100">
+        <v>0.771195321905612</v>
+      </c>
+      <c r="E100">
+        <v>3.52732</v>
+      </c>
+      <c r="F100">
+        <v>3.56132</v>
+      </c>
+      <c r="G100">
+        <v>1.03</v>
+      </c>
+      <c r="H100">
+        <v>3.6</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.325</v>
+      </c>
+      <c r="K100">
+        <v>0.109</v>
+      </c>
+      <c r="L100">
+        <v>0.216</v>
+      </c>
+      <c r="M100">
+        <v>0.8504432159999999</v>
+      </c>
+      <c r="N100">
+        <v>-0.634443216</v>
+      </c>
+      <c r="O100">
+        <v>-0.09516648239999999</v>
+      </c>
+      <c r="P100">
+        <v>-0.5392767335999999</v>
+      </c>
+      <c r="Q100">
+        <v>-0.4302767336</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.757722838968039</v>
+      </c>
+      <c r="T100">
+        <v>45.01616859599927</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03809778171009597</v>
+      </c>
+      <c r="W100">
+        <v>0.2297022497276291</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2539852114006398</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3022626615124374</v>
+      </c>
+      <c r="C101">
+        <v>-1.802318982590353</v>
+      </c>
+      <c r="D101">
+        <v>0.7653410174096467</v>
+      </c>
+      <c r="E101">
+        <v>3.56366</v>
+      </c>
+      <c r="F101">
+        <v>3.59766</v>
+      </c>
+      <c r="G101">
+        <v>1.03</v>
+      </c>
+      <c r="H101">
+        <v>3.6</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.325</v>
+      </c>
+      <c r="K101">
+        <v>0.109</v>
+      </c>
+      <c r="L101">
+        <v>0.216</v>
+      </c>
+      <c r="M101">
+        <v>0.859121208</v>
+      </c>
+      <c r="N101">
+        <v>-0.6431212080000001</v>
+      </c>
+      <c r="O101">
+        <v>-0.0964681812</v>
+      </c>
+      <c r="P101">
+        <v>-0.5466530268000001</v>
+      </c>
+      <c r="Q101">
+        <v>-0.4376530268000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.476645677936078</v>
+      </c>
+      <c r="T101">
+        <v>90.03233719199854</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03771295563221622</v>
+      </c>
+      <c r="W101">
+        <v>0.2297941461950268</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2514197042147748</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/oman/oman_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_chemical_specialty.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1175575463200601</v>
+        <v>0.11741946000058</v>
       </c>
       <c r="C2">
-        <v>4.012168203170761</v>
+        <v>3.977345976082947</v>
       </c>
       <c r="D2">
-        <v>2.732168203170761</v>
+        <v>2.737435976082947</v>
       </c>
       <c r="E2">
-        <v>-0.029</v>
+        <v>0.01109000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.04009000000000001</v>
       </c>
       <c r="G2">
         <v>1.28</v>
@@ -1451,28 +1451,28 @@
         <v>0.167</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002016527</v>
       </c>
       <c r="N2">
-        <v>0.167</v>
+        <v>0.164983473</v>
       </c>
       <c r="O2">
-        <v>0.02505</v>
+        <v>0.02474752095</v>
       </c>
       <c r="P2">
-        <v>0.14195</v>
+        <v>0.14023595205</v>
       </c>
       <c r="Q2">
-        <v>0.21695</v>
+        <v>0.21523595205</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1175575463200601</v>
+        <v>0.1181736464652323</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778209</v>
+        <v>0.9432712317228323</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>82.81565285265211</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.11741946000058</v>
+        <v>0.1172813736810999</v>
       </c>
       <c r="C3">
-        <v>3.977345976082947</v>
+        <v>3.942544101356477</v>
       </c>
       <c r="D3">
-        <v>2.737435976082947</v>
+        <v>2.742724101356477</v>
       </c>
       <c r="E3">
-        <v>0.01109000000000001</v>
+        <v>0.05118000000000002</v>
       </c>
       <c r="F3">
-        <v>0.04009000000000001</v>
+        <v>0.08018000000000002</v>
       </c>
       <c r="G3">
         <v>1.28</v>
@@ -1533,28 +1533,28 @@
         <v>0.167</v>
       </c>
       <c r="M3">
-        <v>0.002016527</v>
+        <v>0.004033054</v>
       </c>
       <c r="N3">
-        <v>0.164983473</v>
+        <v>0.162966946</v>
       </c>
       <c r="O3">
-        <v>0.02474752095</v>
+        <v>0.0244450419</v>
       </c>
       <c r="P3">
-        <v>0.14023595205</v>
+        <v>0.1385219041</v>
       </c>
       <c r="Q3">
-        <v>0.21523595205</v>
+        <v>0.2135219041</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1181736464652323</v>
+        <v>0.118802320082755</v>
       </c>
       <c r="T3">
-        <v>0.9432712317228323</v>
+        <v>0.9514649564626403</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>82.81565285265211</v>
+        <v>41.40782642632605</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1172813736810999</v>
+        <v>0.1171432873616198</v>
       </c>
       <c r="C4">
-        <v>3.942544101356477</v>
+        <v>3.907762697168525</v>
       </c>
       <c r="D4">
-        <v>2.742724101356477</v>
+        <v>2.748032697168525</v>
       </c>
       <c r="E4">
-        <v>0.05118000000000002</v>
+        <v>0.09127</v>
       </c>
       <c r="F4">
-        <v>0.08018000000000002</v>
+        <v>0.12027</v>
       </c>
       <c r="G4">
         <v>1.28</v>
@@ -1615,28 +1615,28 @@
         <v>0.167</v>
       </c>
       <c r="M4">
-        <v>0.004033054</v>
+        <v>0.006049581</v>
       </c>
       <c r="N4">
-        <v>0.162966946</v>
+        <v>0.160950419</v>
       </c>
       <c r="O4">
-        <v>0.0244450419</v>
+        <v>0.02414256285</v>
       </c>
       <c r="P4">
-        <v>0.1385219041</v>
+        <v>0.13680785615</v>
       </c>
       <c r="Q4">
-        <v>0.2135219041</v>
+        <v>0.21180785615</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.118802320082755</v>
+        <v>0.1194439560429071</v>
       </c>
       <c r="T4">
-        <v>0.9514649564626403</v>
+        <v>0.9598276239805883</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>41.40782642632605</v>
+        <v>27.6052176175507</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1171432873616198</v>
+        <v>0.1170052010421398</v>
       </c>
       <c r="C5">
-        <v>3.907762697168525</v>
+        <v>3.873001882612976</v>
       </c>
       <c r="D5">
-        <v>2.748032697168525</v>
+        <v>2.753361882612976</v>
       </c>
       <c r="E5">
-        <v>0.09127</v>
+        <v>0.13136</v>
       </c>
       <c r="F5">
-        <v>0.12027</v>
+        <v>0.16036</v>
       </c>
       <c r="G5">
         <v>1.28</v>
@@ -1697,28 +1697,28 @@
         <v>0.167</v>
       </c>
       <c r="M5">
-        <v>0.006049581</v>
+        <v>0.008066108000000001</v>
       </c>
       <c r="N5">
-        <v>0.160950419</v>
+        <v>0.158933892</v>
       </c>
       <c r="O5">
-        <v>0.02414256285</v>
+        <v>0.0238400838</v>
       </c>
       <c r="P5">
-        <v>0.13680785615</v>
+        <v>0.1350938082</v>
       </c>
       <c r="Q5">
-        <v>0.21180785615</v>
+        <v>0.2100938082</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1194439560429071</v>
+        <v>0.1200989594188956</v>
       </c>
       <c r="T5">
-        <v>0.9598276239805883</v>
+        <v>0.9683645137384936</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.6052176175507</v>
+        <v>20.70391321316303</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1170052010421398</v>
+        <v>0.1168671147226597</v>
       </c>
       <c r="C6">
-        <v>3.873001882612976</v>
+        <v>3.83826177770933</v>
       </c>
       <c r="D6">
-        <v>2.753361882612976</v>
+        <v>2.75871177770933</v>
       </c>
       <c r="E6">
-        <v>0.13136</v>
+        <v>0.17145</v>
       </c>
       <c r="F6">
-        <v>0.16036</v>
+        <v>0.20045</v>
       </c>
       <c r="G6">
         <v>1.28</v>
@@ -1779,28 +1779,28 @@
         <v>0.167</v>
       </c>
       <c r="M6">
-        <v>0.008066108000000001</v>
+        <v>0.010082635</v>
       </c>
       <c r="N6">
-        <v>0.158933892</v>
+        <v>0.156917365</v>
       </c>
       <c r="O6">
-        <v>0.0238400838</v>
+        <v>0.02353760475</v>
       </c>
       <c r="P6">
-        <v>0.1350938082</v>
+        <v>0.13337976025</v>
       </c>
       <c r="Q6">
-        <v>0.2100938082</v>
+        <v>0.20837976025</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1200989594188956</v>
+        <v>0.1207677523396418</v>
       </c>
       <c r="T6">
-        <v>0.9683645137384936</v>
+        <v>0.9770811274913024</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.70391321316303</v>
+        <v>16.56313057053042</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1168671147226597</v>
+        <v>0.1167290284031796</v>
       </c>
       <c r="C7">
-        <v>3.83826177770933</v>
+        <v>3.803542503411715</v>
       </c>
       <c r="D7">
-        <v>2.75871177770933</v>
+        <v>2.764082503411716</v>
       </c>
       <c r="E7">
-        <v>0.17145</v>
+        <v>0.21154</v>
       </c>
       <c r="F7">
-        <v>0.20045</v>
+        <v>0.24054</v>
       </c>
       <c r="G7">
         <v>1.28</v>
@@ -1861,28 +1861,28 @@
         <v>0.167</v>
       </c>
       <c r="M7">
-        <v>0.010082635</v>
+        <v>0.012099162</v>
       </c>
       <c r="N7">
-        <v>0.156917365</v>
+        <v>0.154900838</v>
       </c>
       <c r="O7">
-        <v>0.02353760475</v>
+        <v>0.0232351257</v>
       </c>
       <c r="P7">
-        <v>0.13337976025</v>
+        <v>0.1316657123</v>
       </c>
       <c r="Q7">
-        <v>0.20837976025</v>
+        <v>0.2066657123</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1207677523396418</v>
+        <v>0.1214507748969996</v>
       </c>
       <c r="T7">
-        <v>0.9770811274913024</v>
+        <v>0.985983201111192</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.56313057053042</v>
+        <v>13.80260880877535</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1167290284031796</v>
+        <v>0.1166801920836995</v>
       </c>
       <c r="C8">
-        <v>3.803542503411715</v>
+        <v>3.765356951075268</v>
       </c>
       <c r="D8">
-        <v>2.764082503411716</v>
+        <v>2.765986951075268</v>
       </c>
       <c r="E8">
-        <v>0.21154</v>
+        <v>0.25163</v>
       </c>
       <c r="F8">
-        <v>0.24054</v>
+        <v>0.28063</v>
       </c>
       <c r="G8">
         <v>1.28</v>
@@ -1943,45 +1943,45 @@
         <v>0.167</v>
       </c>
       <c r="M8">
-        <v>0.012099162</v>
+        <v>0.014536634</v>
       </c>
       <c r="N8">
-        <v>0.154900838</v>
+        <v>0.152463366</v>
       </c>
       <c r="O8">
-        <v>0.0232351257</v>
+        <v>0.0228695049</v>
       </c>
       <c r="P8">
-        <v>0.1316657123</v>
+        <v>0.1295938611</v>
       </c>
       <c r="Q8">
-        <v>0.2066657123</v>
+        <v>0.2045938611</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1214507748969996</v>
+        <v>0.1221484861115048</v>
       </c>
       <c r="T8">
-        <v>0.985983201111192</v>
+        <v>0.9950767171745202</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.15</v>
       </c>
       <c r="W8">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.80260880877535</v>
+        <v>11.48821659814783</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1166801920836995</v>
+        <v>0.1165548557642194</v>
       </c>
       <c r="C9">
-        <v>3.765356951075268</v>
+        <v>3.73016666601968</v>
       </c>
       <c r="D9">
-        <v>2.765986951075268</v>
+        <v>2.770886666019681</v>
       </c>
       <c r="E9">
-        <v>0.25163</v>
+        <v>0.29172</v>
       </c>
       <c r="F9">
-        <v>0.28063</v>
+        <v>0.3207200000000001</v>
       </c>
       <c r="G9">
         <v>1.28</v>
@@ -2025,28 +2025,28 @@
         <v>0.167</v>
       </c>
       <c r="M9">
-        <v>0.014536634</v>
+        <v>0.016613296</v>
       </c>
       <c r="N9">
-        <v>0.152463366</v>
+        <v>0.150386704</v>
       </c>
       <c r="O9">
-        <v>0.0228695049</v>
+        <v>0.0225580056</v>
       </c>
       <c r="P9">
-        <v>0.1295938611</v>
+        <v>0.1278286984</v>
       </c>
       <c r="Q9">
-        <v>0.2045938611</v>
+        <v>0.2028286984</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1221484861115048</v>
+        <v>0.1228613649611081</v>
       </c>
       <c r="T9">
-        <v>0.9950767171745202</v>
+        <v>1.00436791836966</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.48821659814782</v>
+        <v>10.05218952337935</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1165548557642194</v>
+        <v>0.1165595694447393</v>
       </c>
       <c r="C10">
-        <v>3.73016666601968</v>
+        <v>3.689892082159109</v>
       </c>
       <c r="D10">
-        <v>2.770886666019681</v>
+        <v>2.770702082159109</v>
       </c>
       <c r="E10">
-        <v>0.29172</v>
+        <v>0.33181</v>
       </c>
       <c r="F10">
-        <v>0.3207200000000001</v>
+        <v>0.36081</v>
       </c>
       <c r="G10">
         <v>1.28</v>
@@ -2107,45 +2107,45 @@
         <v>0.167</v>
       </c>
       <c r="M10">
-        <v>0.016613296</v>
+        <v>0.019303335</v>
       </c>
       <c r="N10">
-        <v>0.150386704</v>
+        <v>0.147696665</v>
       </c>
       <c r="O10">
-        <v>0.0225580056</v>
+        <v>0.02215449975</v>
       </c>
       <c r="P10">
-        <v>0.1278286984</v>
+        <v>0.12554216525</v>
       </c>
       <c r="Q10">
-        <v>0.2028286984</v>
+        <v>0.20054216525</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1228613649611081</v>
+        <v>0.1235899114777355</v>
       </c>
       <c r="T10">
-        <v>1.00436791836966</v>
+        <v>1.013863321788868</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.15</v>
       </c>
       <c r="W10">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.05218952337935</v>
+        <v>8.65135480475265</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1165595694447393</v>
+        <v>0.1164486831252592</v>
       </c>
       <c r="C11">
-        <v>3.689892082159109</v>
+        <v>3.654150825018502</v>
       </c>
       <c r="D11">
-        <v>2.770702082159109</v>
+        <v>2.775050825018502</v>
       </c>
       <c r="E11">
-        <v>0.33181</v>
+        <v>0.3719</v>
       </c>
       <c r="F11">
-        <v>0.36081</v>
+        <v>0.4009</v>
       </c>
       <c r="G11">
         <v>1.28</v>
@@ -2189,28 +2189,28 @@
         <v>0.167</v>
       </c>
       <c r="M11">
-        <v>0.019303335</v>
+        <v>0.02144815</v>
       </c>
       <c r="N11">
-        <v>0.147696665</v>
+        <v>0.14555185</v>
       </c>
       <c r="O11">
-        <v>0.02215449975</v>
+        <v>0.0218327775</v>
       </c>
       <c r="P11">
-        <v>0.12554216525</v>
+        <v>0.1237190725</v>
       </c>
       <c r="Q11">
-        <v>0.20054216525</v>
+        <v>0.1987190725</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1235899114777355</v>
+        <v>0.1243346479169547</v>
       </c>
       <c r="T11">
-        <v>1.013863321788868</v>
+        <v>1.023569734172949</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.65135480475265</v>
+        <v>7.786219324277386</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1164486831252592</v>
+        <v>0.1164125968057791</v>
       </c>
       <c r="C12">
-        <v>3.654150825018502</v>
+        <v>3.615479004991695</v>
       </c>
       <c r="D12">
-        <v>2.775050825018502</v>
+        <v>2.776469004991695</v>
       </c>
       <c r="E12">
-        <v>0.3719</v>
+        <v>0.41199</v>
       </c>
       <c r="F12">
-        <v>0.4009</v>
+        <v>0.44099</v>
       </c>
       <c r="G12">
         <v>1.28</v>
@@ -2271,45 +2271,45 @@
         <v>0.167</v>
       </c>
       <c r="M12">
-        <v>0.02144815</v>
+        <v>0.023945757</v>
       </c>
       <c r="N12">
-        <v>0.14555185</v>
+        <v>0.143054243</v>
       </c>
       <c r="O12">
-        <v>0.0218327775</v>
+        <v>0.02145813645</v>
       </c>
       <c r="P12">
-        <v>0.1237190725</v>
+        <v>0.12159610655</v>
       </c>
       <c r="Q12">
-        <v>0.1987190725</v>
+        <v>0.19659610655</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1243346479169547</v>
+        <v>0.1250961200064934</v>
       </c>
       <c r="T12">
-        <v>1.023569734172949</v>
+        <v>1.033494268183637</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.15</v>
       </c>
       <c r="W12">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.786219324277385</v>
+        <v>6.974095661289805</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1164125968057791</v>
+        <v>0.116308510486299</v>
       </c>
       <c r="C13">
-        <v>3.615479004991695</v>
+        <v>3.579487693758299</v>
       </c>
       <c r="D13">
-        <v>2.776469004991695</v>
+        <v>2.780567693758298</v>
       </c>
       <c r="E13">
-        <v>0.41199</v>
+        <v>0.45208</v>
       </c>
       <c r="F13">
-        <v>0.44099</v>
+        <v>0.48108</v>
       </c>
       <c r="G13">
         <v>1.28</v>
@@ -2353,28 +2353,28 @@
         <v>0.167</v>
       </c>
       <c r="M13">
-        <v>0.023945757</v>
+        <v>0.026122644</v>
       </c>
       <c r="N13">
-        <v>0.143054243</v>
+        <v>0.140877356</v>
       </c>
       <c r="O13">
-        <v>0.02145813645</v>
+        <v>0.0211316034</v>
       </c>
       <c r="P13">
-        <v>0.12159610655</v>
+        <v>0.1197457526</v>
       </c>
       <c r="Q13">
-        <v>0.19659610655</v>
+        <v>0.1947457526</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1250961200064934</v>
+        <v>0.1258748982798853</v>
       </c>
       <c r="T13">
-        <v>1.033494268183637</v>
+        <v>1.043644359785477</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.974095661289805</v>
+        <v>6.392921022848989</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.116308510486299</v>
+        <v>0.1163149241668189</v>
       </c>
       <c r="C14">
-        <v>3.579487693758299</v>
+        <v>3.539144787397519</v>
       </c>
       <c r="D14">
-        <v>2.780567693758298</v>
+        <v>2.780314787397518</v>
       </c>
       <c r="E14">
-        <v>0.45208</v>
+        <v>0.49217</v>
       </c>
       <c r="F14">
-        <v>0.48108</v>
+        <v>0.52117</v>
       </c>
       <c r="G14">
         <v>1.28</v>
@@ -2435,45 +2435,45 @@
         <v>0.167</v>
       </c>
       <c r="M14">
-        <v>0.026122644</v>
+        <v>0.028820701</v>
       </c>
       <c r="N14">
-        <v>0.140877356</v>
+        <v>0.138179299</v>
       </c>
       <c r="O14">
-        <v>0.0211316034</v>
+        <v>0.02072689485</v>
       </c>
       <c r="P14">
-        <v>0.1197457526</v>
+        <v>0.11745240415</v>
       </c>
       <c r="Q14">
-        <v>0.1947457526</v>
+        <v>0.19245240415</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1258748982798853</v>
+        <v>0.1266715795020907</v>
       </c>
       <c r="T14">
-        <v>1.043644359785477</v>
+        <v>1.05402778682644</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.392921022848989</v>
+        <v>5.794446151743498</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1163149241668189</v>
+        <v>0.1162193378473388</v>
       </c>
       <c r="C15">
-        <v>3.539144787397519</v>
+        <v>3.502828751562014</v>
       </c>
       <c r="D15">
-        <v>2.780314787397518</v>
+        <v>2.784088751562015</v>
       </c>
       <c r="E15">
-        <v>0.49217</v>
+        <v>0.5322600000000001</v>
       </c>
       <c r="F15">
-        <v>0.52117</v>
+        <v>0.5612600000000001</v>
       </c>
       <c r="G15">
         <v>1.28</v>
@@ -2517,28 +2517,28 @@
         <v>0.167</v>
       </c>
       <c r="M15">
-        <v>0.028820701</v>
+        <v>0.03103767800000001</v>
       </c>
       <c r="N15">
-        <v>0.138179299</v>
+        <v>0.135962322</v>
       </c>
       <c r="O15">
-        <v>0.02072689485</v>
+        <v>0.0203943483</v>
       </c>
       <c r="P15">
-        <v>0.11745240415</v>
+        <v>0.1155679737</v>
       </c>
       <c r="Q15">
-        <v>0.19245240415</v>
+        <v>0.1905679737</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1266715795020907</v>
+        <v>0.1274867881945801</v>
       </c>
       <c r="T15">
-        <v>1.05402778682644</v>
+        <v>1.064652688914868</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.794446151743498</v>
+        <v>5.380557140904676</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1162193378473388</v>
+        <v>0.1161237515278588</v>
       </c>
       <c r="C16">
-        <v>3.502828751562014</v>
+        <v>3.466522975115025</v>
       </c>
       <c r="D16">
-        <v>2.784088751562015</v>
+        <v>2.787872975115024</v>
       </c>
       <c r="E16">
-        <v>0.5322600000000001</v>
+        <v>0.5723500000000001</v>
       </c>
       <c r="F16">
-        <v>0.5612600000000001</v>
+        <v>0.6013500000000002</v>
       </c>
       <c r="G16">
         <v>1.28</v>
@@ -2599,28 +2599,28 @@
         <v>0.167</v>
       </c>
       <c r="M16">
-        <v>0.03103767800000001</v>
+        <v>0.03325465500000001</v>
       </c>
       <c r="N16">
-        <v>0.135962322</v>
+        <v>0.133745345</v>
       </c>
       <c r="O16">
-        <v>0.0203943483</v>
+        <v>0.02006180175</v>
       </c>
       <c r="P16">
-        <v>0.1155679737</v>
+        <v>0.11368354325</v>
       </c>
       <c r="Q16">
-        <v>0.1905679737</v>
+        <v>0.18868354325</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1274867881945801</v>
+        <v>0.1283211782680691</v>
       </c>
       <c r="T16">
-        <v>1.064652688914868</v>
+        <v>1.075527588699494</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.380557140904676</v>
+        <v>5.021853331511031</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1161237515278588</v>
+        <v>0.1160281652083787</v>
       </c>
       <c r="C17">
-        <v>3.466522975115025</v>
+        <v>3.430227499948166</v>
       </c>
       <c r="D17">
-        <v>2.787872975115024</v>
+        <v>2.791667499948166</v>
       </c>
       <c r="E17">
-        <v>0.57235</v>
+        <v>0.6124400000000001</v>
       </c>
       <c r="F17">
-        <v>0.6013500000000001</v>
+        <v>0.6414400000000001</v>
       </c>
       <c r="G17">
         <v>1.28</v>
@@ -2681,28 +2681,28 @@
         <v>0.167</v>
       </c>
       <c r="M17">
-        <v>0.033254655</v>
+        <v>0.03547163200000001</v>
       </c>
       <c r="N17">
-        <v>0.133745345</v>
+        <v>0.131528368</v>
       </c>
       <c r="O17">
-        <v>0.02006180175</v>
+        <v>0.0197292552</v>
       </c>
       <c r="P17">
-        <v>0.11368354325</v>
+        <v>0.1117991128</v>
       </c>
       <c r="Q17">
-        <v>0.18868354325</v>
+        <v>0.1867991128</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1283211782680691</v>
+        <v>0.1291754347718794</v>
       </c>
       <c r="T17">
-        <v>1.075527588699494</v>
+        <v>1.086661414669468</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.021853331511032</v>
+        <v>4.707987498291592</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1160281652083787</v>
+        <v>0.1162938288888986</v>
       </c>
       <c r="C18">
-        <v>3.430227499948166</v>
+        <v>3.379616796582871</v>
       </c>
       <c r="D18">
-        <v>2.791667499948166</v>
+        <v>2.781146796582871</v>
       </c>
       <c r="E18">
-        <v>0.6124400000000001</v>
+        <v>0.6525300000000001</v>
       </c>
       <c r="F18">
-        <v>0.6414400000000001</v>
+        <v>0.6815300000000001</v>
       </c>
       <c r="G18">
         <v>1.28</v>
@@ -2763,45 +2763,45 @@
         <v>0.167</v>
       </c>
       <c r="M18">
-        <v>0.03547163200000001</v>
+        <v>0.03939243400000001</v>
       </c>
       <c r="N18">
-        <v>0.131528368</v>
+        <v>0.127607566</v>
       </c>
       <c r="O18">
-        <v>0.0197292552</v>
+        <v>0.0191411349</v>
       </c>
       <c r="P18">
-        <v>0.1117991128</v>
+        <v>0.1084664311</v>
       </c>
       <c r="Q18">
-        <v>0.1867991128</v>
+        <v>0.1834664311</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1291754347718794</v>
+        <v>0.1300502757697573</v>
       </c>
       <c r="T18">
-        <v>1.086661414669468</v>
+        <v>1.098063525602574</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.15</v>
       </c>
       <c r="W18">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.707987498291592</v>
+        <v>4.239392772733972</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1162938288888986</v>
+        <v>0.1162194925694185</v>
       </c>
       <c r="C19">
-        <v>3.379616796582871</v>
+        <v>3.342462634505702</v>
       </c>
       <c r="D19">
-        <v>2.781146796582871</v>
+        <v>2.784082634505702</v>
       </c>
       <c r="E19">
-        <v>0.6525300000000001</v>
+        <v>0.6926200000000001</v>
       </c>
       <c r="F19">
-        <v>0.6815300000000001</v>
+        <v>0.7216200000000002</v>
       </c>
       <c r="G19">
         <v>1.28</v>
@@ -2845,28 +2845,28 @@
         <v>0.167</v>
       </c>
       <c r="M19">
-        <v>0.03939243400000001</v>
+        <v>0.04170963600000001</v>
       </c>
       <c r="N19">
-        <v>0.127607566</v>
+        <v>0.125290364</v>
       </c>
       <c r="O19">
-        <v>0.0191411349</v>
+        <v>0.0187935546</v>
       </c>
       <c r="P19">
-        <v>0.1084664311</v>
+        <v>0.1064968094</v>
       </c>
       <c r="Q19">
-        <v>0.1834664311</v>
+        <v>0.1814968094</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1300502757697573</v>
+        <v>0.1309464543529494</v>
       </c>
       <c r="T19">
-        <v>1.098063525602574</v>
+        <v>1.109743736802341</v>
       </c>
       <c r="U19">
         <v>0.0578</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.239392772733972</v>
+        <v>4.003870952026528</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1162194925694185</v>
+        <v>0.1167104062499384</v>
       </c>
       <c r="C20">
-        <v>3.342462634505701</v>
+        <v>3.28309839359726</v>
       </c>
       <c r="D20">
-        <v>2.784082634505701</v>
+        <v>2.76480839359726</v>
       </c>
       <c r="E20">
-        <v>0.69262</v>
+        <v>0.7327100000000001</v>
       </c>
       <c r="F20">
-        <v>0.72162</v>
+        <v>0.7617100000000001</v>
       </c>
       <c r="G20">
         <v>1.28</v>
@@ -2927,45 +2927,45 @@
         <v>0.167</v>
       </c>
       <c r="M20">
-        <v>0.04170963600000001</v>
+        <v>0.04669282300000001</v>
       </c>
       <c r="N20">
-        <v>0.125290364</v>
+        <v>0.120307177</v>
       </c>
       <c r="O20">
-        <v>0.0187935546</v>
+        <v>0.01804607655</v>
       </c>
       <c r="P20">
-        <v>0.1064968094</v>
+        <v>0.10226110045</v>
       </c>
       <c r="Q20">
-        <v>0.1814968094</v>
+        <v>0.17726110045</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1309464543529494</v>
+        <v>0.1318647608023931</v>
       </c>
       <c r="T20">
-        <v>1.109743736802341</v>
+        <v>1.121712348278646</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.003870952026528</v>
+        <v>3.576566788433417</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1167104062499384</v>
+        <v>0.1171418199304583</v>
       </c>
       <c r="C21">
-        <v>3.28309839359726</v>
+        <v>3.226289221501892</v>
       </c>
       <c r="D21">
-        <v>2.76480839359726</v>
+        <v>2.748089221501892</v>
       </c>
       <c r="E21">
-        <v>0.7327100000000001</v>
+        <v>0.7728</v>
       </c>
       <c r="F21">
-        <v>0.7617100000000001</v>
+        <v>0.8018000000000001</v>
       </c>
       <c r="G21">
         <v>1.28</v>
@@ -3009,45 +3009,45 @@
         <v>0.167</v>
       </c>
       <c r="M21">
-        <v>0.04669282300000001</v>
+        <v>0.05139538</v>
       </c>
       <c r="N21">
-        <v>0.120307177</v>
+        <v>0.11560462</v>
       </c>
       <c r="O21">
-        <v>0.01804607655</v>
+        <v>0.017340693</v>
       </c>
       <c r="P21">
-        <v>0.10226110045</v>
+        <v>0.098263927</v>
       </c>
       <c r="Q21">
-        <v>0.17726110045</v>
+        <v>0.173263927</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1318647608023931</v>
+        <v>0.1328060249130729</v>
       </c>
       <c r="T21">
-        <v>1.121712348278646</v>
+        <v>1.133980175041858</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.576566788433417</v>
+        <v>3.249319296792824</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1171418199304583</v>
+        <v>0.1171210336109783</v>
       </c>
       <c r="C22">
-        <v>3.226289221501892</v>
+        <v>3.187000144562393</v>
       </c>
       <c r="D22">
-        <v>2.748089221501892</v>
+        <v>2.748890144562393</v>
       </c>
       <c r="E22">
-        <v>0.7728</v>
+        <v>0.8128900000000001</v>
       </c>
       <c r="F22">
-        <v>0.8018000000000001</v>
+        <v>0.8418900000000001</v>
       </c>
       <c r="G22">
         <v>1.28</v>
@@ -3091,28 +3091,28 @@
         <v>0.167</v>
       </c>
       <c r="M22">
-        <v>0.05139538</v>
+        <v>0.05396514900000001</v>
       </c>
       <c r="N22">
-        <v>0.11560462</v>
+        <v>0.113034851</v>
       </c>
       <c r="O22">
-        <v>0.017340693</v>
+        <v>0.01695522765</v>
       </c>
       <c r="P22">
-        <v>0.098263927</v>
+        <v>0.09607962334999999</v>
       </c>
       <c r="Q22">
-        <v>0.173263927</v>
+        <v>0.17107962335</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1328060249130729</v>
+        <v>0.1337711184949092</v>
       </c>
       <c r="T22">
-        <v>1.133980175041858</v>
+        <v>1.146558579697809</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.249319296792824</v>
+        <v>3.094589806469356</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1171210336109783</v>
+        <v>0.1185588472914982</v>
       </c>
       <c r="C23">
-        <v>3.187000144562393</v>
+        <v>3.092588340366356</v>
       </c>
       <c r="D23">
-        <v>2.748890144562393</v>
+        <v>2.694568340366356</v>
       </c>
       <c r="E23">
-        <v>0.81289</v>
+        <v>0.8529800000000001</v>
       </c>
       <c r="F23">
-        <v>0.84189</v>
+        <v>0.8819800000000001</v>
       </c>
       <c r="G23">
         <v>1.28</v>
@@ -3173,45 +3173,45 @@
         <v>0.167</v>
       </c>
       <c r="M23">
-        <v>0.053965149</v>
+        <v>0.06341436200000002</v>
       </c>
       <c r="N23">
-        <v>0.113034851</v>
+        <v>0.103585638</v>
       </c>
       <c r="O23">
-        <v>0.01695522765</v>
+        <v>0.0155378457</v>
       </c>
       <c r="P23">
-        <v>0.09607962335</v>
+        <v>0.0880477923</v>
       </c>
       <c r="Q23">
-        <v>0.17107962335</v>
+        <v>0.1630477923</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1337711184949092</v>
+        <v>0.1347609580660233</v>
       </c>
       <c r="T23">
-        <v>1.146558579697809</v>
+        <v>1.159459507550068</v>
       </c>
       <c r="U23">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.094589806469357</v>
+        <v>2.633472840111518</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1185588472914982</v>
+        <v>0.118604360972018</v>
       </c>
       <c r="C24">
-        <v>3.092588340366356</v>
+        <v>3.050813829700442</v>
       </c>
       <c r="D24">
-        <v>2.694568340366356</v>
+        <v>2.692883829700442</v>
       </c>
       <c r="E24">
-        <v>0.8529800000000001</v>
+        <v>0.8930700000000001</v>
       </c>
       <c r="F24">
-        <v>0.8819800000000001</v>
+        <v>0.9220700000000002</v>
       </c>
       <c r="G24">
         <v>1.28</v>
@@ -3255,28 +3255,28 @@
         <v>0.167</v>
       </c>
       <c r="M24">
-        <v>0.06341436200000002</v>
+        <v>0.06629683300000001</v>
       </c>
       <c r="N24">
-        <v>0.103585638</v>
+        <v>0.100703167</v>
       </c>
       <c r="O24">
-        <v>0.0155378457</v>
+        <v>0.01510547505</v>
       </c>
       <c r="P24">
-        <v>0.0880477923</v>
+        <v>0.08559769195</v>
       </c>
       <c r="Q24">
-        <v>0.1630477923</v>
+        <v>0.16059769195</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1347609580660233</v>
+        <v>0.1357765077558676</v>
       </c>
       <c r="T24">
-        <v>1.159459507550068</v>
+        <v>1.172695524437449</v>
       </c>
       <c r="U24">
         <v>0.07190000000000001</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.633472840111518</v>
+        <v>2.518974020976235</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.118604360972018</v>
+        <v>0.119445474652538</v>
       </c>
       <c r="C25">
-        <v>3.050813829700442</v>
+        <v>2.979968084830872</v>
       </c>
       <c r="D25">
-        <v>2.692883829700442</v>
+        <v>2.662128084830871</v>
       </c>
       <c r="E25">
-        <v>0.8930700000000001</v>
+        <v>0.9331600000000001</v>
       </c>
       <c r="F25">
-        <v>0.9220700000000002</v>
+        <v>0.9621600000000001</v>
       </c>
       <c r="G25">
         <v>1.28</v>
@@ -3337,45 +3337,45 @@
         <v>0.167</v>
       </c>
       <c r="M25">
-        <v>0.06629683300000001</v>
+        <v>0.07293172800000002</v>
       </c>
       <c r="N25">
-        <v>0.100703167</v>
+        <v>0.09406827199999999</v>
       </c>
       <c r="O25">
-        <v>0.01510547505</v>
+        <v>0.0141102408</v>
       </c>
       <c r="P25">
-        <v>0.08559769195</v>
+        <v>0.0799580312</v>
       </c>
       <c r="Q25">
-        <v>0.16059769195</v>
+        <v>0.1549580312</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1357765077558676</v>
+        <v>0.1368187824375499</v>
       </c>
       <c r="T25">
-        <v>1.172695524437449</v>
+        <v>1.18627985755871</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.518974020976235</v>
+        <v>2.289812741033642</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.119445474652538</v>
+        <v>0.1195241383330579</v>
       </c>
       <c r="C26">
-        <v>2.979968084830872</v>
+        <v>2.937037593264565</v>
       </c>
       <c r="D26">
-        <v>2.662128084830871</v>
+        <v>2.659287593264565</v>
       </c>
       <c r="E26">
-        <v>0.93316</v>
+        <v>0.9732500000000001</v>
       </c>
       <c r="F26">
-        <v>0.96216</v>
+        <v>1.00225</v>
       </c>
       <c r="G26">
         <v>1.28</v>
@@ -3419,28 +3419,28 @@
         <v>0.167</v>
       </c>
       <c r="M26">
-        <v>0.072931728</v>
+        <v>0.07597055000000001</v>
       </c>
       <c r="N26">
-        <v>0.09406827200000001</v>
+        <v>0.09102945</v>
       </c>
       <c r="O26">
-        <v>0.0141102408</v>
+        <v>0.0136544175</v>
       </c>
       <c r="P26">
-        <v>0.0799580312</v>
+        <v>0.0773750325</v>
       </c>
       <c r="Q26">
-        <v>0.1549580312</v>
+        <v>0.1523750325</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1368187824375499</v>
+        <v>0.1378888511107438</v>
       </c>
       <c r="T26">
-        <v>1.18627985755871</v>
+        <v>1.200226439563203</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.289812741033642</v>
+        <v>2.198220231392296</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1195241383330579</v>
+        <v>0.1196028020135778</v>
       </c>
       <c r="C27">
-        <v>2.937037593264565</v>
+        <v>2.894113156848334</v>
       </c>
       <c r="D27">
-        <v>2.659287593264565</v>
+        <v>2.656453156848335</v>
       </c>
       <c r="E27">
-        <v>0.9732500000000001</v>
+        <v>1.01334</v>
       </c>
       <c r="F27">
-        <v>1.00225</v>
+        <v>1.04234</v>
       </c>
       <c r="G27">
         <v>1.28</v>
@@ -3501,28 +3501,28 @@
         <v>0.167</v>
       </c>
       <c r="M27">
-        <v>0.07597055000000001</v>
+        <v>0.07900937200000001</v>
       </c>
       <c r="N27">
-        <v>0.09102945</v>
+        <v>0.087990628</v>
       </c>
       <c r="O27">
-        <v>0.0136544175</v>
+        <v>0.0131985942</v>
       </c>
       <c r="P27">
-        <v>0.0773750325</v>
+        <v>0.0747920338</v>
       </c>
       <c r="Q27">
-        <v>0.1523750325</v>
+        <v>0.1497920338</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1378888511107438</v>
+        <v>0.1389878405588889</v>
       </c>
       <c r="T27">
-        <v>1.200226439563203</v>
+        <v>1.214549956216467</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.198220231392296</v>
+        <v>2.11367329941567</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1196028020135778</v>
+        <v>0.1196814656940977</v>
       </c>
       <c r="C28">
-        <v>2.894113156848334</v>
+        <v>2.851194756240912</v>
       </c>
       <c r="D28">
-        <v>2.656453156848335</v>
+        <v>2.653624756240913</v>
       </c>
       <c r="E28">
-        <v>1.01334</v>
+        <v>1.05343</v>
       </c>
       <c r="F28">
-        <v>1.04234</v>
+        <v>1.08243</v>
       </c>
       <c r="G28">
         <v>1.28</v>
@@ -3583,28 +3583,28 @@
         <v>0.167</v>
       </c>
       <c r="M28">
-        <v>0.07900937200000001</v>
+        <v>0.08204819400000002</v>
       </c>
       <c r="N28">
-        <v>0.087990628</v>
+        <v>0.08495180599999999</v>
       </c>
       <c r="O28">
-        <v>0.0131985942</v>
+        <v>0.0127427709</v>
       </c>
       <c r="P28">
-        <v>0.0747920338</v>
+        <v>0.07220903509999999</v>
       </c>
       <c r="Q28">
-        <v>0.1497920338</v>
+        <v>0.1472090351</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1389878405588889</v>
+        <v>0.1401169393069831</v>
       </c>
       <c r="T28">
-        <v>1.214549956216467</v>
+        <v>1.229265897983519</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.11367329941567</v>
+        <v>2.035389103141014</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1196814656940977</v>
+        <v>0.1231397293746176</v>
       </c>
       <c r="C29">
-        <v>2.851194756240912</v>
+        <v>2.69244731858962</v>
       </c>
       <c r="D29">
-        <v>2.653624756240913</v>
+        <v>2.53496731858962</v>
       </c>
       <c r="E29">
-        <v>1.05343</v>
+        <v>1.09352</v>
       </c>
       <c r="F29">
-        <v>1.08243</v>
+        <v>1.12252</v>
       </c>
       <c r="G29">
         <v>1.28</v>
@@ -3665,45 +3665,45 @@
         <v>0.167</v>
       </c>
       <c r="M29">
-        <v>0.08204819400000002</v>
+        <v>0.1010268</v>
       </c>
       <c r="N29">
-        <v>0.08495180599999999</v>
+        <v>0.0659732</v>
       </c>
       <c r="O29">
-        <v>0.0127427709</v>
+        <v>0.009895979999999999</v>
       </c>
       <c r="P29">
-        <v>0.07220903509999999</v>
+        <v>0.05607722</v>
       </c>
       <c r="Q29">
-        <v>0.1472090351</v>
+        <v>0.13107722</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1401169393069831</v>
+        <v>0.1412774019091911</v>
       </c>
       <c r="T29">
-        <v>1.229265897983519</v>
+        <v>1.244390615910767</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.15</v>
       </c>
       <c r="W29">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.035389103141014</v>
+        <v>1.653026721622381</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1231397293746176</v>
+        <v>0.1233390930551375</v>
       </c>
       <c r="C30">
-        <v>2.69244731858962</v>
+        <v>2.645839568707347</v>
       </c>
       <c r="D30">
-        <v>2.53496731858962</v>
+        <v>2.528449568707347</v>
       </c>
       <c r="E30">
-        <v>1.09352</v>
+        <v>1.13361</v>
       </c>
       <c r="F30">
-        <v>1.12252</v>
+        <v>1.16261</v>
       </c>
       <c r="G30">
         <v>1.28</v>
@@ -3747,28 +3747,28 @@
         <v>0.167</v>
       </c>
       <c r="M30">
-        <v>0.1010268</v>
+        <v>0.1046349</v>
       </c>
       <c r="N30">
-        <v>0.0659732</v>
+        <v>0.06236510000000001</v>
       </c>
       <c r="O30">
-        <v>0.009895979999999999</v>
+        <v>0.009354765000000001</v>
       </c>
       <c r="P30">
-        <v>0.05607722</v>
+        <v>0.05301033500000001</v>
       </c>
       <c r="Q30">
-        <v>0.13107722</v>
+        <v>0.128010335</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1412774019091911</v>
+        <v>0.1424705535987852</v>
       </c>
       <c r="T30">
-        <v>1.244390615910767</v>
+        <v>1.259941382230332</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.653026721622381</v>
+        <v>1.596025800187127</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1233390930551375</v>
+        <v>0.1235384567356574</v>
       </c>
       <c r="C31">
-        <v>2.645839568707347</v>
+        <v>2.599265248935724</v>
       </c>
       <c r="D31">
-        <v>2.528449568707347</v>
+        <v>2.521965248935724</v>
       </c>
       <c r="E31">
-        <v>1.13361</v>
+        <v>1.1737</v>
       </c>
       <c r="F31">
-        <v>1.16261</v>
+        <v>1.2027</v>
       </c>
       <c r="G31">
         <v>1.28</v>
@@ -3829,28 +3829,28 @@
         <v>0.167</v>
       </c>
       <c r="M31">
-        <v>0.1046349</v>
+        <v>0.108243</v>
       </c>
       <c r="N31">
-        <v>0.06236510000000002</v>
+        <v>0.058757</v>
       </c>
       <c r="O31">
-        <v>0.009354765000000003</v>
+        <v>0.00881355</v>
       </c>
       <c r="P31">
-        <v>0.05301033500000002</v>
+        <v>0.04994345</v>
       </c>
       <c r="Q31">
-        <v>0.128010335</v>
+        <v>0.12494345</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1424705535987852</v>
+        <v>0.1436977953366535</v>
       </c>
       <c r="T31">
-        <v>1.259941382230332</v>
+        <v>1.275936456159027</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.596025800187127</v>
+        <v>1.542824940180889</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1235384567356574</v>
+        <v>0.1395647947194084</v>
       </c>
       <c r="C32">
-        <v>2.599265248935724</v>
+        <v>2.128119354410821</v>
       </c>
       <c r="D32">
-        <v>2.521965248935724</v>
+        <v>2.090909354410821</v>
       </c>
       <c r="E32">
-        <v>1.1737</v>
+        <v>1.21379</v>
       </c>
       <c r="F32">
-        <v>1.2027</v>
+        <v>1.24279</v>
       </c>
       <c r="G32">
         <v>1.28</v>
@@ -3911,45 +3911,45 @@
         <v>0.167</v>
       </c>
       <c r="M32">
-        <v>0.108243</v>
+        <v>0.182441572</v>
       </c>
       <c r="N32">
-        <v>0.058757</v>
+        <v>-0.01544157200000001</v>
       </c>
       <c r="O32">
-        <v>0.00881355</v>
+        <v>-0.002316235800000002</v>
       </c>
       <c r="P32">
-        <v>0.04994345</v>
+        <v>-0.01312533620000001</v>
       </c>
       <c r="Q32">
-        <v>0.12494345</v>
+        <v>0.06187466379999997</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1436977953366535</v>
+        <v>0.1453699068509289</v>
       </c>
       <c r="T32">
-        <v>1.275936456159027</v>
+        <v>1.29772967461191</v>
       </c>
       <c r="U32">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.15</v>
+        <v>0.1373042323928232</v>
       </c>
       <c r="W32">
-        <v>0.0765</v>
+        <v>0.1266437386847336</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.542824940180889</v>
+        <v>0.9153615492854884</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1395647947194084</v>
+        <v>0.1405747947194083</v>
       </c>
       <c r="C33">
-        <v>2.128119354410821</v>
+        <v>2.0657468640693</v>
       </c>
       <c r="D33">
-        <v>2.090909354410821</v>
+        <v>2.0686268640693</v>
       </c>
       <c r="E33">
-        <v>1.21379</v>
+        <v>1.25388</v>
       </c>
       <c r="F33">
-        <v>1.24279</v>
+        <v>1.28288</v>
       </c>
       <c r="G33">
         <v>1.28</v>
@@ -3993,37 +3993,37 @@
         <v>0.167</v>
       </c>
       <c r="M33">
-        <v>0.182441572</v>
+        <v>0.1883267840000001</v>
       </c>
       <c r="N33">
-        <v>-0.01544157200000001</v>
+        <v>-0.02132678400000004</v>
       </c>
       <c r="O33">
-        <v>-0.002316235800000002</v>
+        <v>-0.003199017600000006</v>
       </c>
       <c r="P33">
-        <v>-0.01312533620000001</v>
+        <v>-0.01812776640000004</v>
       </c>
       <c r="Q33">
-        <v>0.06187466379999997</v>
+        <v>0.05687223359999995</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1453699068509289</v>
+        <v>0.146834170186972</v>
       </c>
       <c r="T33">
-        <v>1.29772967461191</v>
+        <v>1.316813934532673</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.1373042323928232</v>
+        <v>0.1330134751305475</v>
       </c>
       <c r="W33">
-        <v>0.1266437386847336</v>
+        <v>0.1272736218508356</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9153615492854884</v>
+        <v>0.8867565008703168</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1405747947194083</v>
+        <v>0.1415847947194084</v>
       </c>
       <c r="C34">
-        <v>2.0657468640693</v>
+        <v>2.003844287878783</v>
       </c>
       <c r="D34">
-        <v>2.0686268640693</v>
+        <v>2.046814287878784</v>
       </c>
       <c r="E34">
-        <v>1.25388</v>
+        <v>1.29397</v>
       </c>
       <c r="F34">
-        <v>1.28288</v>
+        <v>1.32297</v>
       </c>
       <c r="G34">
         <v>1.28</v>
@@ -4075,37 +4075,37 @@
         <v>0.167</v>
       </c>
       <c r="M34">
-        <v>0.1883267840000001</v>
+        <v>0.1942119960000001</v>
       </c>
       <c r="N34">
-        <v>-0.02132678400000004</v>
+        <v>-0.02721199600000004</v>
       </c>
       <c r="O34">
-        <v>-0.003199017600000006</v>
+        <v>-0.004081799400000007</v>
       </c>
       <c r="P34">
-        <v>-0.01812776640000004</v>
+        <v>-0.02313019660000004</v>
       </c>
       <c r="Q34">
-        <v>0.05687223359999995</v>
+        <v>0.05186980339999994</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.146834170186972</v>
+        <v>0.1483421428763298</v>
       </c>
       <c r="T34">
-        <v>1.316813934532673</v>
+        <v>1.336467873854057</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.1330134751305475</v>
+        <v>0.1289827637629552</v>
       </c>
       <c r="W34">
-        <v>0.1272736218508356</v>
+        <v>0.1278653302795982</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8867565008703168</v>
+        <v>0.8598850917530345</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1415847947194084</v>
+        <v>0.1425947947194083</v>
       </c>
       <c r="C35">
-        <v>2.003844287878783</v>
+        <v>1.942396915958628</v>
       </c>
       <c r="D35">
-        <v>2.046814287878784</v>
+        <v>2.025456915958628</v>
       </c>
       <c r="E35">
-        <v>1.29397</v>
+        <v>1.33406</v>
       </c>
       <c r="F35">
-        <v>1.32297</v>
+        <v>1.36306</v>
       </c>
       <c r="G35">
         <v>1.28</v>
@@ -4157,37 +4157,37 @@
         <v>0.167</v>
       </c>
       <c r="M35">
-        <v>0.1942119960000001</v>
+        <v>0.2000972080000001</v>
       </c>
       <c r="N35">
-        <v>-0.02721199600000004</v>
+        <v>-0.03309720800000004</v>
       </c>
       <c r="O35">
-        <v>-0.004081799400000007</v>
+        <v>-0.004964581200000006</v>
       </c>
       <c r="P35">
-        <v>-0.02313019660000004</v>
+        <v>-0.02813262680000004</v>
       </c>
       <c r="Q35">
-        <v>0.05186980339999994</v>
+        <v>0.04686737319999994</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1483421428763298</v>
+        <v>0.1498958117077893</v>
       </c>
       <c r="T35">
-        <v>1.336467873854057</v>
+        <v>1.35671738709427</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.1289827637629552</v>
+        <v>0.1251891530640447</v>
       </c>
       <c r="W35">
-        <v>0.1278653302795982</v>
+        <v>0.1284222323301982</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8598850917530345</v>
+        <v>0.8345943537602982</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1425947947194083</v>
+        <v>0.1436047947194083</v>
       </c>
       <c r="C36">
-        <v>1.942396915958628</v>
+        <v>1.881390646045816</v>
       </c>
       <c r="D36">
-        <v>2.025456915958628</v>
+        <v>2.004540646045817</v>
       </c>
       <c r="E36">
-        <v>1.33406</v>
+        <v>1.37415</v>
       </c>
       <c r="F36">
-        <v>1.36306</v>
+        <v>1.40315</v>
       </c>
       <c r="G36">
         <v>1.28</v>
@@ -4239,37 +4239,37 @@
         <v>0.167</v>
       </c>
       <c r="M36">
-        <v>0.2000972080000001</v>
+        <v>0.2059824200000001</v>
       </c>
       <c r="N36">
-        <v>-0.03309720800000004</v>
+        <v>-0.03898242000000007</v>
       </c>
       <c r="O36">
-        <v>-0.004964581200000006</v>
+        <v>-0.005847363000000011</v>
       </c>
       <c r="P36">
-        <v>-0.02813262680000004</v>
+        <v>-0.03313505700000006</v>
       </c>
       <c r="Q36">
-        <v>0.04686737319999994</v>
+        <v>0.04186494299999992</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1498958117077893</v>
+        <v>0.151497285734063</v>
       </c>
       <c r="T36">
-        <v>1.35671738709427</v>
+        <v>1.377589962280336</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.1251891530640447</v>
+        <v>0.1216123201193577</v>
       </c>
       <c r="W36">
-        <v>0.1284222323301982</v>
+        <v>0.1289473114064783</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8345943537602982</v>
+        <v>0.8107488007957181</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1436047947194083</v>
+        <v>0.1648761730661097</v>
       </c>
       <c r="C37">
-        <v>1.881390646045816</v>
+        <v>1.483216057034807</v>
       </c>
       <c r="D37">
-        <v>2.004540646045817</v>
+        <v>1.646456057034807</v>
       </c>
       <c r="E37">
-        <v>1.37415</v>
+        <v>1.41424</v>
       </c>
       <c r="F37">
-        <v>1.40315</v>
+        <v>1.44324</v>
       </c>
       <c r="G37">
         <v>1.28</v>
@@ -4321,45 +4321,45 @@
         <v>0.167</v>
       </c>
       <c r="M37">
-        <v>0.2059824200000001</v>
+        <v>0.2898025920000001</v>
       </c>
       <c r="N37">
-        <v>-0.03898242000000007</v>
+        <v>-0.1228025920000001</v>
       </c>
       <c r="O37">
-        <v>-0.005847363000000011</v>
+        <v>-0.01842038880000001</v>
       </c>
       <c r="P37">
-        <v>-0.03313505700000006</v>
+        <v>-0.1043822032000001</v>
       </c>
       <c r="Q37">
-        <v>0.04186494299999992</v>
+        <v>-0.02938220320000008</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.151497285734063</v>
+        <v>0.1544322094903786</v>
       </c>
       <c r="T37">
-        <v>1.377589962280336</v>
+        <v>1.415841857574327</v>
       </c>
       <c r="U37">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1216123201193577</v>
+        <v>0.08643815028403885</v>
       </c>
       <c r="W37">
-        <v>0.1289473114064783</v>
+        <v>0.183443219422965</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8107488007957181</v>
+        <v>0.5762543352269256</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1648761730661097</v>
+        <v>0.1664261730661097</v>
       </c>
       <c r="C38">
-        <v>1.483216057034807</v>
+        <v>1.421969728988113</v>
       </c>
       <c r="D38">
-        <v>1.646456057034807</v>
+        <v>1.625299728988113</v>
       </c>
       <c r="E38">
-        <v>1.41424</v>
+        <v>1.45433</v>
       </c>
       <c r="F38">
-        <v>1.44324</v>
+        <v>1.48333</v>
       </c>
       <c r="G38">
         <v>1.28</v>
@@ -4403,37 +4403,37 @@
         <v>0.167</v>
       </c>
       <c r="M38">
-        <v>0.289802592</v>
+        <v>0.297852664</v>
       </c>
       <c r="N38">
-        <v>-0.122802592</v>
+        <v>-0.130852664</v>
       </c>
       <c r="O38">
-        <v>-0.0184203888</v>
+        <v>-0.01962789959999999</v>
       </c>
       <c r="P38">
-        <v>-0.1043822032</v>
+        <v>-0.1112247644</v>
       </c>
       <c r="Q38">
-        <v>-0.02938220320000003</v>
+        <v>-0.0362247644</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1544322094903786</v>
+        <v>0.1561565302759402</v>
       </c>
       <c r="T38">
-        <v>1.415841857574327</v>
+        <v>1.438315537853285</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.08643815028403887</v>
+        <v>0.08410198406014593</v>
       </c>
       <c r="W38">
-        <v>0.183443219422965</v>
+        <v>0.1839123216007227</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5762543352269258</v>
+        <v>0.5606798937343063</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1664261730661097</v>
+        <v>0.1679761730661097</v>
       </c>
       <c r="C39">
-        <v>1.421969728988113</v>
+        <v>1.361260204602057</v>
       </c>
       <c r="D39">
-        <v>1.625299728988113</v>
+        <v>1.604680204602057</v>
       </c>
       <c r="E39">
-        <v>1.45433</v>
+        <v>1.49442</v>
       </c>
       <c r="F39">
-        <v>1.48333</v>
+        <v>1.52342</v>
       </c>
       <c r="G39">
         <v>1.28</v>
@@ -4485,37 +4485,37 @@
         <v>0.167</v>
       </c>
       <c r="M39">
-        <v>0.297852664</v>
+        <v>0.3059027360000001</v>
       </c>
       <c r="N39">
-        <v>-0.130852664</v>
+        <v>-0.1389027360000001</v>
       </c>
       <c r="O39">
-        <v>-0.01962789959999999</v>
+        <v>-0.02083541040000001</v>
       </c>
       <c r="P39">
-        <v>-0.1112247644</v>
+        <v>-0.1180673256000001</v>
       </c>
       <c r="Q39">
-        <v>-0.0362247644</v>
+        <v>-0.04306732560000007</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1561565302759402</v>
+        <v>0.1579364743126489</v>
       </c>
       <c r="T39">
-        <v>1.438315537853285</v>
+        <v>1.461514175560596</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.08410198406014593</v>
+        <v>0.08188877395329995</v>
       </c>
       <c r="W39">
-        <v>0.1839123216007227</v>
+        <v>0.1843567341901774</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5606798937343063</v>
+        <v>0.5459251596886665</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1679761730661097</v>
+        <v>0.1695261730661097</v>
       </c>
       <c r="C40">
-        <v>1.361260204602057</v>
+        <v>1.30106730918797</v>
       </c>
       <c r="D40">
-        <v>1.604680204602057</v>
+        <v>1.58457730918797</v>
       </c>
       <c r="E40">
-        <v>1.49442</v>
+        <v>1.53451</v>
       </c>
       <c r="F40">
-        <v>1.52342</v>
+        <v>1.56351</v>
       </c>
       <c r="G40">
         <v>1.28</v>
@@ -4567,37 +4567,37 @@
         <v>0.167</v>
       </c>
       <c r="M40">
-        <v>0.3059027360000001</v>
+        <v>0.313952808</v>
       </c>
       <c r="N40">
-        <v>-0.1389027360000001</v>
+        <v>-0.146952808</v>
       </c>
       <c r="O40">
-        <v>-0.02083541040000001</v>
+        <v>-0.0220429212</v>
       </c>
       <c r="P40">
-        <v>-0.1180673256000001</v>
+        <v>-0.1249098868</v>
       </c>
       <c r="Q40">
-        <v>-0.04306732560000007</v>
+        <v>-0.04990988680000003</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1579364743126489</v>
+        <v>0.1597747771702333</v>
       </c>
       <c r="T40">
-        <v>1.461514175560596</v>
+        <v>1.485473424340278</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.08188877395329995</v>
+        <v>0.07978906180065126</v>
       </c>
       <c r="W40">
-        <v>0.1843567341901774</v>
+        <v>0.1847783563904292</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5459251596886665</v>
+        <v>0.5319270786710084</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1695261730661097</v>
+        <v>0.1710761730661097</v>
       </c>
       <c r="C41">
-        <v>1.30106730918797</v>
+        <v>1.241371866515761</v>
       </c>
       <c r="D41">
-        <v>1.58457730918797</v>
+        <v>1.564971866515761</v>
       </c>
       <c r="E41">
-        <v>1.53451</v>
+        <v>1.5746</v>
       </c>
       <c r="F41">
-        <v>1.56351</v>
+        <v>1.6036</v>
       </c>
       <c r="G41">
         <v>1.28</v>
@@ -4649,37 +4649,37 @@
         <v>0.167</v>
       </c>
       <c r="M41">
-        <v>0.313952808</v>
+        <v>0.32200288</v>
       </c>
       <c r="N41">
-        <v>-0.146952808</v>
+        <v>-0.15500288</v>
       </c>
       <c r="O41">
-        <v>-0.0220429212</v>
+        <v>-0.023250432</v>
       </c>
       <c r="P41">
-        <v>-0.1249098868</v>
+        <v>-0.131752448</v>
       </c>
       <c r="Q41">
-        <v>-0.04990988680000003</v>
+        <v>-0.05675244800000004</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1597747771702333</v>
+        <v>0.1616743567897372</v>
       </c>
       <c r="T41">
-        <v>1.485473424340278</v>
+        <v>1.510231314745949</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.07978906180065126</v>
+        <v>0.07779433525563496</v>
       </c>
       <c r="W41">
-        <v>0.1847783563904292</v>
+        <v>0.1851788974806685</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5319270786710084</v>
+        <v>0.5186289017042331</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1710761730661097</v>
+        <v>0.1726261730661097</v>
       </c>
       <c r="C42">
-        <v>1.241371866515761</v>
+        <v>1.182155637800849</v>
       </c>
       <c r="D42">
-        <v>1.564971866515761</v>
+        <v>1.54584563780085</v>
       </c>
       <c r="E42">
-        <v>1.5746</v>
+        <v>1.61469</v>
       </c>
       <c r="F42">
-        <v>1.6036</v>
+        <v>1.64369</v>
       </c>
       <c r="G42">
         <v>1.28</v>
@@ -4731,37 +4731,37 @@
         <v>0.167</v>
       </c>
       <c r="M42">
-        <v>0.32200288</v>
+        <v>0.3300529520000001</v>
       </c>
       <c r="N42">
-        <v>-0.15500288</v>
+        <v>-0.1630529520000001</v>
       </c>
       <c r="O42">
-        <v>-0.023250432</v>
+        <v>-0.02445794280000001</v>
       </c>
       <c r="P42">
-        <v>-0.131752448</v>
+        <v>-0.1385950092000001</v>
       </c>
       <c r="Q42">
-        <v>-0.05675244800000004</v>
+        <v>-0.06359500920000008</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1616743567897372</v>
+        <v>0.1636383289387158</v>
       </c>
       <c r="T42">
-        <v>1.510231314745949</v>
+        <v>1.535828455673846</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.07779433525563496</v>
+        <v>0.07589691244452192</v>
       </c>
       <c r="W42">
-        <v>0.1851788974806685</v>
+        <v>0.18555989998114</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5186289017042331</v>
+        <v>0.5059794162968128</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1726261730661097</v>
+        <v>0.1892076091501539</v>
       </c>
       <c r="C43">
-        <v>1.182155637800849</v>
+        <v>0.9633279767318668</v>
       </c>
       <c r="D43">
-        <v>1.54584563780085</v>
+        <v>1.367107976731867</v>
       </c>
       <c r="E43">
-        <v>1.61469</v>
+        <v>1.65478</v>
       </c>
       <c r="F43">
-        <v>1.64369</v>
+        <v>1.68378</v>
       </c>
       <c r="G43">
         <v>1.28</v>
@@ -4813,45 +4813,45 @@
         <v>0.167</v>
       </c>
       <c r="M43">
-        <v>0.3300529520000001</v>
+        <v>0.3970353240000001</v>
       </c>
       <c r="N43">
-        <v>-0.1630529520000001</v>
+        <v>-0.2300353240000001</v>
       </c>
       <c r="O43">
-        <v>-0.02445794280000001</v>
+        <v>-0.03450529860000001</v>
       </c>
       <c r="P43">
-        <v>-0.1385950092000001</v>
+        <v>-0.1955300254000001</v>
       </c>
       <c r="Q43">
-        <v>-0.06359500920000008</v>
+        <v>-0.1205300254000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1636383289387158</v>
+        <v>0.1662414657894596</v>
       </c>
       <c r="T43">
-        <v>1.535828455673846</v>
+        <v>1.569756055338508</v>
       </c>
       <c r="U43">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07589691244452192</v>
+        <v>0.06309262296268631</v>
       </c>
       <c r="W43">
-        <v>0.18555989998114</v>
+        <v>0.2209227595053986</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.5059794162968128</v>
+        <v>0.4206174864179086</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1892076091501539</v>
+        <v>0.1911076091501539</v>
       </c>
       <c r="C44">
-        <v>0.963327976731867</v>
+        <v>0.9053620707763403</v>
       </c>
       <c r="D44">
-        <v>1.367107976731867</v>
+        <v>1.349232070776341</v>
       </c>
       <c r="E44">
-        <v>1.65478</v>
+        <v>1.69487</v>
       </c>
       <c r="F44">
-        <v>1.68378</v>
+        <v>1.72387</v>
       </c>
       <c r="G44">
         <v>1.28</v>
@@ -4895,37 +4895,37 @@
         <v>0.167</v>
       </c>
       <c r="M44">
-        <v>0.397035324</v>
+        <v>0.406488546</v>
       </c>
       <c r="N44">
-        <v>-0.230035324</v>
+        <v>-0.239488546</v>
       </c>
       <c r="O44">
-        <v>-0.0345052986</v>
+        <v>-0.0359232819</v>
       </c>
       <c r="P44">
-        <v>-0.1955300254</v>
+        <v>-0.2035652641</v>
       </c>
       <c r="Q44">
-        <v>-0.1205300254</v>
+        <v>-0.1285652641</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1662414657894595</v>
+        <v>0.1683544739612044</v>
       </c>
       <c r="T44">
-        <v>1.569756055338508</v>
+        <v>1.597295635256727</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06309262296268631</v>
+        <v>0.06162535266122849</v>
       </c>
       <c r="W44">
-        <v>0.2209227595053986</v>
+        <v>0.2212687418424823</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4206174864179087</v>
+        <v>0.41083568440819</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1911076091501539</v>
+        <v>0.1930076091501539</v>
       </c>
       <c r="C45">
-        <v>0.9053620707763403</v>
+        <v>0.8478576113657528</v>
       </c>
       <c r="D45">
-        <v>1.349232070776341</v>
+        <v>1.331817611365753</v>
       </c>
       <c r="E45">
-        <v>1.69487</v>
+        <v>1.73496</v>
       </c>
       <c r="F45">
-        <v>1.72387</v>
+        <v>1.76396</v>
       </c>
       <c r="G45">
         <v>1.28</v>
@@ -4977,37 +4977,37 @@
         <v>0.167</v>
       </c>
       <c r="M45">
-        <v>0.406488546</v>
+        <v>0.415941768</v>
       </c>
       <c r="N45">
-        <v>-0.239488546</v>
+        <v>-0.248941768</v>
       </c>
       <c r="O45">
-        <v>-0.0359232819</v>
+        <v>-0.0373412652</v>
       </c>
       <c r="P45">
-        <v>-0.2035652641</v>
+        <v>-0.2116005028</v>
       </c>
       <c r="Q45">
-        <v>-0.1285652641</v>
+        <v>-0.1366005028000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1683544739612044</v>
+        <v>0.1705429467105116</v>
       </c>
       <c r="T45">
-        <v>1.597295635256727</v>
+        <v>1.625818771600597</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06162535266122849</v>
+        <v>0.06022477646438239</v>
       </c>
       <c r="W45">
-        <v>0.2212687418424823</v>
+        <v>0.2215989977096986</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.41083568440819</v>
+        <v>0.4014985097625492</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1930076091501539</v>
+        <v>0.194907609150154</v>
       </c>
       <c r="C46">
-        <v>0.8478576113657528</v>
+        <v>0.7907969585867467</v>
       </c>
       <c r="D46">
-        <v>1.331817611365753</v>
+        <v>1.314846958586747</v>
       </c>
       <c r="E46">
-        <v>1.73496</v>
+        <v>1.77505</v>
       </c>
       <c r="F46">
-        <v>1.76396</v>
+        <v>1.80405</v>
       </c>
       <c r="G46">
         <v>1.28</v>
@@ -5059,37 +5059,37 @@
         <v>0.167</v>
       </c>
       <c r="M46">
-        <v>0.415941768</v>
+        <v>0.42539499</v>
       </c>
       <c r="N46">
-        <v>-0.248941768</v>
+        <v>-0.25839499</v>
       </c>
       <c r="O46">
-        <v>-0.0373412652</v>
+        <v>-0.0387592485</v>
       </c>
       <c r="P46">
-        <v>-0.2116005028</v>
+        <v>-0.2196357415</v>
       </c>
       <c r="Q46">
-        <v>-0.1366005028000001</v>
+        <v>-0.1446357415</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1705429467105116</v>
+        <v>0.1728110002870664</v>
       </c>
       <c r="T46">
-        <v>1.625818771600597</v>
+        <v>1.655379112902426</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06022477646438239</v>
+        <v>0.05888644809850722</v>
       </c>
       <c r="W46">
-        <v>0.2215989977096986</v>
+        <v>0.221914575538372</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4014985097625492</v>
+        <v>0.3925763206567149</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.194907609150154</v>
+        <v>0.1968076091501539</v>
       </c>
       <c r="C47">
-        <v>0.7907969585867467</v>
+        <v>0.7341633603179289</v>
       </c>
       <c r="D47">
-        <v>1.314846958586747</v>
+        <v>1.298303360317929</v>
       </c>
       <c r="E47">
-        <v>1.77505</v>
+        <v>1.81514</v>
       </c>
       <c r="F47">
-        <v>1.80405</v>
+        <v>1.84414</v>
       </c>
       <c r="G47">
         <v>1.28</v>
@@ -5141,37 +5141,37 @@
         <v>0.167</v>
       </c>
       <c r="M47">
-        <v>0.42539499</v>
+        <v>0.4348482120000001</v>
       </c>
       <c r="N47">
-        <v>-0.25839499</v>
+        <v>-0.2678482120000001</v>
       </c>
       <c r="O47">
-        <v>-0.0387592485</v>
+        <v>-0.04017723180000001</v>
       </c>
       <c r="P47">
-        <v>-0.2196357415</v>
+        <v>-0.2276709802000001</v>
       </c>
       <c r="Q47">
-        <v>-0.1446357415</v>
+        <v>-0.1526709802000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1728110002870664</v>
+        <v>0.175163055847938</v>
       </c>
       <c r="T47">
-        <v>1.655379112902426</v>
+        <v>1.686034281659879</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05888644809850722</v>
+        <v>0.05760630792245271</v>
       </c>
       <c r="W47">
-        <v>0.221914575538372</v>
+        <v>0.2222164325918857</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3925763206567149</v>
+        <v>0.3840420528163514</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1968076091501539</v>
+        <v>0.198707609150154</v>
       </c>
       <c r="C48">
-        <v>0.7341633603179289</v>
+        <v>0.6779408970722198</v>
       </c>
       <c r="D48">
-        <v>1.298303360317929</v>
+        <v>1.28217089707222</v>
       </c>
       <c r="E48">
-        <v>1.81514</v>
+        <v>1.85523</v>
       </c>
       <c r="F48">
-        <v>1.84414</v>
+        <v>1.88423</v>
       </c>
       <c r="G48">
         <v>1.28</v>
@@ -5223,37 +5223,37 @@
         <v>0.167</v>
       </c>
       <c r="M48">
-        <v>0.4348482120000001</v>
+        <v>0.4443014340000001</v>
       </c>
       <c r="N48">
-        <v>-0.2678482120000001</v>
+        <v>-0.2773014340000001</v>
       </c>
       <c r="O48">
-        <v>-0.04017723180000001</v>
+        <v>-0.04159521510000001</v>
       </c>
       <c r="P48">
-        <v>-0.2276709802000001</v>
+        <v>-0.2357062189000001</v>
       </c>
       <c r="Q48">
-        <v>-0.1526709802000001</v>
+        <v>-0.1607062189000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.175163055847938</v>
+        <v>0.1776038682224274</v>
       </c>
       <c r="T48">
-        <v>1.686034281659879</v>
+        <v>1.717846249238367</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05760630792245271</v>
+        <v>0.05638064179644307</v>
       </c>
       <c r="W48">
-        <v>0.2222164325918857</v>
+        <v>0.2225054446643987</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3840420528163514</v>
+        <v>0.3758709453096206</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.198707609150154</v>
+        <v>0.2006076091501539</v>
       </c>
       <c r="C49">
-        <v>0.6779408970722198</v>
+        <v>0.6221144309010107</v>
       </c>
       <c r="D49">
-        <v>1.28217089707222</v>
+        <v>1.266434430901011</v>
       </c>
       <c r="E49">
-        <v>1.85523</v>
+        <v>1.89532</v>
       </c>
       <c r="F49">
-        <v>1.88423</v>
+        <v>1.92432</v>
       </c>
       <c r="G49">
         <v>1.28</v>
@@ -5305,37 +5305,37 @@
         <v>0.167</v>
       </c>
       <c r="M49">
-        <v>0.4443014340000001</v>
+        <v>0.4537546560000001</v>
       </c>
       <c r="N49">
-        <v>-0.2773014340000001</v>
+        <v>-0.2867546560000001</v>
       </c>
       <c r="O49">
-        <v>-0.04159521510000001</v>
+        <v>-0.04301319840000001</v>
       </c>
       <c r="P49">
-        <v>-0.2357062189000001</v>
+        <v>-0.2437414576</v>
       </c>
       <c r="Q49">
-        <v>-0.1607062189000001</v>
+        <v>-0.1687414576000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1776038682224274</v>
+        <v>0.1801385579959356</v>
       </c>
       <c r="T49">
-        <v>1.717846249238367</v>
+        <v>1.750881754031412</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05638064179644307</v>
+        <v>0.05520604509235052</v>
       </c>
       <c r="W49">
-        <v>0.2225054446643987</v>
+        <v>0.2227824145672238</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3758709453096206</v>
+        <v>0.3680403006156702</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2006076091501539</v>
+        <v>0.2025076091501539</v>
       </c>
       <c r="C50">
-        <v>0.6221144309010109</v>
+        <v>0.5666695580153787</v>
       </c>
       <c r="D50">
-        <v>1.266434430901011</v>
+        <v>1.251079558015379</v>
       </c>
       <c r="E50">
-        <v>1.89532</v>
+        <v>1.93541</v>
       </c>
       <c r="F50">
-        <v>1.92432</v>
+        <v>1.96441</v>
       </c>
       <c r="G50">
         <v>1.28</v>
@@ -5387,37 +5387,37 @@
         <v>0.167</v>
       </c>
       <c r="M50">
-        <v>0.453754656</v>
+        <v>0.4632078780000001</v>
       </c>
       <c r="N50">
-        <v>-0.2867546560000001</v>
+        <v>-0.296207878</v>
       </c>
       <c r="O50">
-        <v>-0.04301319840000001</v>
+        <v>-0.0444311817</v>
       </c>
       <c r="P50">
-        <v>-0.2437414576</v>
+        <v>-0.2517766963</v>
       </c>
       <c r="Q50">
-        <v>-0.1687414576000001</v>
+        <v>-0.1767766963000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1801385579959356</v>
+        <v>0.1827726473684049</v>
       </c>
       <c r="T50">
-        <v>1.750881754031412</v>
+        <v>1.785212768816342</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05520604509235053</v>
+        <v>0.05407939111087397</v>
       </c>
       <c r="W50">
-        <v>0.2227824145672238</v>
+        <v>0.2230480795760559</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3680403006156701</v>
+        <v>0.3605292740724932</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2025076091501539</v>
+        <v>0.2044076091501539</v>
       </c>
       <c r="C51">
-        <v>0.5666695580153787</v>
+        <v>0.5115925648126827</v>
       </c>
       <c r="D51">
-        <v>1.251079558015379</v>
+        <v>1.236092564812683</v>
       </c>
       <c r="E51">
-        <v>1.93541</v>
+        <v>1.9755</v>
       </c>
       <c r="F51">
-        <v>1.96441</v>
+        <v>2.0045</v>
       </c>
       <c r="G51">
         <v>1.28</v>
@@ -5469,37 +5469,37 @@
         <v>0.167</v>
       </c>
       <c r="M51">
-        <v>0.4632078780000001</v>
+        <v>0.4726611000000001</v>
       </c>
       <c r="N51">
-        <v>-0.296207878</v>
+        <v>-0.3056611</v>
       </c>
       <c r="O51">
-        <v>-0.0444311817</v>
+        <v>-0.045849165</v>
       </c>
       <c r="P51">
-        <v>-0.2517766963</v>
+        <v>-0.259811935</v>
       </c>
       <c r="Q51">
-        <v>-0.1767766963000001</v>
+        <v>-0.184811935</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1827726473684049</v>
+        <v>0.1855121003157731</v>
       </c>
       <c r="T51">
-        <v>1.785212768816342</v>
+        <v>1.820917024192669</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05407939111087397</v>
+        <v>0.0529978032886565</v>
       </c>
       <c r="W51">
-        <v>0.2230480795760559</v>
+        <v>0.2233031179845348</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3605292740724932</v>
+        <v>0.3533186885910434</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2044076091501539</v>
+        <v>0.2063076091501539</v>
       </c>
       <c r="C52">
-        <v>0.5115925648126827</v>
+        <v>0.4568703870263509</v>
       </c>
       <c r="D52">
-        <v>1.236092564812683</v>
+        <v>1.221460387026351</v>
       </c>
       <c r="E52">
-        <v>1.9755</v>
+        <v>2.01559</v>
       </c>
       <c r="F52">
-        <v>2.0045</v>
+        <v>2.04459</v>
       </c>
       <c r="G52">
         <v>1.28</v>
@@ -5551,37 +5551,37 @@
         <v>0.167</v>
       </c>
       <c r="M52">
-        <v>0.4726611000000001</v>
+        <v>0.4821143220000001</v>
       </c>
       <c r="N52">
-        <v>-0.3056611</v>
+        <v>-0.3151143220000001</v>
       </c>
       <c r="O52">
-        <v>-0.045849165</v>
+        <v>-0.04726714830000001</v>
       </c>
       <c r="P52">
-        <v>-0.259811935</v>
+        <v>-0.2678471737000001</v>
       </c>
       <c r="Q52">
-        <v>-0.184811935</v>
+        <v>-0.1928471737000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1855121003157731</v>
+        <v>0.1883633676691562</v>
       </c>
       <c r="T52">
-        <v>1.820917024192669</v>
+        <v>1.858078596114968</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0529978032886565</v>
+        <v>0.05195863067515342</v>
       </c>
       <c r="W52">
-        <v>0.2233031179845348</v>
+        <v>0.2235481548867988</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3533186885910434</v>
+        <v>0.3463908711676894</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2063076091501539</v>
+        <v>0.2082076091501539</v>
       </c>
       <c r="C53">
-        <v>0.4568703870263509</v>
+        <v>0.4024905717431007</v>
       </c>
       <c r="D53">
-        <v>1.221460387026351</v>
+        <v>1.2071705717431</v>
       </c>
       <c r="E53">
-        <v>2.01559</v>
+        <v>2.05568</v>
       </c>
       <c r="F53">
-        <v>2.04459</v>
+        <v>2.08468</v>
       </c>
       <c r="G53">
         <v>1.28</v>
@@ -5633,37 +5633,37 @@
         <v>0.167</v>
       </c>
       <c r="M53">
-        <v>0.4821143220000001</v>
+        <v>0.491567544</v>
       </c>
       <c r="N53">
-        <v>-0.3151143220000001</v>
+        <v>-0.324567544</v>
       </c>
       <c r="O53">
-        <v>-0.04726714830000001</v>
+        <v>-0.04868513159999999</v>
       </c>
       <c r="P53">
-        <v>-0.2678471737000001</v>
+        <v>-0.2758824124</v>
       </c>
       <c r="Q53">
-        <v>-0.1928471737000001</v>
+        <v>-0.2008824124</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1883633676691562</v>
+        <v>0.1913334378289303</v>
       </c>
       <c r="T53">
-        <v>1.858078596114968</v>
+        <v>1.896788566867363</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05195863067515342</v>
+        <v>0.05095942623909279</v>
       </c>
       <c r="W53">
-        <v>0.2235481548867988</v>
+        <v>0.2237837672928219</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3463908711676894</v>
+        <v>0.3397295082606187</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2082076091501539</v>
+        <v>0.2101076091501539</v>
       </c>
       <c r="C54">
-        <v>0.4024905717431007</v>
+        <v>0.3484412420554786</v>
       </c>
       <c r="D54">
-        <v>1.2071705717431</v>
+        <v>1.193211242055479</v>
       </c>
       <c r="E54">
-        <v>2.05568</v>
+        <v>2.09577</v>
       </c>
       <c r="F54">
-        <v>2.08468</v>
+        <v>2.12477</v>
       </c>
       <c r="G54">
         <v>1.28</v>
@@ -5715,37 +5715,37 @@
         <v>0.167</v>
       </c>
       <c r="M54">
-        <v>0.491567544</v>
+        <v>0.5010207660000001</v>
       </c>
       <c r="N54">
-        <v>-0.324567544</v>
+        <v>-0.3340207660000001</v>
       </c>
       <c r="O54">
-        <v>-0.04868513159999999</v>
+        <v>-0.05010311490000001</v>
       </c>
       <c r="P54">
-        <v>-0.2758824124</v>
+        <v>-0.2839176511000001</v>
       </c>
       <c r="Q54">
-        <v>-0.2008824124</v>
+        <v>-0.2089176511000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1913334378289303</v>
+        <v>0.1944298939529501</v>
       </c>
       <c r="T54">
-        <v>1.896788566867363</v>
+        <v>1.937145770417733</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05095942623909279</v>
+        <v>0.04999792763080801</v>
       </c>
       <c r="W54">
-        <v>0.2237837672928219</v>
+        <v>0.2240104886646555</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3397295082606187</v>
+        <v>0.3333195175387201</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2101076091501539</v>
+        <v>0.2120076091501539</v>
       </c>
       <c r="C55">
-        <v>0.3484412420554786</v>
+        <v>0.2947110641388506</v>
       </c>
       <c r="D55">
-        <v>1.193211242055479</v>
+        <v>1.179571064138851</v>
       </c>
       <c r="E55">
-        <v>2.09577</v>
+        <v>2.135860000000001</v>
       </c>
       <c r="F55">
-        <v>2.12477</v>
+        <v>2.16486</v>
       </c>
       <c r="G55">
         <v>1.28</v>
@@ -5797,37 +5797,37 @@
         <v>0.167</v>
       </c>
       <c r="M55">
-        <v>0.5010207660000001</v>
+        <v>0.5104739880000001</v>
       </c>
       <c r="N55">
-        <v>-0.3340207660000001</v>
+        <v>-0.3434739880000001</v>
       </c>
       <c r="O55">
-        <v>-0.05010311490000001</v>
+        <v>-0.05152109820000001</v>
       </c>
       <c r="P55">
-        <v>-0.2839176511000001</v>
+        <v>-0.2919528898000001</v>
       </c>
       <c r="Q55">
-        <v>-0.2089176511000001</v>
+        <v>-0.2169528898000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1944298939529501</v>
+        <v>0.1976609786041011</v>
       </c>
       <c r="T55">
-        <v>1.937145770417733</v>
+        <v>1.979257634992031</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04999792763080801</v>
+        <v>0.04907204008208934</v>
       </c>
       <c r="W55">
-        <v>0.2240104886646555</v>
+        <v>0.2242288129486434</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3333195175387201</v>
+        <v>0.3271469338805957</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2120076091501539</v>
+        <v>0.2139076091501539</v>
       </c>
       <c r="C56">
-        <v>0.2947110641388506</v>
+        <v>0.2412892165610172</v>
       </c>
       <c r="D56">
-        <v>1.179571064138851</v>
+        <v>1.166239216561018</v>
       </c>
       <c r="E56">
-        <v>2.135860000000001</v>
+        <v>2.17595</v>
       </c>
       <c r="F56">
-        <v>2.16486</v>
+        <v>2.20495</v>
       </c>
       <c r="G56">
         <v>1.28</v>
@@ -5879,37 +5879,37 @@
         <v>0.167</v>
       </c>
       <c r="M56">
-        <v>0.5104739880000001</v>
+        <v>0.5199272100000001</v>
       </c>
       <c r="N56">
-        <v>-0.3434739880000001</v>
+        <v>-0.35292721</v>
       </c>
       <c r="O56">
-        <v>-0.05152109820000001</v>
+        <v>-0.05293908150000001</v>
       </c>
       <c r="P56">
-        <v>-0.2919528898000001</v>
+        <v>-0.2999881285000001</v>
       </c>
       <c r="Q56">
-        <v>-0.2169528898000001</v>
+        <v>-0.2249881285000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1976609786041011</v>
+        <v>0.2010356670175256</v>
       </c>
       <c r="T56">
-        <v>1.979257634992031</v>
+        <v>2.023241137991854</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04907204008208934</v>
+        <v>0.04817982117150591</v>
       </c>
       <c r="W56">
-        <v>0.2242288129486434</v>
+        <v>0.2244391981677589</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3271469338805957</v>
+        <v>0.3211988078100394</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2139076091501539</v>
+        <v>0.215807609150154</v>
       </c>
       <c r="C57">
-        <v>0.2412892165610172</v>
+        <v>0.1881653616498005</v>
       </c>
       <c r="D57">
-        <v>1.166239216561018</v>
+        <v>1.153205361649801</v>
       </c>
       <c r="E57">
-        <v>2.17595</v>
+        <v>2.21604</v>
       </c>
       <c r="F57">
-        <v>2.20495</v>
+        <v>2.24504</v>
       </c>
       <c r="G57">
         <v>1.28</v>
@@ -5961,37 +5961,37 @@
         <v>0.167</v>
       </c>
       <c r="M57">
-        <v>0.5199272100000001</v>
+        <v>0.5293804320000001</v>
       </c>
       <c r="N57">
-        <v>-0.35292721</v>
+        <v>-0.362380432</v>
       </c>
       <c r="O57">
-        <v>-0.05293908150000001</v>
+        <v>-0.0543570648</v>
       </c>
       <c r="P57">
-        <v>-0.2999881285000001</v>
+        <v>-0.3080233672</v>
       </c>
       <c r="Q57">
-        <v>-0.2249881285000001</v>
+        <v>-0.2330233672</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2010356670175256</v>
+        <v>0.204563750358833</v>
       </c>
       <c r="T57">
-        <v>2.023241137991854</v>
+        <v>2.069223891128033</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04817982117150591</v>
+        <v>0.04731946722201473</v>
       </c>
       <c r="W57">
-        <v>0.2244391981677589</v>
+        <v>0.2246420696290489</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3211988078100394</v>
+        <v>0.3154631148134316</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.215807609150154</v>
+        <v>0.217707609150154</v>
       </c>
       <c r="C58">
-        <v>0.1881653616498005</v>
+        <v>0.1353296187593807</v>
       </c>
       <c r="D58">
-        <v>1.153205361649801</v>
+        <v>1.140459618759381</v>
       </c>
       <c r="E58">
-        <v>2.21604</v>
+        <v>2.256130000000001</v>
       </c>
       <c r="F58">
-        <v>2.24504</v>
+        <v>2.285130000000001</v>
       </c>
       <c r="G58">
         <v>1.28</v>
@@ -6043,37 +6043,37 @@
         <v>0.167</v>
       </c>
       <c r="M58">
-        <v>0.5293804320000001</v>
+        <v>0.5388336540000002</v>
       </c>
       <c r="N58">
-        <v>-0.362380432</v>
+        <v>-0.3718336540000001</v>
       </c>
       <c r="O58">
-        <v>-0.0543570648</v>
+        <v>-0.05577504810000002</v>
       </c>
       <c r="P58">
-        <v>-0.3080233672</v>
+        <v>-0.3160586059000001</v>
       </c>
       <c r="Q58">
-        <v>-0.2330233672</v>
+        <v>-0.2410586059000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.204563750358833</v>
+        <v>0.2082559305997361</v>
       </c>
       <c r="T58">
-        <v>2.069223891128033</v>
+        <v>2.11734537696822</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04731946722201473</v>
+        <v>0.04648930113040042</v>
       </c>
       <c r="W58">
-        <v>0.2246420696290489</v>
+        <v>0.2248378227934516</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3154631148134316</v>
+        <v>0.3099286742026696</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.217707609150154</v>
+        <v>0.219607609150154</v>
       </c>
       <c r="C59">
-        <v>0.1353296187593807</v>
+        <v>0.08277253929008799</v>
       </c>
       <c r="D59">
-        <v>1.140459618759381</v>
+        <v>1.127992539290088</v>
       </c>
       <c r="E59">
-        <v>2.256130000000001</v>
+        <v>2.29622</v>
       </c>
       <c r="F59">
-        <v>2.285130000000001</v>
+        <v>2.32522</v>
       </c>
       <c r="G59">
         <v>1.28</v>
@@ -6125,37 +6125,37 @@
         <v>0.167</v>
       </c>
       <c r="M59">
-        <v>0.5388336540000002</v>
+        <v>0.5482868760000001</v>
       </c>
       <c r="N59">
-        <v>-0.3718336540000001</v>
+        <v>-0.3812868760000001</v>
       </c>
       <c r="O59">
-        <v>-0.05577504810000002</v>
+        <v>-0.05719303140000001</v>
       </c>
       <c r="P59">
-        <v>-0.3160586059000001</v>
+        <v>-0.3240938446000001</v>
       </c>
       <c r="Q59">
-        <v>-0.2410586059000001</v>
+        <v>-0.2490938446000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2082559305997361</v>
+        <v>0.2121239289473489</v>
       </c>
       <c r="T59">
-        <v>2.11734537696822</v>
+        <v>2.16775836213413</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04648930113040042</v>
+        <v>0.04568776145573836</v>
       </c>
       <c r="W59">
-        <v>0.2248378227934516</v>
+        <v>0.2250268258487369</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3099286742026696</v>
+        <v>0.304585076371589</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2196076091501539</v>
+        <v>0.2215076091501539</v>
       </c>
       <c r="C60">
-        <v>0.08277253929008843</v>
+        <v>0.03048508332891986</v>
       </c>
       <c r="D60">
-        <v>1.127992539290088</v>
+        <v>1.11579508332892</v>
       </c>
       <c r="E60">
-        <v>2.29622</v>
+        <v>2.33631</v>
       </c>
       <c r="F60">
-        <v>2.32522</v>
+        <v>2.36531</v>
       </c>
       <c r="G60">
         <v>1.28</v>
@@ -6207,37 +6207,37 @@
         <v>0.167</v>
       </c>
       <c r="M60">
-        <v>0.548286876</v>
+        <v>0.557740098</v>
       </c>
       <c r="N60">
-        <v>-0.381286876</v>
+        <v>-0.390740098</v>
       </c>
       <c r="O60">
-        <v>-0.0571930314</v>
+        <v>-0.05861101469999999</v>
       </c>
       <c r="P60">
-        <v>-0.3240938446</v>
+        <v>-0.3321290833</v>
       </c>
       <c r="Q60">
-        <v>-0.2490938446</v>
+        <v>-0.2571290833000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2121239289473489</v>
+        <v>0.2161806101411866</v>
       </c>
       <c r="T60">
-        <v>2.167758362134129</v>
+        <v>2.220630517308133</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04568776145573836</v>
+        <v>0.04491339261750551</v>
       </c>
       <c r="W60">
-        <v>0.2250268258487369</v>
+        <v>0.2252094220207922</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3045850763715892</v>
+        <v>0.2994226174500368</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2215076091501539</v>
+        <v>0.2234076091501539</v>
       </c>
       <c r="C61">
-        <v>0.03048508332891986</v>
+        <v>-0.02154140221057421</v>
       </c>
       <c r="D61">
-        <v>1.11579508332892</v>
+        <v>1.103858597789426</v>
       </c>
       <c r="E61">
-        <v>2.33631</v>
+        <v>2.3764</v>
       </c>
       <c r="F61">
-        <v>2.36531</v>
+        <v>2.4054</v>
       </c>
       <c r="G61">
         <v>1.28</v>
@@ -6289,37 +6289,37 @@
         <v>0.167</v>
       </c>
       <c r="M61">
-        <v>0.557740098</v>
+        <v>0.5671933200000001</v>
       </c>
       <c r="N61">
-        <v>-0.390740098</v>
+        <v>-0.4001933200000001</v>
       </c>
       <c r="O61">
-        <v>-0.05861101469999999</v>
+        <v>-0.06002899800000001</v>
       </c>
       <c r="P61">
-        <v>-0.3321290833</v>
+        <v>-0.3401643220000001</v>
       </c>
       <c r="Q61">
-        <v>-0.2571290833000001</v>
+        <v>-0.2651643220000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2161806101411866</v>
+        <v>0.2204401253947163</v>
       </c>
       <c r="T61">
-        <v>2.220630517308133</v>
+        <v>2.276146280240836</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04491339261750551</v>
+        <v>0.04416483607388041</v>
       </c>
       <c r="W61">
-        <v>0.2252094220207922</v>
+        <v>0.225385931653779</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2994226174500368</v>
+        <v>0.2944322404925361</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2234076091501539</v>
+        <v>0.2253076091501539</v>
       </c>
       <c r="C62">
-        <v>-0.02154140221057421</v>
+        <v>-0.0733152040601408</v>
       </c>
       <c r="D62">
-        <v>1.103858597789426</v>
+        <v>1.092174795939859</v>
       </c>
       <c r="E62">
-        <v>2.3764</v>
+        <v>2.41649</v>
       </c>
       <c r="F62">
-        <v>2.4054</v>
+        <v>2.44549</v>
       </c>
       <c r="G62">
         <v>1.28</v>
@@ -6371,37 +6371,37 @@
         <v>0.167</v>
       </c>
       <c r="M62">
-        <v>0.5671933200000001</v>
+        <v>0.576646542</v>
       </c>
       <c r="N62">
-        <v>-0.4001933200000001</v>
+        <v>-0.4096465419999999</v>
       </c>
       <c r="O62">
-        <v>-0.06002899800000001</v>
+        <v>-0.06144698129999999</v>
       </c>
       <c r="P62">
-        <v>-0.3401643220000001</v>
+        <v>-0.3481995607</v>
       </c>
       <c r="Q62">
-        <v>-0.2651643220000001</v>
+        <v>-0.2731995607</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2204401253947163</v>
+        <v>0.2249180773279142</v>
       </c>
       <c r="T62">
-        <v>2.276146280240836</v>
+        <v>2.334509005375216</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04416483607388041</v>
+        <v>0.04344082236775123</v>
       </c>
       <c r="W62">
-        <v>0.225385931653779</v>
+        <v>0.2255566540856843</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2944322404925361</v>
+        <v>0.2896054824516749</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2253076091501539</v>
+        <v>0.2272076091501539</v>
       </c>
       <c r="C63">
-        <v>-0.0733152040601408</v>
+        <v>-0.1248442617821803</v>
       </c>
       <c r="D63">
-        <v>1.092174795939859</v>
+        <v>1.08073573821782</v>
       </c>
       <c r="E63">
-        <v>2.41649</v>
+        <v>2.45658</v>
       </c>
       <c r="F63">
-        <v>2.44549</v>
+        <v>2.48558</v>
       </c>
       <c r="G63">
         <v>1.28</v>
@@ -6453,37 +6453,37 @@
         <v>0.167</v>
       </c>
       <c r="M63">
-        <v>0.576646542</v>
+        <v>0.5860997640000001</v>
       </c>
       <c r="N63">
-        <v>-0.4096465419999999</v>
+        <v>-0.419099764</v>
       </c>
       <c r="O63">
-        <v>-0.06144698129999999</v>
+        <v>-0.0628649646</v>
       </c>
       <c r="P63">
-        <v>-0.3481995607</v>
+        <v>-0.3562347994</v>
       </c>
       <c r="Q63">
-        <v>-0.2731995607</v>
+        <v>-0.2812347994000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2249180773279142</v>
+        <v>0.2296317109418066</v>
       </c>
       <c r="T63">
-        <v>2.334509005375216</v>
+        <v>2.395943452885091</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04344082236775123</v>
+        <v>0.04274016394246492</v>
       </c>
       <c r="W63">
-        <v>0.2255566540856843</v>
+        <v>0.2257218693423668</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2896054824516749</v>
+        <v>0.2849344262830995</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2272076091501539</v>
+        <v>0.2291076091501539</v>
       </c>
       <c r="C64">
-        <v>-0.1248442617821803</v>
+        <v>-0.176136185761953</v>
       </c>
       <c r="D64">
-        <v>1.08073573821782</v>
+        <v>1.069533814238047</v>
       </c>
       <c r="E64">
-        <v>2.45658</v>
+        <v>2.49667</v>
       </c>
       <c r="F64">
-        <v>2.48558</v>
+        <v>2.52567</v>
       </c>
       <c r="G64">
         <v>1.28</v>
@@ -6535,37 +6535,37 @@
         <v>0.167</v>
       </c>
       <c r="M64">
-        <v>0.5860997640000001</v>
+        <v>0.5955529860000001</v>
       </c>
       <c r="N64">
-        <v>-0.419099764</v>
+        <v>-0.428552986</v>
       </c>
       <c r="O64">
-        <v>-0.0628649646</v>
+        <v>-0.0642829479</v>
       </c>
       <c r="P64">
-        <v>-0.3562347994</v>
+        <v>-0.3642700381</v>
       </c>
       <c r="Q64">
-        <v>-0.2812347994000001</v>
+        <v>-0.2892700381000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2296317109418066</v>
+        <v>0.2346001355618555</v>
       </c>
       <c r="T64">
-        <v>2.395943452885091</v>
+        <v>2.460698681341444</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04274016394246492</v>
+        <v>0.04206174864179087</v>
       </c>
       <c r="W64">
-        <v>0.2257218693423668</v>
+        <v>0.2258818396702657</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2849344262830995</v>
+        <v>0.2804116576119392</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2291076091501539</v>
+        <v>0.2310076091501539</v>
       </c>
       <c r="C65">
-        <v>-0.176136185761953</v>
+        <v>-0.227198274092324</v>
       </c>
       <c r="D65">
-        <v>1.069533814238047</v>
+        <v>1.058561725907676</v>
       </c>
       <c r="E65">
-        <v>2.49667</v>
+        <v>2.536760000000001</v>
       </c>
       <c r="F65">
-        <v>2.52567</v>
+        <v>2.56576</v>
       </c>
       <c r="G65">
         <v>1.28</v>
@@ -6617,37 +6617,37 @@
         <v>0.167</v>
       </c>
       <c r="M65">
-        <v>0.5955529860000001</v>
+        <v>0.6050062080000002</v>
       </c>
       <c r="N65">
-        <v>-0.428552986</v>
+        <v>-0.4380062080000001</v>
       </c>
       <c r="O65">
-        <v>-0.0642829479</v>
+        <v>-0.06570093120000002</v>
       </c>
       <c r="P65">
-        <v>-0.3642700381</v>
+        <v>-0.3723052768000001</v>
       </c>
       <c r="Q65">
-        <v>-0.2892700381000001</v>
+        <v>-0.2973052768000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2346001355618555</v>
+        <v>0.239844583771907</v>
       </c>
       <c r="T65">
-        <v>2.460698681341444</v>
+        <v>2.529051422489818</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04206174864179087</v>
+        <v>0.04140453381926288</v>
       </c>
       <c r="W65">
-        <v>0.2258818396702657</v>
+        <v>0.2260368109254178</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2804116576119392</v>
+        <v>0.2760302254617526</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2310076091501539</v>
+        <v>0.2329076091501539</v>
       </c>
       <c r="C66">
-        <v>-0.227198274092324</v>
+        <v>-0.2780375284297598</v>
       </c>
       <c r="D66">
-        <v>1.058561725907676</v>
+        <v>1.04781247157024</v>
       </c>
       <c r="E66">
-        <v>2.536760000000001</v>
+        <v>2.57685</v>
       </c>
       <c r="F66">
-        <v>2.56576</v>
+        <v>2.60585</v>
       </c>
       <c r="G66">
         <v>1.28</v>
@@ -6699,37 +6699,37 @@
         <v>0.167</v>
       </c>
       <c r="M66">
-        <v>0.6050062080000002</v>
+        <v>0.61445943</v>
       </c>
       <c r="N66">
-        <v>-0.4380062080000001</v>
+        <v>-0.44745943</v>
       </c>
       <c r="O66">
-        <v>-0.06570093120000002</v>
+        <v>-0.0671189145</v>
       </c>
       <c r="P66">
-        <v>-0.3723052768000001</v>
+        <v>-0.3803405155</v>
       </c>
       <c r="Q66">
-        <v>-0.2973052768000001</v>
+        <v>-0.3053405155</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.239844583771907</v>
+        <v>0.2453887147368187</v>
       </c>
       <c r="T66">
-        <v>2.529051422489818</v>
+        <v>2.601310034560956</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04140453381926288</v>
+        <v>0.04076754099127423</v>
       </c>
       <c r="W66">
-        <v>0.2260368109254178</v>
+        <v>0.2261870138342575</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2760302254617526</v>
+        <v>0.271783606608495</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2329076091501539</v>
+        <v>0.2348076091501539</v>
       </c>
       <c r="C67">
-        <v>-0.2780375284297598</v>
+        <v>-0.3286606688939719</v>
       </c>
       <c r="D67">
-        <v>1.04781247157024</v>
+        <v>1.037279331106028</v>
       </c>
       <c r="E67">
-        <v>2.57685</v>
+        <v>2.61694</v>
       </c>
       <c r="F67">
-        <v>2.60585</v>
+        <v>2.64594</v>
       </c>
       <c r="G67">
         <v>1.28</v>
@@ -6781,37 +6781,37 @@
         <v>0.167</v>
       </c>
       <c r="M67">
-        <v>0.61445943</v>
+        <v>0.6239126520000001</v>
       </c>
       <c r="N67">
-        <v>-0.44745943</v>
+        <v>-0.4569126520000001</v>
       </c>
       <c r="O67">
-        <v>-0.0671189145</v>
+        <v>-0.06853689780000001</v>
       </c>
       <c r="P67">
-        <v>-0.3803405155</v>
+        <v>-0.3883757542000001</v>
       </c>
       <c r="Q67">
-        <v>-0.3053405155</v>
+        <v>-0.3133757542000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2453887147368187</v>
+        <v>0.2512589710526075</v>
       </c>
       <c r="T67">
-        <v>2.601310034560956</v>
+        <v>2.677819153224513</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04076754099127423</v>
+        <v>0.04014985097625492</v>
       </c>
       <c r="W67">
-        <v>0.2261870138342575</v>
+        <v>0.2263326651397991</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.271783606608495</v>
+        <v>0.2676656731750329</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2348076091501539</v>
+        <v>0.2367076091501539</v>
       </c>
       <c r="C68">
-        <v>-0.3286606688939719</v>
+        <v>-0.3790741480778288</v>
       </c>
       <c r="D68">
-        <v>1.037279331106028</v>
+        <v>1.026955851922172</v>
       </c>
       <c r="E68">
-        <v>2.61694</v>
+        <v>2.657030000000001</v>
       </c>
       <c r="F68">
-        <v>2.64594</v>
+        <v>2.686030000000001</v>
       </c>
       <c r="G68">
         <v>1.28</v>
@@ -6863,37 +6863,37 @@
         <v>0.167</v>
       </c>
       <c r="M68">
-        <v>0.6239126520000001</v>
+        <v>0.6333658740000002</v>
       </c>
       <c r="N68">
-        <v>-0.4569126520000001</v>
+        <v>-0.4663658740000002</v>
       </c>
       <c r="O68">
-        <v>-0.06853689780000001</v>
+        <v>-0.06995488110000002</v>
       </c>
       <c r="P68">
-        <v>-0.3883757542000001</v>
+        <v>-0.3964109929000001</v>
       </c>
       <c r="Q68">
-        <v>-0.3133757542000001</v>
+        <v>-0.3214109929000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2512589710526075</v>
+        <v>0.257485000478444</v>
       </c>
       <c r="T68">
-        <v>2.677819153224513</v>
+        <v>2.75896518817071</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04014985097625492</v>
+        <v>0.03955059946914663</v>
       </c>
       <c r="W68">
-        <v>0.2263326651397991</v>
+        <v>0.2264739686451752</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2676656731750329</v>
+        <v>0.2636706631276443</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2367076091501539</v>
+        <v>0.2386076091501539</v>
       </c>
       <c r="C69">
-        <v>-0.3790741480778288</v>
+        <v>-0.4292841642289162</v>
       </c>
       <c r="D69">
-        <v>1.026955851922172</v>
+        <v>1.016835835771084</v>
       </c>
       <c r="E69">
-        <v>2.657030000000001</v>
+        <v>2.69712</v>
       </c>
       <c r="F69">
-        <v>2.686030000000001</v>
+        <v>2.72612</v>
       </c>
       <c r="G69">
         <v>1.28</v>
@@ -6945,37 +6945,37 @@
         <v>0.167</v>
       </c>
       <c r="M69">
-        <v>0.6333658740000002</v>
+        <v>0.6428190960000001</v>
       </c>
       <c r="N69">
-        <v>-0.4663658740000002</v>
+        <v>-0.4758190960000001</v>
       </c>
       <c r="O69">
-        <v>-0.06995488110000002</v>
+        <v>-0.0713728644</v>
       </c>
       <c r="P69">
-        <v>-0.3964109929000001</v>
+        <v>-0.4044462316</v>
       </c>
       <c r="Q69">
-        <v>-0.3214109929000002</v>
+        <v>-0.3294462316000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.257485000478444</v>
+        <v>0.2641001567433954</v>
       </c>
       <c r="T69">
-        <v>2.75896518817071</v>
+        <v>2.845182850301046</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03955059946914663</v>
+        <v>0.03896897300636507</v>
       </c>
       <c r="W69">
-        <v>0.2264739686451752</v>
+        <v>0.2266111161650991</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2636706631276443</v>
+        <v>0.2597931533757671</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2386076091501539</v>
+        <v>0.240507609150154</v>
       </c>
       <c r="C70">
-        <v>-0.4292841642289162</v>
+        <v>-0.4792966736593267</v>
       </c>
       <c r="D70">
-        <v>1.016835835771084</v>
+        <v>1.006913326340674</v>
       </c>
       <c r="E70">
-        <v>2.69712</v>
+        <v>2.737210000000001</v>
       </c>
       <c r="F70">
-        <v>2.72612</v>
+        <v>2.766210000000001</v>
       </c>
       <c r="G70">
         <v>1.28</v>
@@ -7027,37 +7027,37 @@
         <v>0.167</v>
       </c>
       <c r="M70">
-        <v>0.6428190960000001</v>
+        <v>0.6522723180000002</v>
       </c>
       <c r="N70">
-        <v>-0.4758190960000001</v>
+        <v>-0.4852723180000001</v>
       </c>
       <c r="O70">
-        <v>-0.0713728644</v>
+        <v>-0.07279084770000002</v>
       </c>
       <c r="P70">
-        <v>-0.4044462316</v>
+        <v>-0.4124814703000002</v>
       </c>
       <c r="Q70">
-        <v>-0.3294462316000001</v>
+        <v>-0.3374814703000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2641001567433954</v>
+        <v>0.271142097283505</v>
       </c>
       <c r="T70">
-        <v>2.845182850301046</v>
+        <v>2.936962942246241</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03896897300636507</v>
+        <v>0.03840420528163514</v>
       </c>
       <c r="W70">
-        <v>0.2266111161650991</v>
+        <v>0.2267442883945905</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2597931533757671</v>
+        <v>0.256028035210901</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.240507609150154</v>
+        <v>0.2424076091501539</v>
       </c>
       <c r="C71">
-        <v>-0.4792966736593267</v>
+        <v>-0.5291174024358831</v>
       </c>
       <c r="D71">
-        <v>1.006913326340674</v>
+        <v>0.9971825975641176</v>
       </c>
       <c r="E71">
-        <v>2.737210000000001</v>
+        <v>2.777300000000001</v>
       </c>
       <c r="F71">
-        <v>2.766210000000001</v>
+        <v>2.806300000000001</v>
       </c>
       <c r="G71">
         <v>1.28</v>
@@ -7109,37 +7109,37 @@
         <v>0.167</v>
       </c>
       <c r="M71">
-        <v>0.6522723180000002</v>
+        <v>0.6617255400000002</v>
       </c>
       <c r="N71">
-        <v>-0.4852723180000001</v>
+        <v>-0.4947255400000001</v>
       </c>
       <c r="O71">
-        <v>-0.07279084770000002</v>
+        <v>-0.07420883100000002</v>
       </c>
       <c r="P71">
-        <v>-0.4124814703000002</v>
+        <v>-0.4205167090000001</v>
       </c>
       <c r="Q71">
-        <v>-0.3374814703000002</v>
+        <v>-0.3455167090000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.271142097283505</v>
+        <v>0.2786535005262885</v>
       </c>
       <c r="T71">
-        <v>2.936962942246241</v>
+        <v>3.034861706987782</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03840420528163514</v>
+        <v>0.03785557377761178</v>
       </c>
       <c r="W71">
-        <v>0.2267442883945905</v>
+        <v>0.2268736557032391</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.256028035210901</v>
+        <v>0.2523704918507452</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2424076091501539</v>
+        <v>0.2443076091501539</v>
       </c>
       <c r="C72">
-        <v>-0.5291174024358831</v>
+        <v>-0.5787518573990105</v>
       </c>
       <c r="D72">
-        <v>0.9971825975641176</v>
+        <v>0.9876381426009899</v>
       </c>
       <c r="E72">
-        <v>2.777300000000001</v>
+        <v>2.817390000000001</v>
       </c>
       <c r="F72">
-        <v>2.806300000000001</v>
+        <v>2.84639</v>
       </c>
       <c r="G72">
         <v>1.28</v>
@@ -7191,37 +7191,37 @@
         <v>0.167</v>
       </c>
       <c r="M72">
-        <v>0.6617255400000002</v>
+        <v>0.6711787620000002</v>
       </c>
       <c r="N72">
-        <v>-0.4947255400000001</v>
+        <v>-0.5041787620000001</v>
       </c>
       <c r="O72">
-        <v>-0.07420883100000002</v>
+        <v>-0.07562681430000001</v>
       </c>
       <c r="P72">
-        <v>-0.4205167090000001</v>
+        <v>-0.4285519477000001</v>
       </c>
       <c r="Q72">
-        <v>-0.3455167090000001</v>
+        <v>-0.3535519477000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2786535005262885</v>
+        <v>0.2866829315789191</v>
       </c>
       <c r="T72">
-        <v>3.034861706987782</v>
+        <v>3.139512110677016</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03785557377761178</v>
+        <v>0.03732239668215246</v>
       </c>
       <c r="W72">
-        <v>0.2268736557032391</v>
+        <v>0.2269993788623485</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2523704918507452</v>
+        <v>0.2488159778810164</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2443076091501539</v>
+        <v>0.2462076091501539</v>
       </c>
       <c r="C73">
-        <v>-0.57875185739901</v>
+        <v>-0.6282053365548137</v>
       </c>
       <c r="D73">
-        <v>0.9876381426009899</v>
+        <v>0.9782746634451865</v>
       </c>
       <c r="E73">
-        <v>2.81739</v>
+        <v>2.85748</v>
       </c>
       <c r="F73">
-        <v>2.84639</v>
+        <v>2.88648</v>
       </c>
       <c r="G73">
         <v>1.28</v>
@@ -7273,37 +7273,37 @@
         <v>0.167</v>
       </c>
       <c r="M73">
-        <v>0.671178762</v>
+        <v>0.680631984</v>
       </c>
       <c r="N73">
-        <v>-0.504178762</v>
+        <v>-0.513631984</v>
       </c>
       <c r="O73">
-        <v>-0.0756268143</v>
+        <v>-0.07704479759999999</v>
       </c>
       <c r="P73">
-        <v>-0.4285519477</v>
+        <v>-0.4365871864</v>
       </c>
       <c r="Q73">
-        <v>-0.3535519477</v>
+        <v>-0.3615871864</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2866829315789191</v>
+        <v>0.2952858934210232</v>
       </c>
       <c r="T73">
-        <v>3.139512110677015</v>
+        <v>3.251637543201194</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03732239668215247</v>
+        <v>0.03680403006156702</v>
       </c>
       <c r="W73">
-        <v>0.2269993788623485</v>
+        <v>0.2271216097114825</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2488159778810165</v>
+        <v>0.2453602004104468</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2462076091501539</v>
+        <v>0.2481076091501539</v>
       </c>
       <c r="C74">
-        <v>-0.6282053365548137</v>
+        <v>-0.6774829388815573</v>
       </c>
       <c r="D74">
-        <v>0.9782746634451865</v>
+        <v>0.9690870611184432</v>
       </c>
       <c r="E74">
-        <v>2.85748</v>
+        <v>2.89757</v>
       </c>
       <c r="F74">
-        <v>2.88648</v>
+        <v>2.92657</v>
       </c>
       <c r="G74">
         <v>1.28</v>
@@ -7355,37 +7355,37 @@
         <v>0.167</v>
       </c>
       <c r="M74">
-        <v>0.680631984</v>
+        <v>0.6900852060000001</v>
       </c>
       <c r="N74">
-        <v>-0.513631984</v>
+        <v>-0.5230852060000001</v>
       </c>
       <c r="O74">
-        <v>-0.07704479759999999</v>
+        <v>-0.07846278090000001</v>
       </c>
       <c r="P74">
-        <v>-0.4365871864</v>
+        <v>-0.4446224251000001</v>
       </c>
       <c r="Q74">
-        <v>-0.3615871864</v>
+        <v>-0.3696224251000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2952858934210232</v>
+        <v>0.304526111695876</v>
       </c>
       <c r="T74">
-        <v>3.251637543201194</v>
+        <v>3.372068563319757</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03680403006156702</v>
+        <v>0.03629986526620308</v>
       </c>
       <c r="W74">
-        <v>0.2271216097114825</v>
+        <v>0.2272404917702293</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2453602004104468</v>
+        <v>0.2419991017746872</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2481076091501539</v>
+        <v>0.2500076091501539</v>
       </c>
       <c r="C75">
-        <v>-0.6774829388815573</v>
+        <v>-0.7265895735886954</v>
       </c>
       <c r="D75">
-        <v>0.9690870611184432</v>
+        <v>0.9600704264113046</v>
       </c>
       <c r="E75">
-        <v>2.89757</v>
+        <v>2.93766</v>
       </c>
       <c r="F75">
-        <v>2.92657</v>
+        <v>2.96666</v>
       </c>
       <c r="G75">
         <v>1.28</v>
@@ -7437,37 +7437,37 @@
         <v>0.167</v>
       </c>
       <c r="M75">
-        <v>0.6900852060000001</v>
+        <v>0.6995384280000001</v>
       </c>
       <c r="N75">
-        <v>-0.5230852060000001</v>
+        <v>-0.5325384280000001</v>
       </c>
       <c r="O75">
-        <v>-0.07846278090000001</v>
+        <v>-0.07988076420000001</v>
       </c>
       <c r="P75">
-        <v>-0.4446224251000001</v>
+        <v>-0.4526576638000001</v>
       </c>
       <c r="Q75">
-        <v>-0.3696224251000001</v>
+        <v>-0.3776576638000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.304526111695876</v>
+        <v>0.3144771159918712</v>
       </c>
       <c r="T75">
-        <v>3.372068563319757</v>
+        <v>3.501763508062824</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03629986526620308</v>
+        <v>0.03580932654638953</v>
       </c>
       <c r="W75">
-        <v>0.2272404917702293</v>
+        <v>0.2273561608003613</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2419991017746872</v>
+        <v>0.2387288436425968</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2500076091501539</v>
+        <v>0.251907609150154</v>
       </c>
       <c r="C76">
-        <v>-0.7265895735886954</v>
+        <v>-0.7755299688637805</v>
       </c>
       <c r="D76">
-        <v>0.9600704264113046</v>
+        <v>0.9512200311362198</v>
       </c>
       <c r="E76">
-        <v>2.93766</v>
+        <v>2.97775</v>
       </c>
       <c r="F76">
-        <v>2.96666</v>
+        <v>3.00675</v>
       </c>
       <c r="G76">
         <v>1.28</v>
@@ -7519,37 +7519,37 @@
         <v>0.167</v>
       </c>
       <c r="M76">
-        <v>0.6995384280000001</v>
+        <v>0.7089916500000001</v>
       </c>
       <c r="N76">
-        <v>-0.5325384280000001</v>
+        <v>-0.54199165</v>
       </c>
       <c r="O76">
-        <v>-0.07988076420000001</v>
+        <v>-0.0812987475</v>
       </c>
       <c r="P76">
-        <v>-0.4526576638000001</v>
+        <v>-0.4606929025000001</v>
       </c>
       <c r="Q76">
-        <v>-0.3776576638000001</v>
+        <v>-0.3856929025000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3144771159918712</v>
+        <v>0.3252242006315461</v>
       </c>
       <c r="T76">
-        <v>3.501763508062824</v>
+        <v>3.641834048385338</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03580932654638953</v>
+        <v>0.03533186885910433</v>
       </c>
       <c r="W76">
-        <v>0.2273561608003613</v>
+        <v>0.2274687453230232</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2387288436425968</v>
+        <v>0.235545792394029</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.251907609150154</v>
+        <v>0.2538076091501539</v>
       </c>
       <c r="C77">
-        <v>-0.7755299688637805</v>
+        <v>-0.8243086801399828</v>
       </c>
       <c r="D77">
-        <v>0.9512200311362198</v>
+        <v>0.9425313198600177</v>
       </c>
       <c r="E77">
-        <v>2.97775</v>
+        <v>3.017840000000001</v>
       </c>
       <c r="F77">
-        <v>3.00675</v>
+        <v>3.04684</v>
       </c>
       <c r="G77">
         <v>1.28</v>
@@ -7601,37 +7601,37 @@
         <v>0.167</v>
       </c>
       <c r="M77">
-        <v>0.7089916500000001</v>
+        <v>0.7184448720000002</v>
       </c>
       <c r="N77">
-        <v>-0.54199165</v>
+        <v>-0.5514448720000001</v>
       </c>
       <c r="O77">
-        <v>-0.0812987475</v>
+        <v>-0.08271673080000001</v>
       </c>
       <c r="P77">
-        <v>-0.4606929025000001</v>
+        <v>-0.4687281412000001</v>
       </c>
       <c r="Q77">
-        <v>-0.3856929025000001</v>
+        <v>-0.3937281412000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3252242006315461</v>
+        <v>0.3368668756578606</v>
       </c>
       <c r="T77">
-        <v>3.641834048385338</v>
+        <v>3.793577133734727</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03533186885910433</v>
+        <v>0.03486697584780032</v>
       </c>
       <c r="W77">
-        <v>0.2274687453230232</v>
+        <v>0.2275783670950887</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.235545792394029</v>
+        <v>0.2324465056520022</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2538076091501539</v>
+        <v>0.2557076091501539</v>
       </c>
       <c r="C78">
-        <v>-0.8243086801399828</v>
+        <v>-0.8729300979146135</v>
       </c>
       <c r="D78">
-        <v>0.9425313198600177</v>
+        <v>0.9339999020853865</v>
       </c>
       <c r="E78">
-        <v>3.017840000000001</v>
+        <v>3.05793</v>
       </c>
       <c r="F78">
-        <v>3.04684</v>
+        <v>3.08693</v>
       </c>
       <c r="G78">
         <v>1.28</v>
@@ -7683,37 +7683,37 @@
         <v>0.167</v>
       </c>
       <c r="M78">
-        <v>0.7184448720000002</v>
+        <v>0.7278980940000001</v>
       </c>
       <c r="N78">
-        <v>-0.5514448720000001</v>
+        <v>-0.560898094</v>
       </c>
       <c r="O78">
-        <v>-0.08271673080000001</v>
+        <v>-0.08413471409999999</v>
       </c>
       <c r="P78">
-        <v>-0.4687281412000001</v>
+        <v>-0.4767633799</v>
       </c>
       <c r="Q78">
-        <v>-0.3937281412000001</v>
+        <v>-0.4017633799</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3368668756578606</v>
+        <v>0.3495219572082023</v>
       </c>
       <c r="T78">
-        <v>3.793577133734727</v>
+        <v>3.958515269984062</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03486697584780032</v>
+        <v>0.03441415797964708</v>
       </c>
       <c r="W78">
-        <v>0.2275783670950887</v>
+        <v>0.2276851415483992</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2324465056520022</v>
+        <v>0.2294277198643139</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2557076091501539</v>
+        <v>0.2576076091501539</v>
       </c>
       <c r="C79">
-        <v>-0.8729300979146135</v>
+        <v>-0.9213984551468331</v>
       </c>
       <c r="D79">
-        <v>0.9339999020853865</v>
+        <v>0.9256215448531672</v>
       </c>
       <c r="E79">
-        <v>3.05793</v>
+        <v>3.09802</v>
       </c>
       <c r="F79">
-        <v>3.08693</v>
+        <v>3.12702</v>
       </c>
       <c r="G79">
         <v>1.28</v>
@@ -7765,37 +7765,37 @@
         <v>0.167</v>
       </c>
       <c r="M79">
-        <v>0.7278980940000001</v>
+        <v>0.7373513160000001</v>
       </c>
       <c r="N79">
-        <v>-0.560898094</v>
+        <v>-0.5703513160000001</v>
       </c>
       <c r="O79">
-        <v>-0.08413471409999999</v>
+        <v>-0.08555269740000002</v>
       </c>
       <c r="P79">
-        <v>-0.4767633799</v>
+        <v>-0.4847986186000001</v>
       </c>
       <c r="Q79">
-        <v>-0.4017633799</v>
+        <v>-0.4097986186000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3495219572082023</v>
+        <v>0.3633275007176661</v>
       </c>
       <c r="T79">
-        <v>3.958515269984062</v>
+        <v>4.138447782256066</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03441415797964708</v>
+        <v>0.03397295082606185</v>
       </c>
       <c r="W79">
-        <v>0.2276851415483992</v>
+        <v>0.2277891781952146</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2294277198643139</v>
+        <v>0.2264863388404124</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2576076091501539</v>
+        <v>0.259507609150154</v>
       </c>
       <c r="C80">
-        <v>-0.9213984551468331</v>
+        <v>-0.96971783426073</v>
       </c>
       <c r="D80">
-        <v>0.9256215448531672</v>
+        <v>0.9173921657392704</v>
       </c>
       <c r="E80">
-        <v>3.09802</v>
+        <v>3.138110000000001</v>
       </c>
       <c r="F80">
-        <v>3.12702</v>
+        <v>3.167110000000001</v>
       </c>
       <c r="G80">
         <v>1.28</v>
@@ -7847,37 +7847,37 @@
         <v>0.167</v>
       </c>
       <c r="M80">
-        <v>0.7373513160000001</v>
+        <v>0.7468045380000001</v>
       </c>
       <c r="N80">
-        <v>-0.5703513160000001</v>
+        <v>-0.5798045380000001</v>
       </c>
       <c r="O80">
-        <v>-0.08555269740000002</v>
+        <v>-0.08697068070000001</v>
       </c>
       <c r="P80">
-        <v>-0.4847986186000001</v>
+        <v>-0.4928338573000001</v>
       </c>
       <c r="Q80">
-        <v>-0.4097986186000001</v>
+        <v>-0.4178338573000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3633275007176661</v>
+        <v>0.3784478578946979</v>
       </c>
       <c r="T80">
-        <v>4.138447782256066</v>
+        <v>4.335516724268261</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03397295082606185</v>
+        <v>0.03354291347383322</v>
       </c>
       <c r="W80">
-        <v>0.2277891781952146</v>
+        <v>0.2278905810028701</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2264863388404124</v>
+        <v>0.2236194231588882</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.259507609150154</v>
+        <v>0.261407609150154</v>
       </c>
       <c r="C81">
-        <v>-0.96971783426073</v>
+        <v>-1.017892173778129</v>
       </c>
       <c r="D81">
-        <v>0.9173921657392704</v>
+        <v>0.9093078262218711</v>
       </c>
       <c r="E81">
-        <v>3.138110000000001</v>
+        <v>3.1782</v>
       </c>
       <c r="F81">
-        <v>3.167110000000001</v>
+        <v>3.2072</v>
       </c>
       <c r="G81">
         <v>1.28</v>
@@ -7929,37 +7929,37 @@
         <v>0.167</v>
       </c>
       <c r="M81">
-        <v>0.7468045380000001</v>
+        <v>0.7562577600000001</v>
       </c>
       <c r="N81">
-        <v>-0.5798045380000001</v>
+        <v>-0.5892577600000001</v>
       </c>
       <c r="O81">
-        <v>-0.08697068070000001</v>
+        <v>-0.08838866400000001</v>
       </c>
       <c r="P81">
-        <v>-0.4928338573000001</v>
+        <v>-0.5008690960000001</v>
       </c>
       <c r="Q81">
-        <v>-0.4178338573000001</v>
+        <v>-0.4258690960000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3784478578946979</v>
+        <v>0.3950802507894327</v>
       </c>
       <c r="T81">
-        <v>4.335516724268261</v>
+        <v>4.552292560481673</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03354291347383322</v>
+        <v>0.03312362705541031</v>
       </c>
       <c r="W81">
-        <v>0.2278905810028701</v>
+        <v>0.2279894487403343</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2236194231588882</v>
+        <v>0.2208241803694021</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.261407609150154</v>
+        <v>0.2633076091501539</v>
       </c>
       <c r="C82">
-        <v>-1.017892173778129</v>
+        <v>-1.06592527460376</v>
       </c>
       <c r="D82">
-        <v>0.9093078262218711</v>
+        <v>0.9013647253962405</v>
       </c>
       <c r="E82">
-        <v>3.1782</v>
+        <v>3.218290000000001</v>
       </c>
       <c r="F82">
-        <v>3.2072</v>
+        <v>3.24729</v>
       </c>
       <c r="G82">
         <v>1.28</v>
@@ -8011,37 +8011,37 @@
         <v>0.167</v>
       </c>
       <c r="M82">
-        <v>0.7562577600000001</v>
+        <v>0.7657109820000001</v>
       </c>
       <c r="N82">
-        <v>-0.5892577600000001</v>
+        <v>-0.5987109820000001</v>
       </c>
       <c r="O82">
-        <v>-0.08838866400000001</v>
+        <v>-0.0898066473</v>
       </c>
       <c r="P82">
-        <v>-0.5008690960000001</v>
+        <v>-0.5089043347000001</v>
       </c>
       <c r="Q82">
-        <v>-0.4258690960000001</v>
+        <v>-0.4339043347000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3950802507894327</v>
+        <v>0.4134634218836134</v>
       </c>
       <c r="T82">
-        <v>4.552292560481673</v>
+        <v>4.791886905770182</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03312362705541031</v>
+        <v>0.03271469338805957</v>
       </c>
       <c r="W82">
-        <v>0.2279894487403343</v>
+        <v>0.2280858752990956</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2208241803694021</v>
+        <v>0.2180979559203972</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2633076091501539</v>
+        <v>0.265207609150154</v>
       </c>
       <c r="C83">
-        <v>-1.06592527460376</v>
+        <v>-1.113820805983854</v>
       </c>
       <c r="D83">
-        <v>0.9013647253962405</v>
+        <v>0.8935591940161468</v>
       </c>
       <c r="E83">
-        <v>3.218290000000001</v>
+        <v>3.258380000000001</v>
       </c>
       <c r="F83">
-        <v>3.24729</v>
+        <v>3.287380000000001</v>
       </c>
       <c r="G83">
         <v>1.28</v>
@@ -8093,37 +8093,37 @@
         <v>0.167</v>
       </c>
       <c r="M83">
-        <v>0.7657109820000001</v>
+        <v>0.7751642040000002</v>
       </c>
       <c r="N83">
-        <v>-0.5987109820000001</v>
+        <v>-0.6081642040000002</v>
       </c>
       <c r="O83">
-        <v>-0.0898066473</v>
+        <v>-0.09122463060000002</v>
       </c>
       <c r="P83">
-        <v>-0.5089043347000001</v>
+        <v>-0.5169395734000002</v>
       </c>
       <c r="Q83">
-        <v>-0.4339043347000001</v>
+        <v>-0.4419395734000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4134634218836134</v>
+        <v>0.4338891675438141</v>
       </c>
       <c r="T83">
-        <v>4.791886905770182</v>
+        <v>5.058102844979637</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03271469338805957</v>
+        <v>0.03231573371259542</v>
       </c>
       <c r="W83">
-        <v>0.2280858752990956</v>
+        <v>0.22817994999057</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2180979559203972</v>
+        <v>0.2154382247506362</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.265207609150154</v>
+        <v>0.2671076091501539</v>
       </c>
       <c r="C84">
-        <v>-1.113820805983854</v>
+        <v>-1.161582311157807</v>
       </c>
       <c r="D84">
-        <v>0.8935591940161468</v>
+        <v>0.8858876888421934</v>
       </c>
       <c r="E84">
-        <v>3.258380000000001</v>
+        <v>3.29847</v>
       </c>
       <c r="F84">
-        <v>3.287380000000001</v>
+        <v>3.32747</v>
       </c>
       <c r="G84">
         <v>1.28</v>
@@ -8175,37 +8175,37 @@
         <v>0.167</v>
       </c>
       <c r="M84">
-        <v>0.7751642040000002</v>
+        <v>0.7846174260000002</v>
       </c>
       <c r="N84">
-        <v>-0.6081642040000002</v>
+        <v>-0.6176174260000001</v>
       </c>
       <c r="O84">
-        <v>-0.09122463060000002</v>
+        <v>-0.09264261390000002</v>
       </c>
       <c r="P84">
-        <v>-0.5169395734000002</v>
+        <v>-0.5249748121000001</v>
       </c>
       <c r="Q84">
-        <v>-0.4419395734000002</v>
+        <v>-0.4499748121000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4338891675438141</v>
+        <v>0.456717942105215</v>
       </c>
       <c r="T84">
-        <v>5.058102844979637</v>
+        <v>5.355638306449028</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03231573371259542</v>
+        <v>0.03192638752328704</v>
       </c>
       <c r="W84">
-        <v>0.22817994999057</v>
+        <v>0.2282717578220089</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2154382247506362</v>
+        <v>0.2128425834885803</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2671076091501539</v>
+        <v>0.2690076091501539</v>
       </c>
       <c r="C85">
-        <v>-1.161582311157807</v>
+        <v>-1.209213212721194</v>
       </c>
       <c r="D85">
-        <v>0.8858876888421934</v>
+        <v>0.8783467872788068</v>
       </c>
       <c r="E85">
-        <v>3.29847</v>
+        <v>3.338560000000001</v>
       </c>
       <c r="F85">
-        <v>3.32747</v>
+        <v>3.367560000000001</v>
       </c>
       <c r="G85">
         <v>1.28</v>
@@ -8257,37 +8257,37 @@
         <v>0.167</v>
       </c>
       <c r="M85">
-        <v>0.7846174260000002</v>
+        <v>0.7940706480000002</v>
       </c>
       <c r="N85">
-        <v>-0.6176174260000001</v>
+        <v>-0.6270706480000001</v>
       </c>
       <c r="O85">
-        <v>-0.09264261390000002</v>
+        <v>-0.09406059720000001</v>
       </c>
       <c r="P85">
-        <v>-0.5249748121000001</v>
+        <v>-0.5330100508000001</v>
       </c>
       <c r="Q85">
-        <v>-0.4499748121000001</v>
+        <v>-0.4580100508000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.456717942105215</v>
+        <v>0.482400313486791</v>
       </c>
       <c r="T85">
-        <v>5.355638306449028</v>
+        <v>5.690365700602094</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03192638752328704</v>
+        <v>0.03154631148134315</v>
       </c>
       <c r="W85">
-        <v>0.2282717578220089</v>
+        <v>0.2283613797526993</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2128425834885803</v>
+        <v>0.2103087432089544</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2690076091501539</v>
+        <v>0.2709076091501539</v>
       </c>
       <c r="C86">
-        <v>-1.209213212721193</v>
+        <v>-1.256716817717177</v>
       </c>
       <c r="D86">
-        <v>0.8783467872788068</v>
+        <v>0.8709331822828226</v>
       </c>
       <c r="E86">
-        <v>3.33856</v>
+        <v>3.37865</v>
       </c>
       <c r="F86">
-        <v>3.36756</v>
+        <v>3.40765</v>
       </c>
       <c r="G86">
         <v>1.28</v>
@@ -8339,37 +8339,37 @@
         <v>0.167</v>
       </c>
       <c r="M86">
-        <v>0.794070648</v>
+        <v>0.8035238700000001</v>
       </c>
       <c r="N86">
-        <v>-0.627070648</v>
+        <v>-0.6365238700000001</v>
       </c>
       <c r="O86">
-        <v>-0.0940605972</v>
+        <v>-0.09547858050000001</v>
       </c>
       <c r="P86">
-        <v>-0.5330100508</v>
+        <v>-0.5410452895000001</v>
       </c>
       <c r="Q86">
-        <v>-0.4580100508</v>
+        <v>-0.4660452895000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4824003134867907</v>
+        <v>0.5115070010525767</v>
       </c>
       <c r="T86">
-        <v>5.69036570060209</v>
+        <v>6.069723413975562</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03154631148134315</v>
+        <v>0.03117517840509205</v>
       </c>
       <c r="W86">
-        <v>0.2283613797526993</v>
+        <v>0.2284488929320793</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2103087432089544</v>
+        <v>0.2078345227006138</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2709076091501539</v>
+        <v>0.272807609150154</v>
       </c>
       <c r="C87">
-        <v>-1.256716817717177</v>
+        <v>-1.304096322472249</v>
       </c>
       <c r="D87">
-        <v>0.8709331822828226</v>
+        <v>0.863643677527751</v>
       </c>
       <c r="E87">
-        <v>3.37865</v>
+        <v>3.41874</v>
       </c>
       <c r="F87">
-        <v>3.40765</v>
+        <v>3.44774</v>
       </c>
       <c r="G87">
         <v>1.28</v>
@@ -8421,37 +8421,37 @@
         <v>0.167</v>
       </c>
       <c r="M87">
-        <v>0.8035238700000001</v>
+        <v>0.812977092</v>
       </c>
       <c r="N87">
-        <v>-0.6365238700000001</v>
+        <v>-0.645977092</v>
       </c>
       <c r="O87">
-        <v>-0.09547858050000001</v>
+        <v>-0.09689656379999999</v>
       </c>
       <c r="P87">
-        <v>-0.5410452895000001</v>
+        <v>-0.5490805282</v>
       </c>
       <c r="Q87">
-        <v>-0.4660452895000001</v>
+        <v>-0.4740805282</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5115070010525767</v>
+        <v>0.5447717868420465</v>
       </c>
       <c r="T87">
-        <v>6.069723413975562</v>
+        <v>6.503275086402388</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03117517840509205</v>
+        <v>0.03081267633061424</v>
       </c>
       <c r="W87">
-        <v>0.2284488929320793</v>
+        <v>0.2285343709212412</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2078345227006138</v>
+        <v>0.205417842204095</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.272807609150154</v>
+        <v>0.2747076091501539</v>
       </c>
       <c r="C88">
-        <v>-1.304096322472249</v>
+        <v>-1.351354817191122</v>
       </c>
       <c r="D88">
-        <v>0.863643677527751</v>
+        <v>0.8564751828088784</v>
       </c>
       <c r="E88">
-        <v>3.41874</v>
+        <v>3.45883</v>
       </c>
       <c r="F88">
-        <v>3.44774</v>
+        <v>3.48783</v>
       </c>
       <c r="G88">
         <v>1.28</v>
@@ -8503,37 +8503,37 @@
         <v>0.167</v>
       </c>
       <c r="M88">
-        <v>0.812977092</v>
+        <v>0.8224303140000001</v>
       </c>
       <c r="N88">
-        <v>-0.645977092</v>
+        <v>-0.6554303140000001</v>
       </c>
       <c r="O88">
-        <v>-0.09689656379999999</v>
+        <v>-0.09831454710000001</v>
       </c>
       <c r="P88">
-        <v>-0.5490805282</v>
+        <v>-0.5571157669000001</v>
       </c>
       <c r="Q88">
-        <v>-0.4740805282</v>
+        <v>-0.4821157669000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5447717868420465</v>
+        <v>0.5831542319837424</v>
       </c>
       <c r="T88">
-        <v>6.503275086402388</v>
+        <v>7.003527016125648</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03081267633061424</v>
+        <v>0.03045850763715891</v>
       </c>
       <c r="W88">
-        <v>0.2285343709212412</v>
+        <v>0.2286178838991579</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.205417842204095</v>
+        <v>0.2030567175810594</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2747076091501539</v>
+        <v>0.2766076091501539</v>
       </c>
       <c r="C89">
-        <v>-1.351354817191122</v>
+        <v>-1.398495290324693</v>
       </c>
       <c r="D89">
-        <v>0.8564751828088784</v>
+        <v>0.8494247096753073</v>
       </c>
       <c r="E89">
-        <v>3.45883</v>
+        <v>3.49892</v>
       </c>
       <c r="F89">
-        <v>3.48783</v>
+        <v>3.52792</v>
       </c>
       <c r="G89">
         <v>1.28</v>
@@ -8585,37 +8585,37 @@
         <v>0.167</v>
       </c>
       <c r="M89">
-        <v>0.8224303140000001</v>
+        <v>0.8318835360000001</v>
       </c>
       <c r="N89">
-        <v>-0.6554303140000001</v>
+        <v>-0.6648835360000001</v>
       </c>
       <c r="O89">
-        <v>-0.09831454710000001</v>
+        <v>-0.09973253040000001</v>
       </c>
       <c r="P89">
-        <v>-0.5571157669000001</v>
+        <v>-0.5651510056000001</v>
       </c>
       <c r="Q89">
-        <v>-0.4821157669000001</v>
+        <v>-0.4901510056000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5831542319837424</v>
+        <v>0.6279337513157209</v>
       </c>
       <c r="T89">
-        <v>7.003527016125648</v>
+        <v>7.587154267469453</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03045850763715891</v>
+        <v>0.03011238823219119</v>
       </c>
       <c r="W89">
-        <v>0.2286178838991579</v>
+        <v>0.2286994988548493</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2030567175810594</v>
+        <v>0.2007492548812747</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2766076091501539</v>
+        <v>0.2785076091501539</v>
       </c>
       <c r="C90">
-        <v>-1.398495290324693</v>
+        <v>-1.445520632724012</v>
       </c>
       <c r="D90">
-        <v>0.8494247096753073</v>
+        <v>0.8424893672759889</v>
       </c>
       <c r="E90">
-        <v>3.49892</v>
+        <v>3.539010000000001</v>
       </c>
       <c r="F90">
-        <v>3.52792</v>
+        <v>3.568010000000001</v>
       </c>
       <c r="G90">
         <v>1.28</v>
@@ -8667,37 +8667,37 @@
         <v>0.167</v>
       </c>
       <c r="M90">
-        <v>0.8318835360000001</v>
+        <v>0.8413367580000002</v>
       </c>
       <c r="N90">
-        <v>-0.6648835360000001</v>
+        <v>-0.6743367580000001</v>
       </c>
       <c r="O90">
-        <v>-0.09973253040000001</v>
+        <v>-0.1011505137</v>
       </c>
       <c r="P90">
-        <v>-0.5651510056000001</v>
+        <v>-0.5731862443000001</v>
       </c>
       <c r="Q90">
-        <v>-0.4901510056000001</v>
+        <v>-0.4981862443000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6279337513157209</v>
+        <v>0.6808550014353321</v>
       </c>
       <c r="T90">
-        <v>7.587154267469453</v>
+        <v>8.276895564512133</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03011238823219119</v>
+        <v>0.02977404679138005</v>
       </c>
       <c r="W90">
-        <v>0.2286994988548493</v>
+        <v>0.2287792797665926</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2007492548812747</v>
+        <v>0.1984936452758671</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2785076091501539</v>
+        <v>0.2804076091501539</v>
       </c>
       <c r="C91">
-        <v>-1.445520632724012</v>
+        <v>-1.492433641592406</v>
       </c>
       <c r="D91">
-        <v>0.8424893672759889</v>
+        <v>0.8356663584075941</v>
       </c>
       <c r="E91">
-        <v>3.539010000000001</v>
+        <v>3.5791</v>
       </c>
       <c r="F91">
-        <v>3.568010000000001</v>
+        <v>3.6081</v>
       </c>
       <c r="G91">
         <v>1.28</v>
@@ -8749,37 +8749,37 @@
         <v>0.167</v>
       </c>
       <c r="M91">
-        <v>0.8413367580000002</v>
+        <v>0.8507899800000001</v>
       </c>
       <c r="N91">
-        <v>-0.6743367580000001</v>
+        <v>-0.68378998</v>
       </c>
       <c r="O91">
-        <v>-0.1011505137</v>
+        <v>-0.102568497</v>
       </c>
       <c r="P91">
-        <v>-0.5731862443000001</v>
+        <v>-0.581221483</v>
       </c>
       <c r="Q91">
-        <v>-0.4981862443000001</v>
+        <v>-0.506221483</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6808550014353321</v>
+        <v>0.7443605015788654</v>
       </c>
       <c r="T91">
-        <v>8.276895564512133</v>
+        <v>9.104585120963346</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02977404679138005</v>
+        <v>0.02944322404925361</v>
       </c>
       <c r="W91">
-        <v>0.2287792797665926</v>
+        <v>0.228857287769186</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1984936452758671</v>
+        <v>0.1962881603283575</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2804076091501539</v>
+        <v>0.2823076091501539</v>
       </c>
       <c r="C92">
-        <v>-1.492433641592406</v>
+        <v>-1.539237024247111</v>
       </c>
       <c r="D92">
-        <v>0.8356663584075941</v>
+        <v>0.8289529757528891</v>
       </c>
       <c r="E92">
-        <v>3.5791</v>
+        <v>3.619190000000001</v>
       </c>
       <c r="F92">
-        <v>3.6081</v>
+        <v>3.64819</v>
       </c>
       <c r="G92">
         <v>1.28</v>
@@ -8831,37 +8831,37 @@
         <v>0.167</v>
       </c>
       <c r="M92">
-        <v>0.8507899800000001</v>
+        <v>0.8602432020000002</v>
       </c>
       <c r="N92">
-        <v>-0.68378998</v>
+        <v>-0.6932432020000001</v>
       </c>
       <c r="O92">
-        <v>-0.102568497</v>
+        <v>-0.1039864803</v>
       </c>
       <c r="P92">
-        <v>-0.581221483</v>
+        <v>-0.5892567217000001</v>
       </c>
       <c r="Q92">
-        <v>-0.506221483</v>
+        <v>-0.5142567217000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7443605015788654</v>
+        <v>0.8219783350876282</v>
       </c>
       <c r="T92">
-        <v>9.104585120963346</v>
+        <v>10.11620568995927</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02944322404925361</v>
+        <v>0.02911967213662445</v>
       </c>
       <c r="W92">
-        <v>0.228857287769186</v>
+        <v>0.228933581310184</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1962881603283575</v>
+        <v>0.1941311475774964</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2823076091501539</v>
+        <v>0.284207609150154</v>
       </c>
       <c r="C93">
-        <v>-1.539237024247111</v>
+        <v>-1.585933401701023</v>
       </c>
       <c r="D93">
-        <v>0.8289529757528891</v>
+        <v>0.8223465982989774</v>
       </c>
       <c r="E93">
-        <v>3.619190000000001</v>
+        <v>3.659280000000001</v>
       </c>
       <c r="F93">
-        <v>3.64819</v>
+        <v>3.688280000000001</v>
       </c>
       <c r="G93">
         <v>1.28</v>
@@ -8913,37 +8913,37 @@
         <v>0.167</v>
       </c>
       <c r="M93">
-        <v>0.8602432020000002</v>
+        <v>0.8696964240000002</v>
       </c>
       <c r="N93">
-        <v>-0.6932432020000001</v>
+        <v>-0.7026964240000002</v>
       </c>
       <c r="O93">
-        <v>-0.1039864803</v>
+        <v>-0.1054044636</v>
       </c>
       <c r="P93">
-        <v>-0.5892567217000001</v>
+        <v>-0.5972919604000002</v>
       </c>
       <c r="Q93">
-        <v>-0.5142567217000001</v>
+        <v>-0.5222919604000003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8219783350876282</v>
+        <v>0.919000626973582</v>
       </c>
       <c r="T93">
-        <v>10.11620568995927</v>
+        <v>11.38073140120419</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02911967213662445</v>
+        <v>0.02880315396122635</v>
       </c>
       <c r="W93">
-        <v>0.228933581310184</v>
+        <v>0.2290082162959428</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1941311475774964</v>
+        <v>0.1920210264081758</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.284207609150154</v>
+        <v>0.286107609150154</v>
       </c>
       <c r="C94">
-        <v>-1.585933401701023</v>
+        <v>-1.632525312074538</v>
       </c>
       <c r="D94">
-        <v>0.8223465982989774</v>
+        <v>0.8158446879254622</v>
       </c>
       <c r="E94">
-        <v>3.659280000000001</v>
+        <v>3.69937</v>
       </c>
       <c r="F94">
-        <v>3.688280000000001</v>
+        <v>3.72837</v>
       </c>
       <c r="G94">
         <v>1.28</v>
@@ -8995,37 +8995,37 @@
         <v>0.167</v>
       </c>
       <c r="M94">
-        <v>0.8696964240000002</v>
+        <v>0.8791496460000001</v>
       </c>
       <c r="N94">
-        <v>-0.7026964240000002</v>
+        <v>-0.7121496460000001</v>
       </c>
       <c r="O94">
-        <v>-0.1054044636</v>
+        <v>-0.1068224469</v>
       </c>
       <c r="P94">
-        <v>-0.5972919604000002</v>
+        <v>-0.6053271991000001</v>
       </c>
       <c r="Q94">
-        <v>-0.5222919604000003</v>
+        <v>-0.5303271991000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.919000626973582</v>
+        <v>1.043743573684094</v>
       </c>
       <c r="T94">
-        <v>11.38073140120419</v>
+        <v>13.00655017280479</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02880315396122635</v>
+        <v>0.02849344262830995</v>
       </c>
       <c r="W94">
-        <v>0.2290082162959428</v>
+        <v>0.2290812462282445</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1920210264081758</v>
+        <v>0.189956284188733</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.286107609150154</v>
+        <v>0.2880076091501539</v>
       </c>
       <c r="C95">
-        <v>-1.632525312074538</v>
+        <v>-1.679015213846812</v>
       </c>
       <c r="D95">
-        <v>0.8158446879254622</v>
+        <v>0.8094447861531879</v>
       </c>
       <c r="E95">
-        <v>3.69937</v>
+        <v>3.739460000000001</v>
       </c>
       <c r="F95">
-        <v>3.72837</v>
+        <v>3.768460000000001</v>
       </c>
       <c r="G95">
         <v>1.28</v>
@@ -9077,37 +9077,37 @@
         <v>0.167</v>
       </c>
       <c r="M95">
-        <v>0.8791496460000001</v>
+        <v>0.8886028680000002</v>
       </c>
       <c r="N95">
-        <v>-0.7121496460000001</v>
+        <v>-0.7216028680000002</v>
       </c>
       <c r="O95">
-        <v>-0.1068224469</v>
+        <v>-0.1082404302</v>
       </c>
       <c r="P95">
-        <v>-0.6053271991000001</v>
+        <v>-0.6133624378000001</v>
       </c>
       <c r="Q95">
-        <v>-0.5303271991000001</v>
+        <v>-0.5383624378000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.043743573684094</v>
+        <v>1.210067502631443</v>
       </c>
       <c r="T95">
-        <v>13.00655017280479</v>
+        <v>15.17430853493892</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02849344262830995</v>
+        <v>0.02819032089822154</v>
       </c>
       <c r="W95">
-        <v>0.2290812462282445</v>
+        <v>0.2291527223321994</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.189956284188733</v>
+        <v>0.1879354726548103</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2880076091501539</v>
+        <v>0.289907609150154</v>
       </c>
       <c r="C96">
-        <v>-1.679015213846812</v>
+        <v>-1.725405488955177</v>
       </c>
       <c r="D96">
-        <v>0.8094447861531879</v>
+        <v>0.8031445110448237</v>
       </c>
       <c r="E96">
-        <v>3.739460000000001</v>
+        <v>3.779550000000001</v>
       </c>
       <c r="F96">
-        <v>3.768460000000001</v>
+        <v>3.808550000000001</v>
       </c>
       <c r="G96">
         <v>1.28</v>
@@ -9159,37 +9159,37 @@
         <v>0.167</v>
       </c>
       <c r="M96">
-        <v>0.8886028680000002</v>
+        <v>0.8980560900000002</v>
       </c>
       <c r="N96">
-        <v>-0.7216028680000002</v>
+        <v>-0.7310560900000002</v>
       </c>
       <c r="O96">
-        <v>-0.1082404302</v>
+        <v>-0.1096584135</v>
       </c>
       <c r="P96">
-        <v>-0.6133624378000001</v>
+        <v>-0.6213976765000001</v>
       </c>
       <c r="Q96">
-        <v>-0.5383624378000001</v>
+        <v>-0.5463976765000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.210067502631443</v>
+        <v>1.442921003157733</v>
       </c>
       <c r="T96">
-        <v>15.17430853493892</v>
+        <v>18.20917024192672</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02819032089822154</v>
+        <v>0.02789358067824026</v>
       </c>
       <c r="W96">
-        <v>0.2291527223321994</v>
+        <v>0.229222693676071</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1879354726548103</v>
+        <v>0.1859572045216018</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.289907609150154</v>
+        <v>0.2918076091501539</v>
       </c>
       <c r="C97">
-        <v>-1.725405488955177</v>
+        <v>-1.771698445750931</v>
       </c>
       <c r="D97">
-        <v>0.8031445110448237</v>
+        <v>0.7969415542490695</v>
       </c>
       <c r="E97">
-        <v>3.779550000000001</v>
+        <v>3.819640000000001</v>
       </c>
       <c r="F97">
-        <v>3.808550000000001</v>
+        <v>3.848640000000001</v>
       </c>
       <c r="G97">
         <v>1.28</v>
@@ -9241,37 +9241,37 @@
         <v>0.167</v>
       </c>
       <c r="M97">
-        <v>0.8980560900000002</v>
+        <v>0.9075093120000002</v>
       </c>
       <c r="N97">
-        <v>-0.7310560900000002</v>
+        <v>-0.7405093120000001</v>
       </c>
       <c r="O97">
-        <v>-0.1096584135</v>
+        <v>-0.1110763968</v>
       </c>
       <c r="P97">
-        <v>-0.6213976765000001</v>
+        <v>-0.6294329152000001</v>
       </c>
       <c r="Q97">
-        <v>-0.5463976765000002</v>
+        <v>-0.5544329152000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.442921003157733</v>
+        <v>1.792201253947166</v>
       </c>
       <c r="T97">
-        <v>18.20917024192672</v>
+        <v>22.7614628024084</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02789358067824026</v>
+        <v>0.02760302254617526</v>
       </c>
       <c r="W97">
-        <v>0.229222693676071</v>
+        <v>0.2292912072836119</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1859572045216018</v>
+        <v>0.184020150307835</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2918076091501539</v>
+        <v>0.2937076091501539</v>
       </c>
       <c r="C98">
-        <v>-1.771698445750931</v>
+        <v>-1.817896321819213</v>
       </c>
       <c r="D98">
-        <v>0.7969415542490695</v>
+        <v>0.7908336781807875</v>
       </c>
       <c r="E98">
-        <v>3.81964</v>
+        <v>3.85973</v>
       </c>
       <c r="F98">
-        <v>3.84864</v>
+        <v>3.88873</v>
       </c>
       <c r="G98">
         <v>1.28</v>
@@ -9323,37 +9323,37 @@
         <v>0.167</v>
       </c>
       <c r="M98">
-        <v>0.9075093120000001</v>
+        <v>0.9169625340000001</v>
       </c>
       <c r="N98">
-        <v>-0.740509312</v>
+        <v>-0.749962534</v>
       </c>
       <c r="O98">
-        <v>-0.1110763968</v>
+        <v>-0.1124943801</v>
       </c>
       <c r="P98">
-        <v>-0.6294329152</v>
+        <v>-0.6374681539</v>
       </c>
       <c r="Q98">
-        <v>-0.5544329152</v>
+        <v>-0.5624681539</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.792201253947161</v>
+        <v>2.374335005262882</v>
       </c>
       <c r="T98">
-        <v>22.76146280240834</v>
+        <v>30.34861706987779</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02760302254617526</v>
+        <v>0.02731845530343118</v>
       </c>
       <c r="W98">
-        <v>0.2292912072836119</v>
+        <v>0.2293583082394509</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1840201503078351</v>
+        <v>0.182123035356208</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2937076091501539</v>
+        <v>0.2956076091501539</v>
       </c>
       <c r="C99">
-        <v>-1.817896321819213</v>
+        <v>-1.864001286670185</v>
       </c>
       <c r="D99">
-        <v>0.7908336781807875</v>
+        <v>0.7848187133298157</v>
       </c>
       <c r="E99">
-        <v>3.85973</v>
+        <v>3.899820000000001</v>
       </c>
       <c r="F99">
-        <v>3.88873</v>
+        <v>3.92882</v>
       </c>
       <c r="G99">
         <v>1.28</v>
@@ -9405,37 +9405,37 @@
         <v>0.167</v>
       </c>
       <c r="M99">
-        <v>0.9169625340000001</v>
+        <v>0.9264157560000001</v>
       </c>
       <c r="N99">
-        <v>-0.749962534</v>
+        <v>-0.7594157560000001</v>
       </c>
       <c r="O99">
-        <v>-0.1124943801</v>
+        <v>-0.1139123634</v>
       </c>
       <c r="P99">
-        <v>-0.6374681539</v>
+        <v>-0.6455033926000001</v>
       </c>
       <c r="Q99">
-        <v>-0.5624681539</v>
+        <v>-0.5705033926000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.374335005262882</v>
+        <v>3.538602507894323</v>
       </c>
       <c r="T99">
-        <v>30.34861706987779</v>
+        <v>45.52292560481668</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02731845530343118</v>
+        <v>0.02703969555543699</v>
       </c>
       <c r="W99">
-        <v>0.2293583082394509</v>
+        <v>0.229424039788028</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.182123035356208</v>
+        <v>0.1802646370362466</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2956076091501539</v>
+        <v>0.297507609150154</v>
       </c>
       <c r="C100">
-        <v>-1.864001286670185</v>
+        <v>-1.910015444308332</v>
       </c>
       <c r="D100">
-        <v>0.7848187133298157</v>
+        <v>0.7788945556916684</v>
       </c>
       <c r="E100">
-        <v>3.899820000000001</v>
+        <v>3.93991</v>
       </c>
       <c r="F100">
-        <v>3.92882</v>
+        <v>3.96891</v>
       </c>
       <c r="G100">
         <v>1.28</v>
@@ -9487,37 +9487,37 @@
         <v>0.167</v>
       </c>
       <c r="M100">
-        <v>0.9264157560000001</v>
+        <v>0.9358689780000001</v>
       </c>
       <c r="N100">
-        <v>-0.7594157560000001</v>
+        <v>-0.7688689780000001</v>
       </c>
       <c r="O100">
-        <v>-0.1139123634</v>
+        <v>-0.1153303467</v>
       </c>
       <c r="P100">
-        <v>-0.6455033926000001</v>
+        <v>-0.6535386313000001</v>
       </c>
       <c r="Q100">
-        <v>-0.5705033926000002</v>
+        <v>-0.5785386313000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.538602507894323</v>
+        <v>7.031405015788646</v>
       </c>
       <c r="T100">
-        <v>45.52292560481668</v>
+        <v>91.04585120963337</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02703969555543699</v>
+        <v>0.02676656731750328</v>
       </c>
       <c r="W100">
-        <v>0.229424039788028</v>
+        <v>0.2294884434265327</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1802646370362466</v>
+        <v>0.1784437821166885</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.297507609150154</v>
-      </c>
-      <c r="C101">
-        <v>-1.910015444308332</v>
-      </c>
-      <c r="D101">
-        <v>0.7788945556916684</v>
-      </c>
-      <c r="E101">
-        <v>3.93991</v>
-      </c>
-      <c r="F101">
-        <v>3.96891</v>
-      </c>
-      <c r="G101">
-        <v>1.28</v>
-      </c>
-      <c r="H101">
-        <v>3.98</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.242</v>
-      </c>
-      <c r="K101">
-        <v>0.07499999999999998</v>
-      </c>
-      <c r="L101">
-        <v>0.167</v>
-      </c>
-      <c r="M101">
-        <v>0.9358689780000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.7688689780000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.1153303467</v>
-      </c>
-      <c r="P101">
-        <v>-0.6535386313000001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.5785386313000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.031405015788646</v>
-      </c>
-      <c r="T101">
-        <v>91.04585120963337</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02676656731750328</v>
-      </c>
-      <c r="W101">
-        <v>0.2294884434265327</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1784437821166885</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
